--- a/CommonDataModel.xlsx
+++ b/CommonDataModel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doguk\OneDrive\Desktop\DT4H\Repositories\common-data-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEE46FD-D748-4606-A98B-982A6CDC0A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1097F06-BDF1-4D53-8626-E9B1E4B45FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="901" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-900" windowWidth="29040" windowHeight="15720" tabRatio="901" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="10" r:id="rId1"/>
@@ -864,7 +864,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4737" uniqueCount="2047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4742" uniqueCount="2048">
   <si>
     <t>Required</t>
   </si>
@@ -7025,6 +7025,9 @@
   </si>
   <si>
     <t>Patient transported by law enforcement.</t>
+  </si>
+  <si>
+    <t>The preceding encounter that leads into the current one. For example, this can be used to indicate an emergency visit that resulted in a subsequent hospitalization.</t>
   </si>
 </sst>
 </file>
@@ -7291,7 +7294,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -7390,9 +7393,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7402,14 +7406,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7418,11 +7424,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Explanatory Text" xfId="2" builtinId="53"/>
@@ -7723,10 +7724,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="66"/>
+      <c r="C2" s="67"/>
       <c r="E2" s="17" t="s">
         <v>1</v>
       </c>
@@ -7778,14 +7779,14 @@
     </row>
     <row r="6" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="E7" s="67" t="s">
+      <c r="C7" s="67"/>
+      <c r="E7" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="67"/>
+      <c r="F7" s="68"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
@@ -8050,21 +8051,21 @@
       <c r="E12" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>366</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="33" t="s">
         <v>367</v>
       </c>
@@ -8077,10 +8078,10 @@
       <c r="B14" t="s">
         <v>368</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="33" t="s">
         <v>369</v>
       </c>
@@ -8093,10 +8094,10 @@
       <c r="B15" t="s">
         <v>370</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="33" t="s">
         <v>371</v>
       </c>
@@ -8109,10 +8110,10 @@
       <c r="B16" t="s">
         <v>372</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="33" t="s">
         <v>373</v>
       </c>
@@ -8125,10 +8126,10 @@
       <c r="B17" t="s">
         <v>374</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="33" t="s">
         <v>375</v>
       </c>
@@ -8635,12 +8636,12 @@
       <c r="E12" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -8649,10 +8650,10 @@
       <c r="B13" s="41" t="s">
         <v>389</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="33"/>
       <c r="F13" s="63"/>
       <c r="G13" s="64"/>
@@ -8666,10 +8667,10 @@
       <c r="B14" s="41" t="s">
         <v>391</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="33"/>
       <c r="F14" s="63"/>
       <c r="G14" s="64"/>
@@ -8683,10 +8684,10 @@
       <c r="B15" s="41" t="s">
         <v>393</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="33"/>
       <c r="F15" s="63"/>
       <c r="G15" s="64"/>
@@ -8700,10 +8701,10 @@
       <c r="B16" s="41" t="s">
         <v>395</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="33"/>
       <c r="F16" s="63"/>
       <c r="G16" s="64"/>
@@ -8717,10 +8718,10 @@
       <c r="B17" s="41" t="s">
         <v>397</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="33"/>
       <c r="F17" s="63"/>
       <c r="G17" s="64"/>
@@ -8734,10 +8735,10 @@
       <c r="B18" s="41" t="s">
         <v>399</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="33"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64"/>
@@ -8751,10 +8752,10 @@
       <c r="B19" s="41" t="s">
         <v>1328</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64"/>
@@ -8768,10 +8769,10 @@
       <c r="B20" s="41" t="s">
         <v>1329</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64"/>
@@ -8785,24 +8786,13 @@
       <c r="B21" s="51">
         <v>43381005</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="F12:I12"/>
@@ -8810,6 +8800,17 @@
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:I20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9081,12 +9082,12 @@
       <c r="E12" s="32" t="s">
         <v>594</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
       <c r="L12" t="s">
         <v>595</v>
       </c>
@@ -9098,10 +9099,10 @@
       <c r="B13">
         <v>267039000</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="33" t="s">
         <v>599</v>
       </c>
@@ -9120,10 +9121,10 @@
       <c r="B14">
         <v>389026000</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="33" t="s">
         <v>599</v>
       </c>
@@ -9142,10 +9143,10 @@
       <c r="B15">
         <v>267036007</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="33" t="s">
         <v>606</v>
       </c>
@@ -9164,10 +9165,10 @@
       <c r="B16">
         <v>59495006</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="33" t="s">
         <v>599</v>
       </c>
@@ -9186,10 +9187,10 @@
       <c r="B17">
         <v>29857009</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="33" t="s">
         <v>606</v>
       </c>
@@ -9208,10 +9209,10 @@
       <c r="B18">
         <v>90480005</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="33" t="s">
         <v>599</v>
       </c>
@@ -9230,10 +9231,10 @@
       <c r="B19">
         <v>35489007</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33" t="s">
         <v>606</v>
       </c>
@@ -9252,10 +9253,10 @@
       <c r="B20">
         <v>404640003</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33" t="s">
         <v>606</v>
       </c>
@@ -9274,10 +9275,10 @@
       <c r="B21">
         <v>22447003</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="33" t="s">
         <v>599</v>
       </c>
@@ -9293,10 +9294,10 @@
       <c r="B22">
         <v>84229001</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="33" t="s">
         <v>606</v>
       </c>
@@ -9312,10 +9313,10 @@
       <c r="B23">
         <v>72196001</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="62"/>
       <c r="E23" s="33" t="s">
         <v>599</v>
       </c>
@@ -9331,10 +9332,10 @@
       <c r="B24">
         <v>80515008</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="68"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="33" t="s">
         <v>599</v>
       </c>
@@ -9350,10 +9351,10 @@
       <c r="B25">
         <v>361137007</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="68"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="33" t="s">
         <v>597</v>
       </c>
@@ -9369,10 +9370,10 @@
       <c r="B26">
         <v>79890006</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D26" s="68"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="33" t="s">
         <v>606</v>
       </c>
@@ -9388,10 +9389,10 @@
       <c r="B27">
         <v>161947006</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D27" s="68"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="33" t="s">
         <v>606</v>
       </c>
@@ -9407,10 +9408,10 @@
       <c r="B28">
         <v>83128009</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D28" s="68"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="33" t="s">
         <v>599</v>
       </c>
@@ -9426,10 +9427,10 @@
       <c r="B29">
         <v>62744007</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D29" s="68"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="33" t="s">
         <v>606</v>
       </c>
@@ -9445,10 +9446,10 @@
       <c r="B30">
         <v>80313002</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="68"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="33" t="s">
         <v>606</v>
       </c>
@@ -9464,10 +9465,10 @@
       <c r="B31">
         <v>55442000</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="68"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="33" t="s">
         <v>606</v>
       </c>
@@ -9483,10 +9484,10 @@
       <c r="B32">
         <v>271809000</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D32" s="68"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="33" t="s">
         <v>599</v>
       </c>
@@ -9502,10 +9503,10 @@
       <c r="B33">
         <v>60046008</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="68"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="33" t="s">
         <v>600</v>
       </c>
@@ -9521,10 +9522,10 @@
       <c r="B34">
         <v>48409008</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="68"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="33" t="s">
         <v>599</v>
       </c>
@@ -9540,10 +9541,10 @@
       <c r="B35">
         <v>267044007</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="62"/>
       <c r="E35" s="33" t="s">
         <v>606</v>
       </c>
@@ -9559,10 +9560,10 @@
       <c r="B36">
         <v>272030005</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D36" s="68"/>
+      <c r="D36" s="62"/>
       <c r="E36" s="33" t="s">
         <v>606</v>
       </c>
@@ -9578,10 +9579,10 @@
       <c r="B37">
         <v>3424008</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="68"/>
+      <c r="D37" s="62"/>
       <c r="E37" s="33" t="s">
         <v>597</v>
       </c>
@@ -9597,10 +9598,10 @@
       <c r="B38">
         <v>271823003</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="68"/>
+      <c r="D38" s="62"/>
       <c r="E38" s="33" t="s">
         <v>597</v>
       </c>
@@ -9616,10 +9617,10 @@
       <c r="B39">
         <v>1285004</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D39" s="68"/>
+      <c r="D39" s="62"/>
       <c r="E39" s="33" t="s">
         <v>599</v>
       </c>
@@ -9635,10 +9636,10 @@
       <c r="B40">
         <v>8943002</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="68"/>
+      <c r="D40" s="62"/>
       <c r="E40" s="33" t="s">
         <v>597</v>
       </c>
@@ -9654,10 +9655,10 @@
       <c r="B41">
         <v>89362005</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D41" s="68"/>
+      <c r="D41" s="62"/>
       <c r="E41" s="33" t="s">
         <v>597</v>
       </c>
@@ -9668,14 +9669,41 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
@@ -9692,41 +9720,14 @@
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F32:I32"/>
     <mergeCell ref="F33:I33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E41" xr:uid="{14C408A9-075A-4B77-84C3-9F689D082B68}">
@@ -10058,12 +10059,12 @@
       <c r="E15" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
     </row>
     <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -10072,10 +10073,10 @@
       <c r="B16" s="41" t="s">
         <v>314</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="34" t="s">
         <v>419</v>
       </c>
@@ -10091,10 +10092,10 @@
       <c r="B17" s="41" t="s">
         <v>421</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="34" t="s">
         <v>422</v>
       </c>
@@ -10110,10 +10111,10 @@
       <c r="B18" s="41" t="s">
         <v>424</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="34" t="s">
         <v>425</v>
       </c>
@@ -10129,10 +10130,10 @@
       <c r="B19" s="41" t="s">
         <v>427</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="5" t="s">
         <v>428</v>
       </c>
@@ -10148,10 +10149,10 @@
       <c r="B20" s="41" t="s">
         <v>430</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="5" t="s">
         <v>431</v>
       </c>
@@ -10167,10 +10168,10 @@
       <c r="B21" s="41" t="s">
         <v>433</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="5" t="s">
         <v>434</v>
       </c>
@@ -10186,10 +10187,10 @@
       <c r="B22" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="5" t="s">
         <v>435</v>
       </c>
@@ -10230,12 +10231,12 @@
       <c r="E25" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -10244,10 +10245,10 @@
       <c r="B26" s="41" t="s">
         <v>440</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D26" s="68"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="34" t="s">
         <v>441</v>
       </c>
@@ -10263,10 +10264,10 @@
       <c r="B27" s="41" t="s">
         <v>443</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="68"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="34" t="s">
         <v>444</v>
       </c>
@@ -10282,10 +10283,10 @@
       <c r="B28" s="41" t="s">
         <v>446</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D28" s="68"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="34" t="s">
         <v>447</v>
       </c>
@@ -10301,10 +10302,10 @@
       <c r="B29" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D29" s="68"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="5" t="s">
         <v>448</v>
       </c>
@@ -10342,12 +10343,12 @@
       <c r="E32" s="32" t="s">
         <v>451</v>
       </c>
-      <c r="F32" s="62" t="s">
+      <c r="F32" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -10356,10 +10357,10 @@
       <c r="B33" s="41" t="s">
         <v>453</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="68"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="34"/>
       <c r="F33" s="63"/>
       <c r="G33" s="64"/>
@@ -10373,10 +10374,10 @@
       <c r="B34" s="41" t="s">
         <v>455</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="68"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="34"/>
       <c r="F34" s="63"/>
       <c r="G34" s="64"/>
@@ -10390,10 +10391,10 @@
       <c r="B35" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="62"/>
       <c r="E35" s="34"/>
       <c r="F35" s="63"/>
       <c r="G35" s="64"/>
@@ -10422,17 +10423,17 @@
       <c r="B39" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="65" t="s">
         <v>461</v>
       </c>
-      <c r="D39" s="62"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="73" t="s">
+      <c r="D39" s="65"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="72" t="s">
         <v>462</v>
       </c>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="72"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="42" t="s">
@@ -10441,11 +10442,11 @@
       <c r="B40" s="42" t="s">
         <v>464</v>
       </c>
-      <c r="C40" s="71" t="s">
+      <c r="C40" s="69" t="s">
         <v>465</v>
       </c>
-      <c r="D40" s="71"/>
-      <c r="E40" s="72"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="70"/>
       <c r="F40" s="63"/>
       <c r="G40" s="64"/>
       <c r="H40" s="64"/>
@@ -10458,11 +10459,11 @@
       <c r="B41" s="42" t="s">
         <v>467</v>
       </c>
-      <c r="C41" s="71" t="s">
+      <c r="C41" s="69" t="s">
         <v>468</v>
       </c>
-      <c r="D41" s="71"/>
-      <c r="E41" s="72"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="70"/>
       <c r="F41" s="63"/>
       <c r="G41" s="64"/>
       <c r="H41" s="64"/>
@@ -10475,11 +10476,11 @@
       <c r="B42" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="C42" s="71" t="s">
+      <c r="C42" s="69" t="s">
         <v>471</v>
       </c>
-      <c r="D42" s="71"/>
-      <c r="E42" s="72"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="70"/>
       <c r="F42" s="63"/>
       <c r="G42" s="64"/>
       <c r="H42" s="64"/>
@@ -10492,11 +10493,11 @@
       <c r="B43" s="42" t="s">
         <v>473</v>
       </c>
-      <c r="C43" s="71" t="s">
+      <c r="C43" s="69" t="s">
         <v>2011</v>
       </c>
-      <c r="D43" s="71"/>
-      <c r="E43" s="72"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="63"/>
       <c r="G43" s="64"/>
       <c r="H43" s="64"/>
@@ -10509,11 +10510,11 @@
       <c r="B44" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="C44" s="71" t="s">
+      <c r="C44" s="69" t="s">
         <v>476</v>
       </c>
-      <c r="D44" s="71"/>
-      <c r="E44" s="72"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="70"/>
       <c r="F44" s="63"/>
       <c r="G44" s="64"/>
       <c r="H44" s="64"/>
@@ -10526,11 +10527,11 @@
       <c r="B45" s="42" t="s">
         <v>478</v>
       </c>
-      <c r="C45" s="71" t="s">
+      <c r="C45" s="69" t="s">
         <v>479</v>
       </c>
-      <c r="D45" s="71"/>
-      <c r="E45" s="72"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="70"/>
       <c r="F45" s="63"/>
       <c r="G45" s="64"/>
       <c r="H45" s="64"/>
@@ -10543,11 +10544,11 @@
       <c r="B46" s="42" t="s">
         <v>481</v>
       </c>
-      <c r="C46" s="71" t="s">
+      <c r="C46" s="69" t="s">
         <v>482</v>
       </c>
-      <c r="D46" s="71"/>
-      <c r="E46" s="72"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="70"/>
       <c r="F46" s="63"/>
       <c r="G46" s="64"/>
       <c r="H46" s="64"/>
@@ -10560,11 +10561,11 @@
       <c r="B47" s="42" t="s">
         <v>484</v>
       </c>
-      <c r="C47" s="71" t="s">
+      <c r="C47" s="69" t="s">
         <v>2021</v>
       </c>
-      <c r="D47" s="71"/>
-      <c r="E47" s="72"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="70"/>
       <c r="F47" s="63"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
@@ -10577,11 +10578,11 @@
       <c r="B48" s="42" t="s">
         <v>485</v>
       </c>
-      <c r="C48" s="71" t="s">
+      <c r="C48" s="69" t="s">
         <v>2012</v>
       </c>
-      <c r="D48" s="71"/>
-      <c r="E48" s="72"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="70"/>
       <c r="F48" s="63"/>
       <c r="G48" s="64"/>
       <c r="H48" s="64"/>
@@ -10594,11 +10595,11 @@
       <c r="B49" s="42" t="s">
         <v>487</v>
       </c>
-      <c r="C49" s="71" t="s">
+      <c r="C49" s="69" t="s">
         <v>488</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="72"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="70"/>
       <c r="F49" s="63"/>
       <c r="G49" s="64"/>
       <c r="H49" s="64"/>
@@ -10611,11 +10612,11 @@
       <c r="B50" s="42" t="s">
         <v>490</v>
       </c>
-      <c r="C50" s="71" t="s">
+      <c r="C50" s="69" t="s">
         <v>491</v>
       </c>
-      <c r="D50" s="71"/>
-      <c r="E50" s="72"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="70"/>
       <c r="F50" s="63"/>
       <c r="G50" s="64"/>
       <c r="H50" s="64"/>
@@ -10628,11 +10629,11 @@
       <c r="B51" s="42" t="s">
         <v>493</v>
       </c>
-      <c r="C51" s="71" t="s">
+      <c r="C51" s="69" t="s">
         <v>494</v>
       </c>
-      <c r="D51" s="71"/>
-      <c r="E51" s="72"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="70"/>
       <c r="F51" s="63"/>
       <c r="G51" s="64"/>
       <c r="H51" s="64"/>
@@ -10645,11 +10646,11 @@
       <c r="B52" s="42" t="s">
         <v>496</v>
       </c>
-      <c r="C52" s="71" t="s">
+      <c r="C52" s="69" t="s">
         <v>497</v>
       </c>
-      <c r="D52" s="71"/>
-      <c r="E52" s="72"/>
+      <c r="D52" s="69"/>
+      <c r="E52" s="70"/>
       <c r="F52" s="63"/>
       <c r="G52" s="64"/>
       <c r="H52" s="64"/>
@@ -10662,11 +10663,11 @@
       <c r="B53" s="42" t="s">
         <v>499</v>
       </c>
-      <c r="C53" s="71" t="s">
+      <c r="C53" s="69" t="s">
         <v>500</v>
       </c>
-      <c r="D53" s="71"/>
-      <c r="E53" s="72"/>
+      <c r="D53" s="69"/>
+      <c r="E53" s="70"/>
       <c r="F53" s="63"/>
       <c r="G53" s="64"/>
       <c r="H53" s="64"/>
@@ -10679,11 +10680,11 @@
       <c r="B54" s="42" t="s">
         <v>502</v>
       </c>
-      <c r="C54" s="71" t="s">
+      <c r="C54" s="69" t="s">
         <v>503</v>
       </c>
-      <c r="D54" s="71"/>
-      <c r="E54" s="72"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="70"/>
       <c r="F54" s="63"/>
       <c r="G54" s="64"/>
       <c r="H54" s="64"/>
@@ -10696,11 +10697,11 @@
       <c r="B55" s="42" t="s">
         <v>505</v>
       </c>
-      <c r="C55" s="71" t="s">
+      <c r="C55" s="69" t="s">
         <v>506</v>
       </c>
-      <c r="D55" s="71"/>
-      <c r="E55" s="72"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="70"/>
       <c r="F55" s="63"/>
       <c r="G55" s="64"/>
       <c r="H55" s="64"/>
@@ -10713,11 +10714,11 @@
       <c r="B56" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="C56" s="71" t="s">
+      <c r="C56" s="69" t="s">
         <v>509</v>
       </c>
-      <c r="D56" s="71"/>
-      <c r="E56" s="72"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="70"/>
       <c r="F56" s="63"/>
       <c r="G56" s="64"/>
       <c r="H56" s="64"/>
@@ -10730,11 +10731,11 @@
       <c r="B57" s="42" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="71" t="s">
+      <c r="C57" s="69" t="s">
         <v>512</v>
       </c>
-      <c r="D57" s="71"/>
-      <c r="E57" s="72"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="70"/>
       <c r="F57" s="63"/>
       <c r="G57" s="64"/>
       <c r="H57" s="64"/>
@@ -10747,11 +10748,11 @@
       <c r="B58" s="42" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="71" t="s">
+      <c r="C58" s="69" t="s">
         <v>515</v>
       </c>
-      <c r="D58" s="71"/>
-      <c r="E58" s="72"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="70"/>
       <c r="F58" s="63"/>
       <c r="G58" s="64"/>
       <c r="H58" s="64"/>
@@ -10764,11 +10765,11 @@
       <c r="B59" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="C59" s="71" t="s">
+      <c r="C59" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="D59" s="71"/>
-      <c r="E59" s="72"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="70"/>
       <c r="F59" s="63"/>
       <c r="G59" s="64"/>
       <c r="H59" s="64"/>
@@ -10781,11 +10782,11 @@
       <c r="B60" s="42" t="s">
         <v>520</v>
       </c>
-      <c r="C60" s="71" t="s">
+      <c r="C60" s="69" t="s">
         <v>521</v>
       </c>
-      <c r="D60" s="71"/>
-      <c r="E60" s="72"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="70"/>
       <c r="F60" s="63"/>
       <c r="G60" s="64"/>
       <c r="H60" s="64"/>
@@ -10798,11 +10799,11 @@
       <c r="B61" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="C61" s="71" t="s">
+      <c r="C61" s="69" t="s">
         <v>524</v>
       </c>
-      <c r="D61" s="71"/>
-      <c r="E61" s="72"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="70"/>
       <c r="F61" s="63"/>
       <c r="G61" s="64"/>
       <c r="H61" s="64"/>
@@ -10815,11 +10816,11 @@
       <c r="B62" s="42" t="s">
         <v>526</v>
       </c>
-      <c r="C62" s="71" t="s">
+      <c r="C62" s="69" t="s">
         <v>527</v>
       </c>
-      <c r="D62" s="71"/>
-      <c r="E62" s="72"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="70"/>
       <c r="F62" s="63"/>
       <c r="G62" s="64"/>
       <c r="H62" s="64"/>
@@ -10832,11 +10833,11 @@
       <c r="B63" s="42" t="s">
         <v>529</v>
       </c>
-      <c r="C63" s="71" t="s">
+      <c r="C63" s="69" t="s">
         <v>530</v>
       </c>
-      <c r="D63" s="71"/>
-      <c r="E63" s="72"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="70"/>
       <c r="F63" s="63"/>
       <c r="G63" s="64"/>
       <c r="H63" s="64"/>
@@ -10849,11 +10850,11 @@
       <c r="B64" s="42" t="s">
         <v>531</v>
       </c>
-      <c r="C64" s="71" t="s">
+      <c r="C64" s="69" t="s">
         <v>532</v>
       </c>
-      <c r="D64" s="71"/>
-      <c r="E64" s="72"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="70"/>
       <c r="F64" s="63"/>
       <c r="G64" s="64"/>
       <c r="H64" s="64"/>
@@ -10866,11 +10867,11 @@
       <c r="B65" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="C65" s="71" t="s">
+      <c r="C65" s="69" t="s">
         <v>535</v>
       </c>
-      <c r="D65" s="71"/>
-      <c r="E65" s="72"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="70"/>
       <c r="F65" s="63"/>
       <c r="G65" s="64"/>
       <c r="H65" s="64"/>
@@ -10883,11 +10884,11 @@
       <c r="B66" s="42" t="s">
         <v>537</v>
       </c>
-      <c r="C66" s="71" t="s">
+      <c r="C66" s="69" t="s">
         <v>2013</v>
       </c>
-      <c r="D66" s="71"/>
-      <c r="E66" s="72"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="70"/>
       <c r="F66" s="63"/>
       <c r="G66" s="64"/>
       <c r="H66" s="64"/>
@@ -10900,11 +10901,11 @@
       <c r="B67" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="C67" s="71" t="s">
+      <c r="C67" s="69" t="s">
         <v>540</v>
       </c>
-      <c r="D67" s="71"/>
-      <c r="E67" s="72"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="70"/>
       <c r="F67" s="63"/>
       <c r="G67" s="64"/>
       <c r="H67" s="64"/>
@@ -10917,11 +10918,11 @@
       <c r="B68" s="42" t="s">
         <v>542</v>
       </c>
-      <c r="C68" s="71" t="s">
+      <c r="C68" s="69" t="s">
         <v>543</v>
       </c>
-      <c r="D68" s="71"/>
-      <c r="E68" s="72"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="70"/>
       <c r="F68" s="63"/>
       <c r="G68" s="64"/>
       <c r="H68" s="64"/>
@@ -10934,11 +10935,11 @@
       <c r="B69" s="42" t="s">
         <v>545</v>
       </c>
-      <c r="C69" s="71" t="s">
+      <c r="C69" s="69" t="s">
         <v>546</v>
       </c>
-      <c r="D69" s="71"/>
-      <c r="E69" s="72"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="70"/>
       <c r="F69" s="63"/>
       <c r="G69" s="64"/>
       <c r="H69" s="64"/>
@@ -10951,11 +10952,11 @@
       <c r="B70" s="42" t="s">
         <v>548</v>
       </c>
-      <c r="C70" s="71" t="s">
+      <c r="C70" s="69" t="s">
         <v>549</v>
       </c>
-      <c r="D70" s="71"/>
-      <c r="E70" s="72"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="70"/>
       <c r="F70" s="63"/>
       <c r="G70" s="64"/>
       <c r="H70" s="64"/>
@@ -10968,11 +10969,11 @@
       <c r="B71" s="42" t="s">
         <v>551</v>
       </c>
-      <c r="C71" s="71" t="s">
+      <c r="C71" s="69" t="s">
         <v>552</v>
       </c>
-      <c r="D71" s="71"/>
-      <c r="E71" s="72"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="70"/>
       <c r="F71" s="63"/>
       <c r="G71" s="64"/>
       <c r="H71" s="64"/>
@@ -10985,11 +10986,11 @@
       <c r="B72" s="42" t="s">
         <v>554</v>
       </c>
-      <c r="C72" s="71" t="s">
+      <c r="C72" s="69" t="s">
         <v>555</v>
       </c>
-      <c r="D72" s="71"/>
-      <c r="E72" s="72"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="70"/>
       <c r="F72" s="63"/>
       <c r="G72" s="64"/>
       <c r="H72" s="64"/>
@@ -11002,11 +11003,11 @@
       <c r="B73" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="C73" s="71" t="s">
+      <c r="C73" s="69" t="s">
         <v>558</v>
       </c>
-      <c r="D73" s="71"/>
-      <c r="E73" s="72"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="70"/>
       <c r="F73" s="63"/>
       <c r="G73" s="64"/>
       <c r="H73" s="64"/>
@@ -11019,11 +11020,11 @@
       <c r="B74" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="C74" s="71" t="s">
+      <c r="C74" s="69" t="s">
         <v>561</v>
       </c>
-      <c r="D74" s="71"/>
-      <c r="E74" s="72"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="70"/>
       <c r="F74" s="63"/>
       <c r="G74" s="64"/>
       <c r="H74" s="64"/>
@@ -11036,11 +11037,11 @@
       <c r="B75" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="C75" s="71" t="s">
+      <c r="C75" s="69" t="s">
         <v>564</v>
       </c>
-      <c r="D75" s="71"/>
-      <c r="E75" s="72"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="70"/>
       <c r="F75" s="63"/>
       <c r="G75" s="64"/>
       <c r="H75" s="64"/>
@@ -11053,11 +11054,11 @@
       <c r="B76" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="C76" s="71" t="s">
+      <c r="C76" s="69" t="s">
         <v>567</v>
       </c>
-      <c r="D76" s="71"/>
-      <c r="E76" s="72"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="70"/>
       <c r="F76" s="63"/>
       <c r="G76" s="64"/>
       <c r="H76" s="64"/>
@@ -11070,11 +11071,11 @@
       <c r="B77" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="C77" s="71" t="s">
+      <c r="C77" s="69" t="s">
         <v>570</v>
       </c>
-      <c r="D77" s="71"/>
-      <c r="E77" s="72"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="70"/>
       <c r="F77" s="63"/>
       <c r="G77" s="64"/>
       <c r="H77" s="64"/>
@@ -11087,11 +11088,11 @@
       <c r="B78" s="42" t="s">
         <v>572</v>
       </c>
-      <c r="C78" s="71" t="s">
+      <c r="C78" s="69" t="s">
         <v>573</v>
       </c>
-      <c r="D78" s="71"/>
-      <c r="E78" s="72"/>
+      <c r="D78" s="69"/>
+      <c r="E78" s="70"/>
       <c r="F78" s="63"/>
       <c r="G78" s="64"/>
       <c r="H78" s="64"/>
@@ -11104,11 +11105,11 @@
       <c r="B79" s="42" t="s">
         <v>575</v>
       </c>
-      <c r="C79" s="71" t="s">
+      <c r="C79" s="69" t="s">
         <v>576</v>
       </c>
-      <c r="D79" s="71"/>
-      <c r="E79" s="72"/>
+      <c r="D79" s="69"/>
+      <c r="E79" s="70"/>
       <c r="F79" s="63"/>
       <c r="G79" s="64"/>
       <c r="H79" s="64"/>
@@ -11121,11 +11122,11 @@
       <c r="B80" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="C80" s="71" t="s">
+      <c r="C80" s="69" t="s">
         <v>579</v>
       </c>
-      <c r="D80" s="71"/>
-      <c r="E80" s="72"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="70"/>
       <c r="F80" s="63"/>
       <c r="G80" s="64"/>
       <c r="H80" s="64"/>
@@ -11138,11 +11139,11 @@
       <c r="B81" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="C81" s="71" t="s">
+      <c r="C81" s="69" t="s">
         <v>582</v>
       </c>
-      <c r="D81" s="71"/>
-      <c r="E81" s="72"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="70"/>
       <c r="F81" s="63"/>
       <c r="G81" s="64"/>
       <c r="H81" s="64"/>
@@ -11155,11 +11156,11 @@
       <c r="B82" t="s">
         <v>2018</v>
       </c>
-      <c r="C82" s="69" t="s">
+      <c r="C82" s="73" t="s">
         <v>2015</v>
       </c>
-      <c r="D82" s="69"/>
-      <c r="E82" s="69"/>
+      <c r="D82" s="73"/>
+      <c r="E82" s="73"/>
       <c r="F82" s="63"/>
       <c r="G82" s="64"/>
       <c r="H82" s="64"/>
@@ -11172,11 +11173,11 @@
       <c r="B83" t="s">
         <v>2019</v>
       </c>
-      <c r="C83" s="69" t="s">
+      <c r="C83" s="73" t="s">
         <v>2017</v>
       </c>
-      <c r="D83" s="69"/>
-      <c r="E83" s="69"/>
+      <c r="D83" s="73"/>
+      <c r="E83" s="73"/>
       <c r="F83" s="63"/>
       <c r="G83" s="64"/>
       <c r="H83" s="64"/>
@@ -11184,36 +11185,73 @@
     </row>
   </sheetData>
   <mergeCells count="121">
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F70:I70"/>
-    <mergeCell ref="F71:I71"/>
-    <mergeCell ref="F72:I72"/>
-    <mergeCell ref="F73:I73"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="F67:I67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="F69:I69"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="F82:I82"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
     <mergeCell ref="C51:E51"/>
     <mergeCell ref="F48:I48"/>
     <mergeCell ref="F49:I49"/>
@@ -11238,73 +11276,36 @@
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="F82:I82"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F70:I70"/>
+    <mergeCell ref="F71:I71"/>
+    <mergeCell ref="F72:I72"/>
+    <mergeCell ref="F73:I73"/>
+    <mergeCell ref="F74:I74"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12009,12 +12010,12 @@
       <c r="F12" s="7" t="s">
         <v>1805</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -12023,10 +12024,10 @@
       <c r="B13" t="s">
         <v>648</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="33" t="s">
         <v>649</v>
       </c>
@@ -12042,10 +12043,10 @@
       <c r="B14" t="s">
         <v>651</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="33" t="s">
         <v>652</v>
       </c>
@@ -12061,10 +12062,10 @@
       <c r="B15" t="s">
         <v>654</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="33" t="s">
         <v>655</v>
       </c>
@@ -12080,10 +12081,10 @@
       <c r="B16" t="s">
         <v>657</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="33" t="s">
         <v>658</v>
       </c>
@@ -12099,10 +12100,10 @@
       <c r="B17" t="s">
         <v>660</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="33" t="s">
         <v>661</v>
       </c>
@@ -12118,10 +12119,10 @@
       <c r="B18" t="s">
         <v>663</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="33" t="s">
         <v>661</v>
       </c>
@@ -12137,10 +12138,10 @@
       <c r="B19" t="s">
         <v>1684</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33" t="s">
         <v>661</v>
       </c>
@@ -12156,10 +12157,10 @@
       <c r="B20" t="s">
         <v>665</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33" t="s">
         <v>666</v>
       </c>
@@ -12175,10 +12176,10 @@
       <c r="B21" t="s">
         <v>668</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="33" t="s">
         <v>1331</v>
       </c>
@@ -12194,10 +12195,10 @@
       <c r="B22" t="s">
         <v>1333</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="33"/>
       <c r="G22" s="64"/>
       <c r="H22" s="64"/>
@@ -12211,10 +12212,10 @@
       <c r="B23" t="s">
         <v>1335</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="62"/>
       <c r="E23" s="33" t="s">
         <v>1336</v>
       </c>
@@ -12230,10 +12231,10 @@
       <c r="B24" t="s">
         <v>1322</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D24" s="68"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="33" t="s">
         <v>1338</v>
       </c>
@@ -12249,10 +12250,10 @@
       <c r="B25" t="s">
         <v>1340</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D25" s="68"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="33" t="s">
         <v>652</v>
       </c>
@@ -12268,10 +12269,10 @@
       <c r="B26" t="s">
         <v>1342</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D26" s="68"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="33"/>
       <c r="G26" s="64"/>
       <c r="H26" s="64"/>
@@ -12285,10 +12286,10 @@
       <c r="B27" t="s">
         <v>1344</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D27" s="68"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="33" t="s">
         <v>666</v>
       </c>
@@ -12304,10 +12305,10 @@
       <c r="B28" t="s">
         <v>1346</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D28" s="68"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="33"/>
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
@@ -12321,10 +12322,10 @@
       <c r="B29" t="s">
         <v>1348</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D29" s="68"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="33" t="s">
         <v>1349</v>
       </c>
@@ -12340,10 +12341,10 @@
       <c r="B30" t="s">
         <v>1352</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D30" s="68"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="33" t="s">
         <v>1350</v>
       </c>
@@ -12362,10 +12363,10 @@
       <c r="B31" t="s">
         <v>2025</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D31" s="68"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="33" t="s">
         <v>1349</v>
       </c>
@@ -12384,10 +12385,10 @@
       <c r="B32" t="s">
         <v>1354</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D32" s="68"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="33" t="s">
         <v>666</v>
       </c>
@@ -12406,10 +12407,10 @@
       <c r="B33" s="49" t="s">
         <v>1686</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D33" s="68"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="33" t="s">
         <v>1349</v>
       </c>
@@ -12428,10 +12429,10 @@
       <c r="B34" s="49" t="s">
         <v>1688</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D34" s="68"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="33" t="s">
         <v>1349</v>
       </c>
@@ -12450,10 +12451,10 @@
       <c r="B35" s="49" t="s">
         <v>1690</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="62"/>
       <c r="E35" s="33" t="s">
         <v>1349</v>
       </c>
@@ -12472,10 +12473,10 @@
       <c r="B36" s="49" t="s">
         <v>1691</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D36" s="68"/>
+      <c r="D36" s="62"/>
       <c r="E36" s="56" t="s">
         <v>1349</v>
       </c>
@@ -12494,10 +12495,10 @@
       <c r="B37" t="s">
         <v>1844</v>
       </c>
-      <c r="C37" s="68" t="s">
+      <c r="C37" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D37" s="68"/>
+      <c r="D37" s="62"/>
       <c r="E37" t="s">
         <v>1845</v>
       </c>
@@ -12509,39 +12510,29 @@
       <c r="B38" t="s">
         <v>1846</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D38" s="68"/>
+      <c r="D38" s="62"/>
       <c r="E38" t="s">
         <v>666</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
@@ -12555,19 +12546,29 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="C19:D19"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:F21" xr:uid="{7FAB08B6-9907-44B4-A82A-4A3E200D36A8}">
@@ -12859,12 +12860,12 @@
       <c r="E13" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -13707,19 +13708,19 @@
       <c r="B55" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C55" s="62" t="s">
+      <c r="C55" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="D55" s="62"/>
+      <c r="D55" s="65"/>
       <c r="E55" s="32" t="s">
         <v>766</v>
       </c>
-      <c r="F55" s="62" t="s">
+      <c r="F55" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G55" s="62"/>
-      <c r="H55" s="62"/>
-      <c r="I55" s="62"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="65"/>
     </row>
     <row r="56" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -13728,10 +13729,10 @@
       <c r="B56" t="s">
         <v>768</v>
       </c>
-      <c r="C56" s="68" t="s">
+      <c r="C56" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D56" s="68"/>
+      <c r="D56" s="62"/>
       <c r="E56" s="5" t="s">
         <v>769</v>
       </c>
@@ -13747,10 +13748,10 @@
       <c r="B57" t="s">
         <v>771</v>
       </c>
-      <c r="C57" s="68" t="s">
+      <c r="C57" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D57" s="68"/>
+      <c r="D57" s="62"/>
       <c r="E57" s="5" t="s">
         <v>772</v>
       </c>
@@ -13766,10 +13767,10 @@
       <c r="B58" t="s">
         <v>269</v>
       </c>
-      <c r="C58" s="68" t="s">
+      <c r="C58" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D58" s="68"/>
+      <c r="D58" s="62"/>
       <c r="E58" s="5" t="s">
         <v>774</v>
       </c>
@@ -13785,10 +13786,10 @@
       <c r="B59" t="s">
         <v>776</v>
       </c>
-      <c r="C59" s="68" t="s">
+      <c r="C59" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D59" s="68"/>
+      <c r="D59" s="62"/>
       <c r="E59" s="5" t="s">
         <v>777</v>
       </c>
@@ -13804,10 +13805,10 @@
       <c r="B60" t="s">
         <v>779</v>
       </c>
-      <c r="C60" s="68" t="s">
+      <c r="C60" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D60" s="68"/>
+      <c r="D60" s="62"/>
       <c r="E60" s="5" t="s">
         <v>780</v>
       </c>
@@ -13823,10 +13824,10 @@
       <c r="B61" t="s">
         <v>782</v>
       </c>
-      <c r="C61" s="68" t="s">
+      <c r="C61" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D61" s="68"/>
+      <c r="D61" s="62"/>
       <c r="E61" s="5" t="s">
         <v>783</v>
       </c>
@@ -13842,10 +13843,10 @@
       <c r="B62" t="s">
         <v>785</v>
       </c>
-      <c r="C62" s="68" t="s">
+      <c r="C62" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D62" s="68"/>
+      <c r="D62" s="62"/>
       <c r="E62" s="5" t="s">
         <v>786</v>
       </c>
@@ -13861,10 +13862,10 @@
       <c r="B63" t="s">
         <v>788</v>
       </c>
-      <c r="C63" s="68" t="s">
+      <c r="C63" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D63" s="68"/>
+      <c r="D63" s="62"/>
       <c r="E63" s="5" t="s">
         <v>789</v>
       </c>
@@ -13880,10 +13881,10 @@
       <c r="B64" t="s">
         <v>791</v>
       </c>
-      <c r="C64" s="68" t="s">
+      <c r="C64" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D64" s="68"/>
+      <c r="D64" s="62"/>
       <c r="E64" s="5" t="s">
         <v>792</v>
       </c>
@@ -13894,25 +13895,23 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="F55:I55"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="F35:I35"/>
@@ -13926,23 +13925,25 @@
     <mergeCell ref="F49:I49"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F61:I61"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
@@ -15811,12 +15812,12 @@
       <c r="G14" s="32" t="s">
         <v>1360</v>
       </c>
-      <c r="H14" s="62" t="s">
+      <c r="H14" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -18506,24 +18507,87 @@
   </sheetData>
   <dataConsolidate link="1"/>
   <mergeCells count="111">
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="H150:K150"/>
+    <mergeCell ref="H151:K151"/>
+    <mergeCell ref="H152:K152"/>
+    <mergeCell ref="H144:K144"/>
+    <mergeCell ref="H145:K145"/>
+    <mergeCell ref="H146:K146"/>
+    <mergeCell ref="H147:K147"/>
+    <mergeCell ref="H148:K148"/>
+    <mergeCell ref="H149:K149"/>
+    <mergeCell ref="H138:K138"/>
+    <mergeCell ref="H139:K139"/>
+    <mergeCell ref="H140:K140"/>
+    <mergeCell ref="H141:K141"/>
+    <mergeCell ref="H142:K142"/>
+    <mergeCell ref="H143:K143"/>
+    <mergeCell ref="H132:K132"/>
+    <mergeCell ref="H133:K133"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="H135:K135"/>
+    <mergeCell ref="H136:K136"/>
+    <mergeCell ref="H137:K137"/>
+    <mergeCell ref="H126:K126"/>
+    <mergeCell ref="H127:K127"/>
+    <mergeCell ref="H128:K128"/>
+    <mergeCell ref="H129:K129"/>
+    <mergeCell ref="H130:K130"/>
+    <mergeCell ref="H131:K131"/>
+    <mergeCell ref="H120:K120"/>
+    <mergeCell ref="H121:K121"/>
+    <mergeCell ref="H122:K122"/>
+    <mergeCell ref="H123:K123"/>
+    <mergeCell ref="H124:K124"/>
+    <mergeCell ref="H125:K125"/>
+    <mergeCell ref="H114:K114"/>
+    <mergeCell ref="H115:K115"/>
+    <mergeCell ref="H116:K116"/>
+    <mergeCell ref="H117:K117"/>
+    <mergeCell ref="H118:K118"/>
+    <mergeCell ref="H119:K119"/>
+    <mergeCell ref="H108:K108"/>
+    <mergeCell ref="H109:K109"/>
+    <mergeCell ref="H110:K110"/>
+    <mergeCell ref="H111:K111"/>
+    <mergeCell ref="H112:K112"/>
+    <mergeCell ref="H113:K113"/>
+    <mergeCell ref="H101:K101"/>
+    <mergeCell ref="H102:K102"/>
+    <mergeCell ref="H103:K103"/>
+    <mergeCell ref="H104:K104"/>
+    <mergeCell ref="H105:K105"/>
+    <mergeCell ref="H107:K107"/>
+    <mergeCell ref="H95:K95"/>
+    <mergeCell ref="H96:K96"/>
+    <mergeCell ref="H97:K97"/>
+    <mergeCell ref="H98:K98"/>
+    <mergeCell ref="H99:K99"/>
+    <mergeCell ref="H100:K100"/>
+    <mergeCell ref="H89:K89"/>
+    <mergeCell ref="H90:K90"/>
+    <mergeCell ref="H91:K91"/>
+    <mergeCell ref="H92:K92"/>
+    <mergeCell ref="H93:K93"/>
+    <mergeCell ref="H94:K94"/>
+    <mergeCell ref="H83:K83"/>
+    <mergeCell ref="H84:K84"/>
+    <mergeCell ref="H85:K85"/>
+    <mergeCell ref="H86:K86"/>
+    <mergeCell ref="H87:K87"/>
+    <mergeCell ref="H88:K88"/>
+    <mergeCell ref="H77:K77"/>
+    <mergeCell ref="H78:K78"/>
+    <mergeCell ref="H79:K79"/>
+    <mergeCell ref="H80:K80"/>
+    <mergeCell ref="H81:K81"/>
+    <mergeCell ref="H82:K82"/>
+    <mergeCell ref="H69:K69"/>
+    <mergeCell ref="H70:K70"/>
+    <mergeCell ref="H72:K72"/>
+    <mergeCell ref="H73:K73"/>
+    <mergeCell ref="H75:K75"/>
+    <mergeCell ref="H76:K76"/>
     <mergeCell ref="H62:K62"/>
     <mergeCell ref="H63:K63"/>
     <mergeCell ref="H64:K64"/>
@@ -18536,87 +18600,24 @@
     <mergeCell ref="H58:K58"/>
     <mergeCell ref="H60:K60"/>
     <mergeCell ref="H61:K61"/>
-    <mergeCell ref="H77:K77"/>
-    <mergeCell ref="H78:K78"/>
-    <mergeCell ref="H79:K79"/>
-    <mergeCell ref="H80:K80"/>
-    <mergeCell ref="H81:K81"/>
-    <mergeCell ref="H82:K82"/>
-    <mergeCell ref="H69:K69"/>
-    <mergeCell ref="H70:K70"/>
-    <mergeCell ref="H72:K72"/>
-    <mergeCell ref="H73:K73"/>
-    <mergeCell ref="H75:K75"/>
-    <mergeCell ref="H76:K76"/>
-    <mergeCell ref="H89:K89"/>
-    <mergeCell ref="H90:K90"/>
-    <mergeCell ref="H91:K91"/>
-    <mergeCell ref="H92:K92"/>
-    <mergeCell ref="H93:K93"/>
-    <mergeCell ref="H94:K94"/>
-    <mergeCell ref="H83:K83"/>
-    <mergeCell ref="H84:K84"/>
-    <mergeCell ref="H85:K85"/>
-    <mergeCell ref="H86:K86"/>
-    <mergeCell ref="H87:K87"/>
-    <mergeCell ref="H88:K88"/>
-    <mergeCell ref="H101:K101"/>
-    <mergeCell ref="H102:K102"/>
-    <mergeCell ref="H103:K103"/>
-    <mergeCell ref="H104:K104"/>
-    <mergeCell ref="H105:K105"/>
-    <mergeCell ref="H107:K107"/>
-    <mergeCell ref="H95:K95"/>
-    <mergeCell ref="H96:K96"/>
-    <mergeCell ref="H97:K97"/>
-    <mergeCell ref="H98:K98"/>
-    <mergeCell ref="H99:K99"/>
-    <mergeCell ref="H100:K100"/>
-    <mergeCell ref="H114:K114"/>
-    <mergeCell ref="H115:K115"/>
-    <mergeCell ref="H116:K116"/>
-    <mergeCell ref="H117:K117"/>
-    <mergeCell ref="H118:K118"/>
-    <mergeCell ref="H119:K119"/>
-    <mergeCell ref="H108:K108"/>
-    <mergeCell ref="H109:K109"/>
-    <mergeCell ref="H110:K110"/>
-    <mergeCell ref="H111:K111"/>
-    <mergeCell ref="H112:K112"/>
-    <mergeCell ref="H113:K113"/>
-    <mergeCell ref="H126:K126"/>
-    <mergeCell ref="H127:K127"/>
-    <mergeCell ref="H128:K128"/>
-    <mergeCell ref="H129:K129"/>
-    <mergeCell ref="H130:K130"/>
-    <mergeCell ref="H131:K131"/>
-    <mergeCell ref="H120:K120"/>
-    <mergeCell ref="H121:K121"/>
-    <mergeCell ref="H122:K122"/>
-    <mergeCell ref="H123:K123"/>
-    <mergeCell ref="H124:K124"/>
-    <mergeCell ref="H125:K125"/>
-    <mergeCell ref="H138:K138"/>
-    <mergeCell ref="H139:K139"/>
-    <mergeCell ref="H140:K140"/>
-    <mergeCell ref="H141:K141"/>
-    <mergeCell ref="H142:K142"/>
-    <mergeCell ref="H143:K143"/>
-    <mergeCell ref="H132:K132"/>
-    <mergeCell ref="H133:K133"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="H135:K135"/>
-    <mergeCell ref="H136:K136"/>
-    <mergeCell ref="H137:K137"/>
-    <mergeCell ref="H150:K150"/>
-    <mergeCell ref="H151:K151"/>
-    <mergeCell ref="H152:K152"/>
-    <mergeCell ref="H144:K144"/>
-    <mergeCell ref="H145:K145"/>
-    <mergeCell ref="H146:K146"/>
-    <mergeCell ref="H147:K147"/>
-    <mergeCell ref="H148:K148"/>
-    <mergeCell ref="H149:K149"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H48:K48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20890,19 +20891,19 @@
       <c r="B109" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C109" s="62" t="s">
+      <c r="C109" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="D109" s="62"/>
+      <c r="D109" s="65"/>
       <c r="E109" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F109" s="62" t="s">
+      <c r="F109" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G109" s="62"/>
-      <c r="H109" s="62"/>
-      <c r="I109" s="62"/>
+      <c r="G109" s="65"/>
+      <c r="H109" s="65"/>
+      <c r="I109" s="65"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
@@ -20911,10 +20912,10 @@
       <c r="B110" t="s">
         <v>931</v>
       </c>
-      <c r="C110" s="68" t="s">
+      <c r="C110" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D110" s="68"/>
+      <c r="D110" s="62"/>
       <c r="E110" s="34"/>
       <c r="F110" s="63"/>
       <c r="G110" s="64"/>
@@ -20928,10 +20929,10 @@
       <c r="B111" t="s">
         <v>934</v>
       </c>
-      <c r="C111" s="68" t="s">
+      <c r="C111" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D111" s="68"/>
+      <c r="D111" s="62"/>
       <c r="E111" s="34"/>
       <c r="F111" s="63"/>
       <c r="G111" s="64"/>
@@ -20945,10 +20946,10 @@
       <c r="B112" t="s">
         <v>936</v>
       </c>
-      <c r="C112" s="68" t="s">
+      <c r="C112" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D112" s="68"/>
+      <c r="D112" s="62"/>
       <c r="E112" s="34"/>
       <c r="F112" s="63"/>
       <c r="G112" s="64"/>
@@ -20962,10 +20963,10 @@
       <c r="B113" t="s">
         <v>938</v>
       </c>
-      <c r="C113" s="68" t="s">
+      <c r="C113" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D113" s="68"/>
+      <c r="D113" s="62"/>
       <c r="E113" s="34"/>
       <c r="F113" s="63"/>
       <c r="G113" s="64"/>
@@ -20979,10 +20980,10 @@
       <c r="B114" t="s">
         <v>939</v>
       </c>
-      <c r="C114" s="68" t="s">
+      <c r="C114" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D114" s="68"/>
+      <c r="D114" s="62"/>
       <c r="E114" s="34"/>
       <c r="F114" s="46"/>
       <c r="G114" s="10"/>
@@ -20996,10 +20997,10 @@
       <c r="B115" t="s">
         <v>940</v>
       </c>
-      <c r="C115" s="68" t="s">
+      <c r="C115" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D115" s="68"/>
+      <c r="D115" s="62"/>
       <c r="E115" s="34"/>
       <c r="F115" s="46"/>
       <c r="G115" s="10"/>
@@ -21013,10 +21014,10 @@
       <c r="B116" t="s">
         <v>941</v>
       </c>
-      <c r="C116" s="68" t="s">
+      <c r="C116" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D116" s="68"/>
+      <c r="D116" s="62"/>
       <c r="E116" s="34"/>
       <c r="F116" s="46"/>
       <c r="G116" s="10"/>
@@ -21030,10 +21031,10 @@
       <c r="B117" t="s">
         <v>943</v>
       </c>
-      <c r="C117" s="68" t="s">
+      <c r="C117" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D117" s="68"/>
+      <c r="D117" s="62"/>
       <c r="E117" s="34"/>
       <c r="F117" s="46"/>
       <c r="G117" s="10"/>
@@ -21047,10 +21048,10 @@
       <c r="B118" t="s">
         <v>945</v>
       </c>
-      <c r="C118" s="68" t="s">
+      <c r="C118" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D118" s="68"/>
+      <c r="D118" s="62"/>
       <c r="E118" s="34"/>
       <c r="F118" s="46"/>
       <c r="G118" s="10"/>
@@ -21064,10 +21065,10 @@
       <c r="B119" t="s">
         <v>947</v>
       </c>
-      <c r="C119" s="68" t="s">
+      <c r="C119" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D119" s="68"/>
+      <c r="D119" s="62"/>
       <c r="E119" s="34"/>
       <c r="F119" s="46"/>
       <c r="G119" s="10"/>
@@ -21081,10 +21082,10 @@
       <c r="B120" t="s">
         <v>949</v>
       </c>
-      <c r="C120" s="68" t="s">
+      <c r="C120" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D120" s="68"/>
+      <c r="D120" s="62"/>
       <c r="E120" s="34"/>
       <c r="F120" s="46"/>
       <c r="G120" s="10"/>
@@ -21098,10 +21099,10 @@
       <c r="B121" t="s">
         <v>951</v>
       </c>
-      <c r="C121" s="68" t="s">
+      <c r="C121" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D121" s="68"/>
+      <c r="D121" s="62"/>
       <c r="E121" s="34"/>
       <c r="F121" s="46"/>
       <c r="G121" s="10"/>
@@ -21115,10 +21116,10 @@
       <c r="B122" t="s">
         <v>953</v>
       </c>
-      <c r="C122" s="68" t="s">
+      <c r="C122" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D122" s="68"/>
+      <c r="D122" s="62"/>
       <c r="E122" s="34"/>
       <c r="F122" s="46"/>
       <c r="G122" s="10"/>
@@ -21132,10 +21133,10 @@
       <c r="B123" t="s">
         <v>955</v>
       </c>
-      <c r="C123" s="68" t="s">
+      <c r="C123" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D123" s="68"/>
+      <c r="D123" s="62"/>
       <c r="E123" s="34"/>
       <c r="F123" s="46"/>
       <c r="G123" s="10"/>
@@ -21149,10 +21150,10 @@
       <c r="B124" t="s">
         <v>957</v>
       </c>
-      <c r="C124" s="68" t="s">
+      <c r="C124" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D124" s="68"/>
+      <c r="D124" s="62"/>
       <c r="E124" s="34"/>
       <c r="F124" s="46"/>
       <c r="G124" s="10"/>
@@ -21166,10 +21167,10 @@
       <c r="B125" t="s">
         <v>959</v>
       </c>
-      <c r="C125" s="68" t="s">
+      <c r="C125" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D125" s="68"/>
+      <c r="D125" s="62"/>
       <c r="E125" s="34"/>
       <c r="F125" s="46"/>
       <c r="G125" s="10"/>
@@ -21183,10 +21184,10 @@
       <c r="B126" t="s">
         <v>961</v>
       </c>
-      <c r="C126" s="68" t="s">
+      <c r="C126" s="62" t="s">
         <v>932</v>
       </c>
-      <c r="D126" s="68"/>
+      <c r="D126" s="62"/>
       <c r="E126" s="34"/>
       <c r="F126" s="10"/>
       <c r="G126" s="10"/>
@@ -21195,13 +21196,14 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F113:I113"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F109:I109"/>
+    <mergeCell ref="F110:I110"/>
+    <mergeCell ref="F111:I111"/>
+    <mergeCell ref="F112:I112"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
     <mergeCell ref="C126:D126"/>
     <mergeCell ref="C119:D119"/>
     <mergeCell ref="C120:D120"/>
@@ -21210,14 +21212,13 @@
     <mergeCell ref="C123:D123"/>
     <mergeCell ref="C124:D124"/>
     <mergeCell ref="C125:D125"/>
-    <mergeCell ref="F109:I109"/>
-    <mergeCell ref="F110:I110"/>
-    <mergeCell ref="F111:I111"/>
-    <mergeCell ref="F112:I112"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="F113:I113"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C117:D117"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -21523,12 +21524,12 @@
       <c r="G13" s="32" t="s">
         <v>1360</v>
       </c>
-      <c r="H13" s="62" t="s">
+      <c r="H13" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -21930,118 +21931,109 @@
       <c r="K32" s="10"/>
     </row>
     <row r="37" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
+      <c r="H37" s="62"/>
+      <c r="I37" s="62"/>
+      <c r="J37" s="62"/>
+      <c r="K37" s="62"/>
     </row>
     <row r="38" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="62"/>
     </row>
     <row r="39" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="62"/>
     </row>
     <row r="40" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
     </row>
     <row r="41" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="62"/>
+      <c r="K41" s="62"/>
     </row>
     <row r="42" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H42" s="68"/>
-      <c r="I42" s="68"/>
-      <c r="J42" s="68"/>
-      <c r="K42" s="68"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="62"/>
+      <c r="K42" s="62"/>
     </row>
     <row r="43" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
+      <c r="J43" s="62"/>
+      <c r="K43" s="62"/>
     </row>
     <row r="44" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H44" s="68"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="62"/>
+      <c r="J44" s="62"/>
+      <c r="K44" s="62"/>
     </row>
     <row r="45" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H45" s="68"/>
-      <c r="I45" s="68"/>
-      <c r="J45" s="68"/>
-      <c r="K45" s="68"/>
+      <c r="H45" s="62"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="62"/>
+      <c r="K45" s="62"/>
     </row>
     <row r="46" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H46" s="68"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
+      <c r="H46" s="62"/>
+      <c r="I46" s="62"/>
+      <c r="J46" s="62"/>
+      <c r="K46" s="62"/>
     </row>
     <row r="48" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="62"/>
+      <c r="J48" s="62"/>
+      <c r="K48" s="62"/>
     </row>
     <row r="51" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="62"/>
+      <c r="J51" s="62"/>
+      <c r="K51" s="62"/>
     </row>
     <row r="52" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H52" s="68"/>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="68"/>
+      <c r="H52" s="62"/>
+      <c r="I52" s="62"/>
+      <c r="J52" s="62"/>
+      <c r="K52" s="62"/>
     </row>
     <row r="53" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H53" s="68"/>
-      <c r="I53" s="68"/>
-      <c r="J53" s="68"/>
-      <c r="K53" s="68"/>
+      <c r="H53" s="62"/>
+      <c r="I53" s="62"/>
+      <c r="J53" s="62"/>
+      <c r="K53" s="62"/>
     </row>
     <row r="54" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H54" s="68"/>
-      <c r="I54" s="68"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="68"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="62"/>
+      <c r="J54" s="62"/>
+      <c r="K54" s="62"/>
     </row>
     <row r="55" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H55" s="68"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="68"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="62"/>
+      <c r="J55" s="62"/>
+      <c r="K55" s="62"/>
     </row>
     <row r="56" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H56" s="68"/>
-      <c r="I56" s="68"/>
-      <c r="J56" s="68"/>
-      <c r="K56" s="68"/>
+      <c r="H56" s="62"/>
+      <c r="I56" s="62"/>
+      <c r="J56" s="62"/>
+      <c r="K56" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H53:K53"/>
     <mergeCell ref="H44:K44"/>
     <mergeCell ref="H13:K13"/>
     <mergeCell ref="H14:K14"/>
@@ -22054,6 +22046,15 @@
     <mergeCell ref="H41:K41"/>
     <mergeCell ref="H42:K42"/>
     <mergeCell ref="H43:K43"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H53:K53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22299,109 +22300,117 @@
       <c r="K11" s="10"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
     </row>
     <row r="17" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
     </row>
     <row r="18" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
     </row>
     <row r="19" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
     </row>
     <row r="20" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
     </row>
     <row r="21" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
     </row>
     <row r="22" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
     </row>
     <row r="23" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
     </row>
     <row r="24" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
     </row>
     <row r="25" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
     </row>
     <row r="27" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H27" s="68"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
     </row>
     <row r="30" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
     </row>
     <row r="31" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
     </row>
     <row r="32" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H32" s="68"/>
-      <c r="I32" s="68"/>
-      <c r="J32" s="68"/>
-      <c r="K32" s="68"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
     </row>
     <row r="33" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="68"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
     </row>
     <row r="34" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
     </row>
     <row r="35" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="H22:K22"/>
     <mergeCell ref="H33:K33"/>
     <mergeCell ref="H34:K34"/>
     <mergeCell ref="H35:K35"/>
@@ -22411,14 +22420,6 @@
     <mergeCell ref="H30:K30"/>
     <mergeCell ref="H31:K31"/>
     <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="H22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -22665,114 +22666,109 @@
       <c r="K11" s="10"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
     </row>
     <row r="17" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
     </row>
     <row r="18" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
     </row>
     <row r="19" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
     </row>
     <row r="20" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
     </row>
     <row r="21" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
     </row>
     <row r="22" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
     </row>
     <row r="23" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
     </row>
     <row r="24" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
     </row>
     <row r="25" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
     </row>
     <row r="27" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H27" s="68"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
     </row>
     <row r="30" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
     </row>
     <row r="31" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
     </row>
     <row r="32" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H32" s="68"/>
-      <c r="I32" s="68"/>
-      <c r="J32" s="68"/>
-      <c r="K32" s="68"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
     </row>
     <row r="33" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="68"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
     </row>
     <row r="34" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
     </row>
     <row r="35" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
     <mergeCell ref="H30:K30"/>
     <mergeCell ref="H16:K16"/>
     <mergeCell ref="H17:K17"/>
@@ -22785,6 +22781,11 @@
     <mergeCell ref="H24:K24"/>
     <mergeCell ref="H25:K25"/>
     <mergeCell ref="H27:K27"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H35:K35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23042,28 +23043,28 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>977</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>977</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="34"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>977</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="34"/>
     </row>
   </sheetData>
@@ -23422,12 +23423,12 @@
       <c r="E16" s="32" t="s">
         <v>997</v>
       </c>
-      <c r="F16" s="62" t="s">
+      <c r="F16" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -23436,10 +23437,10 @@
       <c r="B17" t="s">
         <v>999</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="34"/>
       <c r="F17" s="63"/>
       <c r="G17" s="64"/>
@@ -23453,10 +23454,10 @@
       <c r="B18" t="s">
         <v>248</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="34"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64"/>
@@ -23470,10 +23471,10 @@
       <c r="B19" t="s">
         <v>1001</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="34"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64"/>
@@ -23487,10 +23488,10 @@
       <c r="B20" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="34"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64"/>
@@ -23504,10 +23505,10 @@
       <c r="B21" t="s">
         <v>1004</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="34"/>
       <c r="F21" s="63"/>
       <c r="G21" s="64"/>
@@ -23521,10 +23522,10 @@
       <c r="B22" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="34"/>
       <c r="F22" s="63"/>
       <c r="G22" s="64"/>
@@ -23538,10 +23539,10 @@
       <c r="B23" t="s">
         <v>260</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="62"/>
       <c r="E23" s="34"/>
       <c r="F23" s="63"/>
       <c r="G23" s="64"/>
@@ -23555,10 +23556,10 @@
       <c r="B24" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D24" s="68"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="34"/>
       <c r="F24" s="63"/>
       <c r="G24" s="64"/>
@@ -23594,12 +23595,12 @@
       <c r="E27" s="32" t="s">
         <v>1007</v>
       </c>
-      <c r="F27" s="62" t="s">
+      <c r="F27" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -23608,10 +23609,10 @@
       <c r="B28">
         <v>24642003</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D28" s="68"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="34"/>
       <c r="F28" s="63"/>
       <c r="G28" s="64"/>
@@ -23625,10 +23626,10 @@
       <c r="B29">
         <v>409063005</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D29" s="68"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="34"/>
       <c r="F29" s="63"/>
       <c r="G29" s="64"/>
@@ -23642,10 +23643,10 @@
       <c r="B30">
         <v>409073007</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C30" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D30" s="68"/>
+      <c r="D30" s="62"/>
       <c r="E30" s="34"/>
       <c r="F30" s="63"/>
       <c r="G30" s="64"/>
@@ -23659,10 +23660,10 @@
       <c r="B31">
         <v>387713003</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="68"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="34"/>
       <c r="F31" s="63"/>
       <c r="G31" s="64"/>
@@ -23676,10 +23677,10 @@
       <c r="B32">
         <v>103693007</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D32" s="68"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="34"/>
       <c r="F32" s="63"/>
       <c r="G32" s="64"/>
@@ -23693,10 +23694,10 @@
       <c r="B33">
         <v>46947000</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="68"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="34"/>
       <c r="F33" s="63"/>
       <c r="G33" s="64"/>
@@ -23710,10 +23711,10 @@
       <c r="B34">
         <v>410606002</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="68"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="34"/>
       <c r="F34" s="63"/>
       <c r="G34" s="64"/>
@@ -23749,12 +23750,12 @@
       <c r="E37" s="32" t="s">
         <v>1017</v>
       </c>
-      <c r="F37" s="62" t="s">
+      <c r="F37" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G37" s="62"/>
-      <c r="H37" s="62"/>
-      <c r="I37" s="62"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -23763,10 +23764,10 @@
       <c r="B38">
         <v>385669000</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D38" s="68"/>
+      <c r="D38" s="62"/>
       <c r="E38" s="34"/>
       <c r="F38" s="63"/>
       <c r="G38" s="64"/>
@@ -23780,10 +23781,10 @@
       <c r="B39">
         <v>385671000</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D39" s="68"/>
+      <c r="D39" s="62"/>
       <c r="E39" s="34"/>
       <c r="F39" s="63"/>
       <c r="G39" s="64"/>
@@ -23797,10 +23798,10 @@
       <c r="B40">
         <v>385670004</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C40" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D40" s="68"/>
+      <c r="D40" s="62"/>
       <c r="F40" s="63"/>
       <c r="G40" s="64"/>
       <c r="H40" s="64"/>
@@ -23826,29 +23827,29 @@
       <c r="B43" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="62" t="s">
+      <c r="C43" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="D43" s="62"/>
+      <c r="D43" s="65"/>
       <c r="E43" s="7" t="s">
         <v>1266</v>
       </c>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="62"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="48" t="s">
         <v>1162</v>
       </c>
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D44" s="69"/>
+      <c r="D44" s="73"/>
       <c r="E44" s="5" t="s">
         <v>1163</v>
       </c>
@@ -23862,10 +23863,10 @@
       <c r="B45" s="48" t="s">
         <v>1164</v>
       </c>
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D45" s="69"/>
+      <c r="D45" s="73"/>
       <c r="E45" s="5" t="s">
         <v>1165</v>
       </c>
@@ -23879,10 +23880,10 @@
       <c r="B46" s="48" t="s">
         <v>1166</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D46" s="69"/>
+      <c r="D46" s="73"/>
       <c r="E46" s="5" t="s">
         <v>1167</v>
       </c>
@@ -23896,10 +23897,10 @@
       <c r="B47" s="48" t="s">
         <v>1168</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D47" s="69"/>
+      <c r="D47" s="73"/>
       <c r="E47" s="5" t="s">
         <v>1169</v>
       </c>
@@ -23913,10 +23914,10 @@
       <c r="B48" s="48" t="s">
         <v>1170</v>
       </c>
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D48" s="69"/>
+      <c r="D48" s="73"/>
       <c r="E48" s="5" t="s">
         <v>1171</v>
       </c>
@@ -23930,10 +23931,10 @@
       <c r="B49" s="48" t="s">
         <v>1172</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C49" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D49" s="69"/>
+      <c r="D49" s="73"/>
       <c r="E49" s="5" t="s">
         <v>1173</v>
       </c>
@@ -23947,10 +23948,10 @@
       <c r="B50" s="48" t="s">
         <v>1174</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="C50" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D50" s="69"/>
+      <c r="D50" s="73"/>
       <c r="E50" s="5" t="s">
         <v>1175</v>
       </c>
@@ -23964,10 +23965,10 @@
       <c r="B51" s="48" t="s">
         <v>1176</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D51" s="69"/>
+      <c r="D51" s="73"/>
       <c r="E51" s="5" t="s">
         <v>1177</v>
       </c>
@@ -23981,10 +23982,10 @@
       <c r="B52" s="48" t="s">
         <v>1178</v>
       </c>
-      <c r="C52" s="69" t="s">
+      <c r="C52" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D52" s="69"/>
+      <c r="D52" s="73"/>
       <c r="E52" s="5" t="s">
         <v>1179</v>
       </c>
@@ -23998,10 +23999,10 @@
       <c r="B53" s="48" t="s">
         <v>1180</v>
       </c>
-      <c r="C53" s="69" t="s">
+      <c r="C53" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D53" s="69"/>
+      <c r="D53" s="73"/>
       <c r="E53" s="5" t="s">
         <v>1181</v>
       </c>
@@ -24015,10 +24016,10 @@
       <c r="B54" s="48" t="s">
         <v>1182</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D54" s="69"/>
+      <c r="D54" s="73"/>
       <c r="E54" s="5" t="s">
         <v>1183</v>
       </c>
@@ -24032,10 +24033,10 @@
       <c r="B55" s="48" t="s">
         <v>1184</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="C55" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D55" s="69"/>
+      <c r="D55" s="73"/>
       <c r="E55" s="5" t="s">
         <v>1185</v>
       </c>
@@ -24049,10 +24050,10 @@
       <c r="B56" s="48" t="s">
         <v>1186</v>
       </c>
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D56" s="69"/>
+      <c r="D56" s="73"/>
       <c r="E56" s="5" t="s">
         <v>1187</v>
       </c>
@@ -24066,10 +24067,10 @@
       <c r="B57" s="48" t="s">
         <v>1188</v>
       </c>
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D57" s="69"/>
+      <c r="D57" s="73"/>
       <c r="E57" s="5" t="s">
         <v>1189</v>
       </c>
@@ -24083,10 +24084,10 @@
       <c r="B58" s="48" t="s">
         <v>1190</v>
       </c>
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D58" s="69"/>
+      <c r="D58" s="73"/>
       <c r="E58" s="5" t="s">
         <v>1191</v>
       </c>
@@ -24100,10 +24101,10 @@
       <c r="B59" s="48" t="s">
         <v>1192</v>
       </c>
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D59" s="69"/>
+      <c r="D59" s="73"/>
       <c r="E59" s="5" t="s">
         <v>1193</v>
       </c>
@@ -24117,10 +24118,10 @@
       <c r="B60" s="48" t="s">
         <v>1194</v>
       </c>
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D60" s="69"/>
+      <c r="D60" s="73"/>
       <c r="E60" s="5" t="s">
         <v>1195</v>
       </c>
@@ -24134,10 +24135,10 @@
       <c r="B61" s="48" t="s">
         <v>1196</v>
       </c>
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D61" s="69"/>
+      <c r="D61" s="73"/>
       <c r="E61" s="5" t="s">
         <v>1197</v>
       </c>
@@ -24151,10 +24152,10 @@
       <c r="B62" s="48" t="s">
         <v>1198</v>
       </c>
-      <c r="C62" s="69" t="s">
+      <c r="C62" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D62" s="69"/>
+      <c r="D62" s="73"/>
       <c r="E62" s="5" t="s">
         <v>1199</v>
       </c>
@@ -24168,10 +24169,10 @@
       <c r="B63" s="48" t="s">
         <v>1200</v>
       </c>
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D63" s="69"/>
+      <c r="D63" s="73"/>
       <c r="E63" s="5" t="s">
         <v>1201</v>
       </c>
@@ -24185,10 +24186,10 @@
       <c r="B64" s="48" t="s">
         <v>1202</v>
       </c>
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D64" s="69"/>
+      <c r="D64" s="73"/>
       <c r="E64" s="5" t="s">
         <v>1203</v>
       </c>
@@ -24202,10 +24203,10 @@
       <c r="B65" s="48" t="s">
         <v>1204</v>
       </c>
-      <c r="C65" s="69" t="s">
+      <c r="C65" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D65" s="69"/>
+      <c r="D65" s="73"/>
       <c r="E65" s="5" t="s">
         <v>1205</v>
       </c>
@@ -24219,10 +24220,10 @@
       <c r="B66" s="48" t="s">
         <v>1206</v>
       </c>
-      <c r="C66" s="69" t="s">
+      <c r="C66" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D66" s="69"/>
+      <c r="D66" s="73"/>
       <c r="E66" s="5" t="s">
         <v>1207</v>
       </c>
@@ -24236,10 +24237,10 @@
       <c r="B67" s="48" t="s">
         <v>1208</v>
       </c>
-      <c r="C67" s="69" t="s">
+      <c r="C67" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D67" s="69"/>
+      <c r="D67" s="73"/>
       <c r="E67" s="5" t="s">
         <v>1209</v>
       </c>
@@ -24253,10 +24254,10 @@
       <c r="B68" s="48" t="s">
         <v>1210</v>
       </c>
-      <c r="C68" s="69" t="s">
+      <c r="C68" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D68" s="69"/>
+      <c r="D68" s="73"/>
       <c r="E68" s="5" t="s">
         <v>1211</v>
       </c>
@@ -24270,10 +24271,10 @@
       <c r="B69" s="48" t="s">
         <v>1212</v>
       </c>
-      <c r="C69" s="69" t="s">
+      <c r="C69" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D69" s="69"/>
+      <c r="D69" s="73"/>
       <c r="E69" s="5" t="s">
         <v>1213</v>
       </c>
@@ -24287,10 +24288,10 @@
       <c r="B70" s="48" t="s">
         <v>1214</v>
       </c>
-      <c r="C70" s="69" t="s">
+      <c r="C70" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D70" s="69"/>
+      <c r="D70" s="73"/>
       <c r="E70" s="5" t="s">
         <v>1215</v>
       </c>
@@ -24304,10 +24305,10 @@
       <c r="B71" s="48" t="s">
         <v>1216</v>
       </c>
-      <c r="C71" s="69" t="s">
+      <c r="C71" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D71" s="69"/>
+      <c r="D71" s="73"/>
       <c r="E71" s="5" t="s">
         <v>1217</v>
       </c>
@@ -24321,10 +24322,10 @@
       <c r="B72" s="48" t="s">
         <v>1218</v>
       </c>
-      <c r="C72" s="69" t="s">
+      <c r="C72" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D72" s="69"/>
+      <c r="D72" s="73"/>
       <c r="E72" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24338,10 +24339,10 @@
       <c r="B73" s="48" t="s">
         <v>1220</v>
       </c>
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D73" s="69"/>
+      <c r="D73" s="73"/>
       <c r="E73" s="5" t="s">
         <v>1221</v>
       </c>
@@ -24355,10 +24356,10 @@
       <c r="B74" s="48" t="s">
         <v>1222</v>
       </c>
-      <c r="C74" s="69" t="s">
+      <c r="C74" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D74" s="69"/>
+      <c r="D74" s="73"/>
       <c r="E74" s="5" t="s">
         <v>1223</v>
       </c>
@@ -24372,10 +24373,10 @@
       <c r="B75" s="48" t="s">
         <v>1224</v>
       </c>
-      <c r="C75" s="69" t="s">
+      <c r="C75" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D75" s="69"/>
+      <c r="D75" s="73"/>
       <c r="E75" s="5" t="s">
         <v>1225</v>
       </c>
@@ -24389,10 +24390,10 @@
       <c r="B76" s="48" t="s">
         <v>1226</v>
       </c>
-      <c r="C76" s="69" t="s">
+      <c r="C76" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D76" s="69"/>
+      <c r="D76" s="73"/>
       <c r="E76" s="5" t="s">
         <v>1227</v>
       </c>
@@ -24406,10 +24407,10 @@
       <c r="B77" s="48" t="s">
         <v>1228</v>
       </c>
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D77" s="69"/>
+      <c r="D77" s="73"/>
       <c r="E77" s="5" t="s">
         <v>1229</v>
       </c>
@@ -24423,10 +24424,10 @@
       <c r="B78" s="48" t="s">
         <v>1230</v>
       </c>
-      <c r="C78" s="69" t="s">
+      <c r="C78" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D78" s="69"/>
+      <c r="D78" s="73"/>
       <c r="E78" s="5" t="s">
         <v>1231</v>
       </c>
@@ -24440,10 +24441,10 @@
       <c r="B79" s="48" t="s">
         <v>1232</v>
       </c>
-      <c r="C79" s="69" t="s">
+      <c r="C79" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D79" s="69"/>
+      <c r="D79" s="73"/>
       <c r="E79" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24457,10 +24458,10 @@
       <c r="B80" s="48" t="s">
         <v>1234</v>
       </c>
-      <c r="C80" s="69" t="s">
+      <c r="C80" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D80" s="69"/>
+      <c r="D80" s="73"/>
       <c r="E80" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24474,10 +24475,10 @@
       <c r="B81" s="48" t="s">
         <v>1236</v>
       </c>
-      <c r="C81" s="69" t="s">
+      <c r="C81" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D81" s="69"/>
+      <c r="D81" s="73"/>
       <c r="E81" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24491,10 +24492,10 @@
       <c r="B82" s="48" t="s">
         <v>1238</v>
       </c>
-      <c r="C82" s="69" t="s">
+      <c r="C82" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D82" s="69"/>
+      <c r="D82" s="73"/>
       <c r="E82" s="5" t="s">
         <v>1239</v>
       </c>
@@ -24508,10 +24509,10 @@
       <c r="B83" s="48" t="s">
         <v>1267</v>
       </c>
-      <c r="C83" s="69" t="s">
+      <c r="C83" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D83" s="69"/>
+      <c r="D83" s="73"/>
       <c r="E83" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24525,10 +24526,10 @@
       <c r="B84" s="48" t="s">
         <v>1268</v>
       </c>
-      <c r="C84" s="69" t="s">
+      <c r="C84" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D84" s="69"/>
+      <c r="D84" s="73"/>
       <c r="E84" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24542,10 +24543,10 @@
       <c r="B85" s="48" t="s">
         <v>1269</v>
       </c>
-      <c r="C85" s="69" t="s">
+      <c r="C85" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D85" s="69"/>
+      <c r="D85" s="73"/>
       <c r="E85" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24559,10 +24560,10 @@
       <c r="B86" s="48" t="s">
         <v>1270</v>
       </c>
-      <c r="C86" s="69" t="s">
+      <c r="C86" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D86" s="69"/>
+      <c r="D86" s="73"/>
       <c r="E86" s="5" t="s">
         <v>1240</v>
       </c>
@@ -24576,10 +24577,10 @@
       <c r="B87" s="48" t="s">
         <v>1241</v>
       </c>
-      <c r="C87" s="69" t="s">
+      <c r="C87" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D87" s="69"/>
+      <c r="D87" s="73"/>
       <c r="E87" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24593,10 +24594,10 @@
       <c r="B88" s="48" t="s">
         <v>1242</v>
       </c>
-      <c r="C88" s="69" t="s">
+      <c r="C88" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D88" s="69"/>
+      <c r="D88" s="73"/>
       <c r="E88" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24610,10 +24611,10 @@
       <c r="B89" s="48" t="s">
         <v>1243</v>
       </c>
-      <c r="C89" s="69" t="s">
+      <c r="C89" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D89" s="69"/>
+      <c r="D89" s="73"/>
       <c r="E89" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24627,10 +24628,10 @@
       <c r="B90" s="48" t="s">
         <v>1244</v>
       </c>
-      <c r="C90" s="69" t="s">
+      <c r="C90" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D90" s="69"/>
+      <c r="D90" s="73"/>
       <c r="E90" s="5" t="s">
         <v>1240</v>
       </c>
@@ -24644,10 +24645,10 @@
       <c r="B91" s="48" t="s">
         <v>1271</v>
       </c>
-      <c r="C91" s="69" t="s">
+      <c r="C91" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D91" s="69"/>
+      <c r="D91" s="73"/>
       <c r="E91" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24661,10 +24662,10 @@
       <c r="B92" s="48" t="s">
         <v>1272</v>
       </c>
-      <c r="C92" s="69" t="s">
+      <c r="C92" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D92" s="69"/>
+      <c r="D92" s="73"/>
       <c r="E92" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24678,10 +24679,10 @@
       <c r="B93" s="48" t="s">
         <v>1273</v>
       </c>
-      <c r="C93" s="69" t="s">
+      <c r="C93" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D93" s="69"/>
+      <c r="D93" s="73"/>
       <c r="E93" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24695,10 +24696,10 @@
       <c r="B94" s="48" t="s">
         <v>1274</v>
       </c>
-      <c r="C94" s="69" t="s">
+      <c r="C94" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D94" s="69"/>
+      <c r="D94" s="73"/>
       <c r="E94" s="5" t="s">
         <v>1240</v>
       </c>
@@ -24712,10 +24713,10 @@
       <c r="B95" s="48" t="s">
         <v>1275</v>
       </c>
-      <c r="C95" s="69" t="s">
+      <c r="C95" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D95" s="69"/>
+      <c r="D95" s="73"/>
       <c r="E95" s="5" t="s">
         <v>1245</v>
       </c>
@@ -24729,10 +24730,10 @@
       <c r="B96" s="48" t="s">
         <v>1246</v>
       </c>
-      <c r="C96" s="69" t="s">
+      <c r="C96" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D96" s="69"/>
+      <c r="D96" s="73"/>
       <c r="E96" s="5" t="s">
         <v>1247</v>
       </c>
@@ -24746,10 +24747,10 @@
       <c r="B97" s="48" t="s">
         <v>1248</v>
       </c>
-      <c r="C97" s="69" t="s">
+      <c r="C97" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D97" s="69"/>
+      <c r="D97" s="73"/>
       <c r="E97" s="5" t="s">
         <v>1249</v>
       </c>
@@ -24763,10 +24764,10 @@
       <c r="B98" s="48" t="s">
         <v>1250</v>
       </c>
-      <c r="C98" s="69" t="s">
+      <c r="C98" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D98" s="69"/>
+      <c r="D98" s="73"/>
       <c r="E98" s="5" t="s">
         <v>1251</v>
       </c>
@@ -24780,10 +24781,10 @@
       <c r="B99" s="48" t="s">
         <v>1252</v>
       </c>
-      <c r="C99" s="69" t="s">
+      <c r="C99" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D99" s="69"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="5" t="s">
         <v>1253</v>
       </c>
@@ -24797,10 +24798,10 @@
       <c r="B100" s="48" t="s">
         <v>1254</v>
       </c>
-      <c r="C100" s="69" t="s">
+      <c r="C100" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D100" s="69"/>
+      <c r="D100" s="73"/>
       <c r="E100" s="5" t="s">
         <v>1255</v>
       </c>
@@ -24814,10 +24815,10 @@
       <c r="B101" s="48" t="s">
         <v>1256</v>
       </c>
-      <c r="C101" s="69" t="s">
+      <c r="C101" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D101" s="69"/>
+      <c r="D101" s="73"/>
       <c r="E101" s="5" t="s">
         <v>1257</v>
       </c>
@@ -24831,10 +24832,10 @@
       <c r="B102" s="48" t="s">
         <v>1258</v>
       </c>
-      <c r="C102" s="69" t="s">
+      <c r="C102" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D102" s="69"/>
+      <c r="D102" s="73"/>
       <c r="E102" s="5" t="s">
         <v>1251</v>
       </c>
@@ -24848,10 +24849,10 @@
       <c r="B103" s="48" t="s">
         <v>1259</v>
       </c>
-      <c r="C103" s="69" t="s">
+      <c r="C103" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D103" s="69"/>
+      <c r="D103" s="73"/>
       <c r="E103" s="5" t="s">
         <v>1253</v>
       </c>
@@ -24865,10 +24866,10 @@
       <c r="B104" s="48" t="s">
         <v>1260</v>
       </c>
-      <c r="C104" s="69" t="s">
+      <c r="C104" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D104" s="69"/>
+      <c r="D104" s="73"/>
       <c r="E104" s="5" t="s">
         <v>1255</v>
       </c>
@@ -24882,10 +24883,10 @@
       <c r="B105" s="48" t="s">
         <v>1261</v>
       </c>
-      <c r="C105" s="69" t="s">
+      <c r="C105" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D105" s="69"/>
+      <c r="D105" s="73"/>
       <c r="E105" s="5" t="s">
         <v>1257</v>
       </c>
@@ -24899,10 +24900,10 @@
       <c r="B106" s="48" t="s">
         <v>1262</v>
       </c>
-      <c r="C106" s="69" t="s">
+      <c r="C106" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D106" s="69"/>
+      <c r="D106" s="73"/>
       <c r="E106" s="5" t="s">
         <v>1263</v>
       </c>
@@ -24916,10 +24917,10 @@
       <c r="B107" s="48" t="s">
         <v>1264</v>
       </c>
-      <c r="C107" s="69" t="s">
+      <c r="C107" s="73" t="s">
         <v>1276</v>
       </c>
-      <c r="D107" s="69"/>
+      <c r="D107" s="73"/>
       <c r="E107" s="5" t="s">
         <v>1265</v>
       </c>
@@ -24930,49 +24931,108 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F104:I104"/>
-    <mergeCell ref="F105:I105"/>
-    <mergeCell ref="F106:I106"/>
-    <mergeCell ref="F107:I107"/>
-    <mergeCell ref="F99:I99"/>
-    <mergeCell ref="F100:I100"/>
-    <mergeCell ref="F101:I101"/>
-    <mergeCell ref="F102:I102"/>
-    <mergeCell ref="F103:I103"/>
-    <mergeCell ref="F94:I94"/>
-    <mergeCell ref="F95:I95"/>
-    <mergeCell ref="F96:I96"/>
-    <mergeCell ref="F97:I97"/>
-    <mergeCell ref="F98:I98"/>
-    <mergeCell ref="F89:I89"/>
-    <mergeCell ref="F90:I90"/>
-    <mergeCell ref="F91:I91"/>
-    <mergeCell ref="F92:I92"/>
-    <mergeCell ref="F93:I93"/>
-    <mergeCell ref="F84:I84"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="F86:I86"/>
-    <mergeCell ref="F87:I87"/>
-    <mergeCell ref="F88:I88"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
-    <mergeCell ref="F82:I82"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="F67:I67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
     <mergeCell ref="C78:D78"/>
     <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
@@ -24997,108 +25057,49 @@
     <mergeCell ref="C74:D74"/>
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F84:I84"/>
+    <mergeCell ref="F85:I85"/>
+    <mergeCell ref="F86:I86"/>
+    <mergeCell ref="F87:I87"/>
+    <mergeCell ref="F88:I88"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="F82:I82"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="F94:I94"/>
+    <mergeCell ref="F95:I95"/>
+    <mergeCell ref="F96:I96"/>
+    <mergeCell ref="F97:I97"/>
+    <mergeCell ref="F98:I98"/>
+    <mergeCell ref="F89:I89"/>
+    <mergeCell ref="F90:I90"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="F92:I92"/>
+    <mergeCell ref="F93:I93"/>
+    <mergeCell ref="F104:I104"/>
+    <mergeCell ref="F105:I105"/>
+    <mergeCell ref="F106:I106"/>
+    <mergeCell ref="F107:I107"/>
+    <mergeCell ref="F99:I99"/>
+    <mergeCell ref="F100:I100"/>
+    <mergeCell ref="F101:I101"/>
+    <mergeCell ref="F102:I102"/>
+    <mergeCell ref="F103:I103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27222,214 +27223,214 @@
       <c r="B14" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="65" t="s">
         <v>1035</v>
       </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="73" t="s">
+      <c r="D14" s="65"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72" t="s">
         <v>462</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="75" t="s">
         <v>1036</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>1037</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="69" t="s">
         <v>1038</v>
       </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="72"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="63"/>
       <c r="G15" s="64"/>
       <c r="H15" s="64"/>
       <c r="I15" s="64"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="74"/>
+      <c r="A16" s="75"/>
       <c r="B16" s="42" t="s">
         <v>1039</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="69" t="s">
         <v>1040</v>
       </c>
-      <c r="D16" s="71"/>
-      <c r="E16" s="72"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="70"/>
       <c r="F16" s="63"/>
       <c r="G16" s="64"/>
       <c r="H16" s="64"/>
       <c r="I16" s="64"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="74"/>
+      <c r="A17" s="75"/>
       <c r="B17" s="42" t="s">
         <v>1041</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="69" t="s">
         <v>1042</v>
       </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="72"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="63"/>
       <c r="G17" s="64"/>
       <c r="H17" s="64"/>
       <c r="I17" s="64"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="74"/>
+      <c r="A18" s="75"/>
       <c r="B18" s="42" t="s">
         <v>1043</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="70" t="s">
         <v>1044</v>
       </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64"/>
       <c r="H18" s="64"/>
       <c r="I18" s="64"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="74"/>
+      <c r="A19" s="75"/>
       <c r="B19" s="42" t="s">
         <v>1045</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="70" t="s">
         <v>1046</v>
       </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64"/>
       <c r="H19" s="64"/>
       <c r="I19" s="64"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="76" t="s">
         <v>1047</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>1048</v>
       </c>
-      <c r="C20" s="72" t="s">
+      <c r="C20" s="70" t="s">
         <v>1049</v>
       </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64"/>
       <c r="H20" s="64"/>
       <c r="I20" s="64"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
+      <c r="A21" s="76"/>
       <c r="B21" s="42" t="s">
         <v>1050</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="70" t="s">
         <v>1051</v>
       </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
       <c r="F21" s="63"/>
       <c r="G21" s="64"/>
       <c r="H21" s="64"/>
       <c r="I21" s="64"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="75"/>
+      <c r="A22" s="76"/>
       <c r="B22" s="42" t="s">
         <v>1052</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="70" t="s">
         <v>1053</v>
       </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
       <c r="F22" s="63"/>
       <c r="G22" s="64"/>
       <c r="H22" s="64"/>
       <c r="I22" s="64"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
+      <c r="A23" s="76"/>
       <c r="B23" s="42" t="s">
         <v>1054</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="70" t="s">
         <v>1055</v>
       </c>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
       <c r="F23" s="63"/>
       <c r="G23" s="64"/>
       <c r="H23" s="64"/>
       <c r="I23" s="64"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="76" t="s">
         <v>1056</v>
       </c>
       <c r="B24" s="42" t="s">
         <v>1048</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="70" t="s">
         <v>1057</v>
       </c>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
       <c r="F24" s="63"/>
       <c r="G24" s="64"/>
       <c r="H24" s="64"/>
       <c r="I24" s="64"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
+      <c r="A25" s="76"/>
       <c r="B25" s="42" t="s">
         <v>1058</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="70" t="s">
         <v>1059</v>
       </c>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
       <c r="F25" s="63"/>
       <c r="G25" s="64"/>
       <c r="H25" s="64"/>
       <c r="I25" s="64"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="42" t="s">
         <v>1052</v>
       </c>
-      <c r="C26" s="72" t="s">
+      <c r="C26" s="70" t="s">
         <v>1060</v>
       </c>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
       <c r="F26" s="63"/>
       <c r="G26" s="64"/>
       <c r="H26" s="64"/>
       <c r="I26" s="64"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
+      <c r="A27" s="76"/>
       <c r="B27" s="42" t="s">
         <v>1054</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="74" t="s">
         <v>1061</v>
       </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
       <c r="F27" s="63"/>
       <c r="G27" s="64"/>
       <c r="H27" s="64"/>
@@ -27442,137 +27443,137 @@
       <c r="B28" s="45" t="s">
         <v>1063</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="74" t="s">
         <v>1064</v>
       </c>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="74"/>
       <c r="F28" s="63"/>
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
       <c r="I28" s="64"/>
     </row>
     <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="76" t="s">
         <v>1065</v>
       </c>
       <c r="B29" s="45" t="s">
         <v>1066</v>
       </c>
-      <c r="C29" s="76" t="s">
+      <c r="C29" s="74" t="s">
         <v>1067</v>
       </c>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
       <c r="F29" s="63"/>
       <c r="G29" s="64"/>
       <c r="H29" s="64"/>
       <c r="I29" s="64"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
+      <c r="A30" s="76"/>
       <c r="B30" s="45" t="s">
         <v>1068</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="74" t="s">
         <v>1069</v>
       </c>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
       <c r="F30" s="63"/>
       <c r="G30" s="64"/>
       <c r="H30" s="64"/>
       <c r="I30" s="64"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="76" t="s">
         <v>1070</v>
       </c>
       <c r="B31" s="45" t="s">
         <v>1071</v>
       </c>
-      <c r="C31" s="76" t="s">
+      <c r="C31" s="74" t="s">
         <v>1072</v>
       </c>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
       <c r="F31" s="63"/>
       <c r="G31" s="64"/>
       <c r="H31" s="64"/>
       <c r="I31" s="64"/>
     </row>
     <row r="32" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
+      <c r="A32" s="76"/>
       <c r="B32" s="45" t="s">
         <v>1073</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="74" t="s">
         <v>1074</v>
       </c>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
       <c r="F32" s="63"/>
       <c r="G32" s="64"/>
       <c r="H32" s="64"/>
       <c r="I32" s="64"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="75" t="s">
+      <c r="A33" s="76" t="s">
         <v>1075</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>1048</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="74" t="s">
         <v>1076</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="74"/>
       <c r="F33" s="63"/>
       <c r="G33" s="64"/>
       <c r="H33" s="64"/>
       <c r="I33" s="64"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
+      <c r="A34" s="76"/>
       <c r="B34" s="45" t="s">
         <v>1077</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="74" t="s">
         <v>1078</v>
       </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
+      <c r="D34" s="74"/>
+      <c r="E34" s="74"/>
       <c r="F34" s="63"/>
       <c r="G34" s="64"/>
       <c r="H34" s="64"/>
       <c r="I34" s="64"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
+      <c r="A35" s="76"/>
       <c r="B35" s="45" t="s">
         <v>1079</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="C35" s="74" t="s">
         <v>1080</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
       <c r="F35" s="63"/>
       <c r="G35" s="64"/>
       <c r="H35" s="64"/>
       <c r="I35" s="64"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
+      <c r="A36" s="76"/>
       <c r="B36" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="74" t="s">
         <v>1081</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="74"/>
       <c r="F36" s="63"/>
       <c r="G36" s="64"/>
       <c r="H36" s="64"/>
@@ -27585,152 +27586,152 @@
       <c r="B37" s="45" t="s">
         <v>1063</v>
       </c>
-      <c r="C37" s="76" t="s">
+      <c r="C37" s="74" t="s">
         <v>1083</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
       <c r="F37" s="63"/>
       <c r="G37" s="64"/>
       <c r="H37" s="64"/>
       <c r="I37" s="64"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="75" t="s">
+      <c r="A38" s="76" t="s">
         <v>1084</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>1085</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="74" t="s">
         <v>1086</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="74"/>
       <c r="F38" s="63"/>
       <c r="G38" s="64"/>
       <c r="H38" s="64"/>
       <c r="I38" s="64"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
+      <c r="A39" s="76"/>
       <c r="B39" s="45" t="s">
         <v>1087</v>
       </c>
-      <c r="C39" s="76" t="s">
+      <c r="C39" s="74" t="s">
         <v>1088</v>
       </c>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="63"/>
       <c r="G39" s="64"/>
       <c r="H39" s="64"/>
       <c r="I39" s="64"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="75"/>
+      <c r="A40" s="76"/>
       <c r="B40" s="45" t="s">
         <v>1089</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="74" t="s">
         <v>1090</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
+      <c r="D40" s="74"/>
+      <c r="E40" s="74"/>
       <c r="F40" s="63"/>
       <c r="G40" s="64"/>
       <c r="H40" s="64"/>
       <c r="I40" s="64"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="75" t="s">
+      <c r="A41" s="76" t="s">
         <v>1091</v>
       </c>
       <c r="B41" s="45" t="s">
         <v>1092</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="74" t="s">
         <v>1093</v>
       </c>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="74"/>
       <c r="F41" s="63"/>
       <c r="G41" s="64"/>
       <c r="H41" s="64"/>
       <c r="I41" s="64"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="75"/>
+      <c r="A42" s="76"/>
       <c r="B42" s="45" t="s">
         <v>1094</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
       <c r="F42" s="63"/>
       <c r="G42" s="64"/>
       <c r="H42" s="64"/>
       <c r="I42" s="64"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="75"/>
+      <c r="A43" s="76"/>
       <c r="B43" s="45" t="s">
         <v>1096</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="62" t="s">
         <v>1097</v>
       </c>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
       <c r="F43" s="63"/>
       <c r="G43" s="64"/>
       <c r="H43" s="64"/>
       <c r="I43" s="64"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="75"/>
+      <c r="A44" s="76"/>
       <c r="B44" s="45" t="s">
         <v>1098</v>
       </c>
-      <c r="C44" s="74" t="s">
+      <c r="C44" s="75" t="s">
         <v>1099</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
       <c r="F44" s="63"/>
       <c r="G44" s="64"/>
       <c r="H44" s="64"/>
       <c r="I44" s="64"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="75" t="s">
+      <c r="A45" s="76" t="s">
         <v>1100</v>
       </c>
       <c r="B45" s="45" t="s">
         <v>1101</v>
       </c>
-      <c r="C45" s="74" t="s">
+      <c r="C45" s="75" t="s">
         <v>1102</v>
       </c>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
+      <c r="D45" s="75"/>
+      <c r="E45" s="75"/>
       <c r="F45" s="63"/>
       <c r="G45" s="64"/>
       <c r="H45" s="64"/>
       <c r="I45" s="64"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="75"/>
+      <c r="A46" s="76"/>
       <c r="B46" s="45" t="s">
         <v>1103</v>
       </c>
-      <c r="C46" s="74" t="s">
+      <c r="C46" s="75" t="s">
         <v>1104</v>
       </c>
-      <c r="D46" s="74"/>
-      <c r="E46" s="74"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
       <c r="F46" s="63"/>
       <c r="G46" s="64"/>
       <c r="H46" s="64"/>
@@ -27743,11 +27744,11 @@
       <c r="B47" s="45" t="s">
         <v>1063</v>
       </c>
-      <c r="C47" s="74" t="s">
+      <c r="C47" s="75" t="s">
         <v>1106</v>
       </c>
-      <c r="D47" s="74"/>
-      <c r="E47" s="74"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
       <c r="F47" s="63"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
@@ -27760,165 +27761,165 @@
       <c r="B48" s="45" t="s">
         <v>1108</v>
       </c>
-      <c r="C48" s="74" t="s">
+      <c r="C48" s="75" t="s">
         <v>1109</v>
       </c>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
       <c r="F48" s="63"/>
       <c r="G48" s="64"/>
       <c r="H48" s="64"/>
       <c r="I48" s="64"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="75" t="s">
+      <c r="A49" s="76" t="s">
         <v>1110</v>
       </c>
       <c r="B49" s="45" t="s">
         <v>1111</v>
       </c>
-      <c r="C49" s="74" t="s">
+      <c r="C49" s="75" t="s">
         <v>1112</v>
       </c>
-      <c r="D49" s="74"/>
-      <c r="E49" s="74"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="75"/>
       <c r="F49" s="63"/>
       <c r="G49" s="64"/>
       <c r="H49" s="64"/>
       <c r="I49" s="64"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="75"/>
+      <c r="A50" s="76"/>
       <c r="B50" s="45" t="s">
         <v>1113</v>
       </c>
-      <c r="C50" s="74" t="s">
+      <c r="C50" s="75" t="s">
         <v>1114</v>
       </c>
-      <c r="D50" s="74"/>
-      <c r="E50" s="74"/>
+      <c r="D50" s="75"/>
+      <c r="E50" s="75"/>
       <c r="F50" s="63"/>
       <c r="G50" s="64"/>
       <c r="H50" s="64"/>
       <c r="I50" s="64"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="75"/>
+      <c r="A51" s="76"/>
       <c r="B51" s="45" t="s">
         <v>1058</v>
       </c>
-      <c r="C51" s="74" t="s">
+      <c r="C51" s="75" t="s">
         <v>1115</v>
       </c>
-      <c r="D51" s="74"/>
-      <c r="E51" s="74"/>
+      <c r="D51" s="75"/>
+      <c r="E51" s="75"/>
       <c r="F51" s="63"/>
       <c r="G51" s="64"/>
       <c r="H51" s="64"/>
       <c r="I51" s="64"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="75"/>
+      <c r="A52" s="76"/>
       <c r="B52" s="45" t="s">
         <v>1116</v>
       </c>
-      <c r="C52" s="74" t="s">
+      <c r="C52" s="75" t="s">
         <v>1117</v>
       </c>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
       <c r="F52" s="63"/>
       <c r="G52" s="64"/>
       <c r="H52" s="64"/>
       <c r="I52" s="64"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="75"/>
+      <c r="A53" s="76"/>
       <c r="B53" s="45" t="s">
         <v>1054</v>
       </c>
-      <c r="C53" s="74" t="s">
+      <c r="C53" s="75" t="s">
         <v>1118</v>
       </c>
-      <c r="D53" s="74"/>
-      <c r="E53" s="74"/>
+      <c r="D53" s="75"/>
+      <c r="E53" s="75"/>
       <c r="F53" s="63"/>
       <c r="G53" s="64"/>
       <c r="H53" s="64"/>
       <c r="I53" s="64"/>
     </row>
     <row r="54" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="75" t="s">
+      <c r="A54" s="76" t="s">
         <v>1119</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="C54" s="74" t="s">
+      <c r="C54" s="75" t="s">
         <v>1121</v>
       </c>
-      <c r="D54" s="74"/>
-      <c r="E54" s="74"/>
+      <c r="D54" s="75"/>
+      <c r="E54" s="75"/>
       <c r="F54" s="63"/>
       <c r="G54" s="64"/>
       <c r="H54" s="64"/>
       <c r="I54" s="64"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="75"/>
+      <c r="A55" s="76"/>
       <c r="B55" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="C55" s="74" t="s">
+      <c r="C55" s="75" t="s">
         <v>1123</v>
       </c>
-      <c r="D55" s="74"/>
-      <c r="E55" s="74"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="75"/>
       <c r="F55" s="63"/>
       <c r="G55" s="64"/>
       <c r="H55" s="64"/>
       <c r="I55" s="64"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="75"/>
+      <c r="A56" s="76"/>
       <c r="B56" s="5" t="s">
         <v>1124</v>
       </c>
-      <c r="C56" s="74" t="s">
+      <c r="C56" s="75" t="s">
         <v>1125</v>
       </c>
-      <c r="D56" s="74"/>
-      <c r="E56" s="74"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
       <c r="F56" s="63"/>
       <c r="G56" s="64"/>
       <c r="H56" s="64"/>
       <c r="I56" s="64"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="75"/>
+      <c r="A57" s="76"/>
       <c r="B57" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="C57" s="74" t="s">
+      <c r="C57" s="75" t="s">
         <v>1127</v>
       </c>
-      <c r="D57" s="74"/>
-      <c r="E57" s="74"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
       <c r="F57" s="63"/>
       <c r="G57" s="64"/>
       <c r="H57" s="64"/>
       <c r="I57" s="64"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
+      <c r="A58" s="76"/>
       <c r="B58" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="C58" s="74" t="s">
+      <c r="C58" s="75" t="s">
         <v>1129</v>
       </c>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
       <c r="F58" s="63"/>
       <c r="G58" s="64"/>
       <c r="H58" s="64"/>
@@ -27931,88 +27932,88 @@
       <c r="B59" s="5" t="s">
         <v>1063</v>
       </c>
-      <c r="C59" s="74" t="s">
+      <c r="C59" s="75" t="s">
         <v>1131</v>
       </c>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
       <c r="F59" s="63"/>
       <c r="G59" s="64"/>
       <c r="H59" s="64"/>
       <c r="I59" s="64"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="75" t="s">
+      <c r="A60" s="76" t="s">
         <v>1132</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>1133</v>
       </c>
-      <c r="C60" s="74" t="s">
+      <c r="C60" s="75" t="s">
         <v>1134</v>
       </c>
-      <c r="D60" s="74"/>
-      <c r="E60" s="74"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
       <c r="F60" s="63"/>
       <c r="G60" s="64"/>
       <c r="H60" s="64"/>
       <c r="I60" s="64"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="75"/>
+      <c r="A61" s="76"/>
       <c r="B61" s="5" t="s">
         <v>1135</v>
       </c>
-      <c r="C61" s="74" t="s">
+      <c r="C61" s="75" t="s">
         <v>1136</v>
       </c>
-      <c r="D61" s="74"/>
-      <c r="E61" s="74"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
       <c r="F61" s="63"/>
       <c r="G61" s="64"/>
       <c r="H61" s="64"/>
       <c r="I61" s="64"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="75"/>
+      <c r="A62" s="76"/>
       <c r="B62" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="C62" s="74" t="s">
+      <c r="C62" s="75" t="s">
         <v>1138</v>
       </c>
-      <c r="D62" s="74"/>
-      <c r="E62" s="74"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
       <c r="F62" s="63"/>
       <c r="G62" s="64"/>
       <c r="H62" s="64"/>
       <c r="I62" s="64"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
+      <c r="A63" s="76"/>
       <c r="B63" s="5" t="s">
         <v>1139</v>
       </c>
-      <c r="C63" s="74" t="s">
+      <c r="C63" s="75" t="s">
         <v>1140</v>
       </c>
-      <c r="D63" s="74"/>
-      <c r="E63" s="74"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
       <c r="F63" s="63"/>
       <c r="G63" s="64"/>
       <c r="H63" s="64"/>
       <c r="I63" s="64"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="75"/>
+      <c r="A64" s="76"/>
       <c r="B64" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="C64" s="74" t="s">
+      <c r="C64" s="75" t="s">
         <v>1142</v>
       </c>
-      <c r="D64" s="74"/>
-      <c r="E64" s="74"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
       <c r="F64" s="63"/>
       <c r="G64" s="64"/>
       <c r="H64" s="64"/>
@@ -28020,30 +28021,72 @@
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A60:A64"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="C46:E46"/>
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="C48:E48"/>
@@ -28068,72 +28111,30 @@
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="A60:A64"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F18:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -28401,12 +28402,12 @@
       <c r="B14" s="7" t="s">
         <v>1696</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -28626,6 +28627,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
@@ -28640,11 +28646,6 @@
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -29214,12 +29215,12 @@
       <c r="E17" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F17" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -29228,10 +29229,10 @@
       <c r="B18" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="33"/>
       <c r="F18" s="64"/>
       <c r="G18" s="64"/>
@@ -29245,10 +29246,10 @@
       <c r="B19" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33"/>
       <c r="F19" s="64"/>
       <c r="G19" s="64"/>
@@ -29262,10 +29263,10 @@
       <c r="B20" t="s">
         <v>152</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33"/>
       <c r="F20" s="64"/>
       <c r="G20" s="64"/>
@@ -29279,10 +29280,10 @@
       <c r="B21" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="33"/>
       <c r="F21" s="64"/>
       <c r="G21" s="64"/>
@@ -29321,12 +29322,12 @@
       <c r="E24" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="62" t="s">
+      <c r="F24" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -29335,10 +29336,10 @@
       <c r="B25">
         <v>413464008</v>
       </c>
-      <c r="C25" s="68" t="s">
+      <c r="C25" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="68"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="33"/>
       <c r="F25" s="64"/>
       <c r="G25" s="64"/>
@@ -29352,10 +29353,10 @@
       <c r="B26">
         <v>413582008</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D26" s="68"/>
+      <c r="D26" s="62"/>
       <c r="E26" s="33"/>
       <c r="F26" s="64"/>
       <c r="G26" s="64"/>
@@ -29369,10 +29370,10 @@
       <c r="B27">
         <v>413773004</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D27" s="68"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="33"/>
       <c r="F27" s="64"/>
       <c r="G27" s="64"/>
@@ -29386,10 +29387,10 @@
       <c r="B28">
         <v>414408004</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D28" s="68"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="33"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
@@ -29403,10 +29404,10 @@
       <c r="B29">
         <v>415794004</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D29" s="68"/>
+      <c r="D29" s="62"/>
       <c r="E29" s="33"/>
       <c r="F29" s="64"/>
       <c r="G29" s="64"/>
@@ -29415,13 +29416,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C28:D28"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="F17:I17"/>
@@ -29434,6 +29428,13 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29634,12 +29635,12 @@
       <c r="E9" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="F9" s="62" t="s">
+      <c r="F9" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -29648,10 +29649,10 @@
       <c r="B10" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="68"/>
+      <c r="D10" s="62"/>
       <c r="E10" s="33"/>
       <c r="F10" s="63"/>
       <c r="G10" s="64"/>
@@ -29665,10 +29666,10 @@
       <c r="B11" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="68"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="33"/>
       <c r="F11" s="63"/>
       <c r="G11" s="64"/>
@@ -29682,10 +29683,10 @@
       <c r="B12" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="68"/>
+      <c r="D12" s="62"/>
       <c r="E12" s="33"/>
       <c r="F12" s="63"/>
       <c r="G12" s="64"/>
@@ -29699,10 +29700,10 @@
       <c r="B13" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="F13" s="63"/>
       <c r="G13" s="64"/>
       <c r="H13" s="64"/>
@@ -29715,10 +29716,10 @@
       <c r="B14" t="s">
         <v>181</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="F14" s="63"/>
       <c r="G14" s="64"/>
       <c r="H14" s="64"/>
@@ -29731,10 +29732,10 @@
       <c r="B15" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="F15" s="63"/>
       <c r="G15" s="64"/>
       <c r="H15" s="64"/>
@@ -29747,10 +29748,10 @@
       <c r="B16" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="F16" s="63"/>
       <c r="G16" s="64"/>
       <c r="H16" s="64"/>
@@ -29763,10 +29764,10 @@
       <c r="B17" t="s">
         <v>187</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="64"/>
       <c r="H17" s="64"/>
@@ -29779,10 +29780,10 @@
       <c r="B18" t="s">
         <v>152</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64"/>
       <c r="H18" s="64"/>
@@ -29799,6 +29800,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="F18:I18"/>
@@ -29806,18 +29819,6 @@
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:I11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -30000,12 +30001,12 @@
       <c r="E8" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
@@ -30014,10 +30015,10 @@
       <c r="B9" t="s">
         <v>198</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="68"/>
+      <c r="D9" s="62"/>
       <c r="E9" s="33"/>
       <c r="F9" s="63"/>
       <c r="G9" s="64"/>
@@ -30031,10 +30032,10 @@
       <c r="B10" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="68"/>
+      <c r="D10" s="62"/>
       <c r="E10" s="33"/>
       <c r="F10" s="63"/>
       <c r="G10" s="64"/>
@@ -30048,10 +30049,10 @@
       <c r="B11" t="s">
         <v>202</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D11" s="68"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="33"/>
       <c r="F11" s="63"/>
       <c r="G11" s="64"/>
@@ -30065,10 +30066,10 @@
       <c r="B12" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="68"/>
+      <c r="D12" s="62"/>
       <c r="F12" s="63"/>
       <c r="G12" s="64"/>
       <c r="H12" s="64"/>
@@ -30081,10 +30082,10 @@
       <c r="B13" t="s">
         <v>206</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="F13" s="63"/>
       <c r="G13" s="64"/>
       <c r="H13" s="64"/>
@@ -30097,10 +30098,10 @@
       <c r="B14" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="F14" s="63"/>
       <c r="G14" s="64"/>
       <c r="H14" s="64"/>
@@ -30140,12 +30141,12 @@
       <c r="E18" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="F18" s="62" t="s">
+      <c r="F18" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
@@ -30154,10 +30155,10 @@
       <c r="B19">
         <v>394579002</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64"/>
@@ -30171,10 +30172,10 @@
       <c r="B20">
         <v>419772000</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64"/>
@@ -30188,10 +30189,10 @@
       <c r="B21">
         <v>394814009</v>
       </c>
-      <c r="C21" s="68" t="s">
+      <c r="C21" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="33"/>
       <c r="F21" s="63"/>
       <c r="G21" s="64"/>
@@ -30205,10 +30206,10 @@
       <c r="B22">
         <v>394811001</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="62"/>
       <c r="F22" s="63"/>
       <c r="G22" s="64"/>
       <c r="H22" s="64"/>
@@ -30221,10 +30222,10 @@
       <c r="B23">
         <v>419192003</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="62"/>
       <c r="F23" s="63"/>
       <c r="G23" s="64"/>
       <c r="H23" s="64"/>
@@ -30237,10 +30238,10 @@
       <c r="B24">
         <v>394593009</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="68"/>
+      <c r="D24" s="62"/>
       <c r="F24" s="63"/>
       <c r="G24" s="64"/>
       <c r="H24" s="64"/>
@@ -30279,6 +30280,19 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="F23:I23"/>
@@ -30292,19 +30306,6 @@
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:I10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -30336,7 +30337,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63947D01-B4BD-4B2C-8904-F72EDA2AD99B}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
@@ -30475,12 +30476,12 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>1811</v>
+        <v>2031</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>330</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -30489,7 +30490,7 @@
         <v>119</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1812</v>
+        <v>2047</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -30498,10 +30499,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>1158</v>
+        <v>1811</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
@@ -30510,7 +30511,7 @@
         <v>119</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1159</v>
+        <v>1812</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -30519,19 +30520,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>230</v>
+        <v>1158</v>
       </c>
       <c r="B9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>232</v>
+        <v>1159</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -30540,19 +30541,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>1681</v>
+        <v>230</v>
       </c>
       <c r="B10" t="s">
-        <v>1682</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1683</v>
+        <v>232</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
@@ -30561,19 +30562,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>233</v>
+        <v>1681</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>1682</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>235</v>
+        <v>1683</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
@@ -30582,10 +30583,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
@@ -30594,7 +30595,7 @@
         <v>119</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -30603,19 +30604,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="C13" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
         <v>119</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -30624,89 +30625,93 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" t="s">
         <v>119</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1321</v>
+        <v>240</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="35" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B18" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="32" t="s">
+      <c r="D18" s="7"/>
+      <c r="E18" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F18" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
         <v>245</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>246</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B19" t="s">
-        <v>248</v>
-      </c>
-      <c r="C19" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64"/>
@@ -30715,15 +30720,15 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
-      </c>
-      <c r="C20" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64"/>
@@ -30732,15 +30737,15 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>252</v>
-      </c>
-      <c r="C21" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="68"/>
+      <c r="D21" s="62"/>
       <c r="E21" s="33"/>
       <c r="F21" s="63"/>
       <c r="G21" s="64"/>
@@ -30749,15 +30754,15 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="68"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="33"/>
       <c r="F22" s="63"/>
       <c r="G22" s="64"/>
@@ -30766,15 +30771,15 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
-      </c>
-      <c r="C23" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="68"/>
+      <c r="D23" s="62"/>
       <c r="E23" s="33"/>
       <c r="F23" s="63"/>
       <c r="G23" s="64"/>
@@ -30783,15 +30788,15 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
-      </c>
-      <c r="C24" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D24" s="68"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="33"/>
       <c r="F24" s="63"/>
       <c r="G24" s="64"/>
@@ -30800,15 +30805,15 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>260</v>
-      </c>
-      <c r="C25" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="68"/>
+      <c r="D25" s="62"/>
       <c r="E25" s="33"/>
       <c r="F25" s="63"/>
       <c r="G25" s="64"/>
@@ -30817,84 +30822,84 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="C26" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D26" s="68"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="63"/>
       <c r="G26" s="64"/>
       <c r="H26" s="64"/>
       <c r="I26" s="64"/>
     </row>
-    <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="62"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="64"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="35" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B30" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="32" t="s">
+      <c r="D30" s="7"/>
+      <c r="E30" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="F29" s="62" t="s">
+      <c r="F30" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="36" t="s">
         <v>1298</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>264</v>
       </c>
-      <c r="C30" s="68" t="s">
+      <c r="C31" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="68"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C31" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="68"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="33"/>
       <c r="F31" s="63"/>
       <c r="G31" s="64"/>
@@ -30903,15 +30908,15 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
-      </c>
-      <c r="C32" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="68"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="33"/>
       <c r="F32" s="63"/>
       <c r="G32" s="64"/>
@@ -30920,15 +30925,15 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B33" t="s">
-        <v>267</v>
-      </c>
-      <c r="C33" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="C33" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="68"/>
+      <c r="D33" s="62"/>
       <c r="E33" s="33"/>
       <c r="F33" s="63"/>
       <c r="G33" s="64"/>
@@ -30937,15 +30942,15 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B34" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D34" s="68"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="33"/>
       <c r="F34" s="63"/>
       <c r="G34" s="64"/>
@@ -30954,15 +30959,15 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B35" t="s">
-        <v>269</v>
-      </c>
-      <c r="C35" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="C35" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="68"/>
+      <c r="D35" s="62"/>
       <c r="E35" s="33"/>
       <c r="F35" s="63"/>
       <c r="G35" s="64"/>
@@ -30971,85 +30976,83 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B36" t="s">
+        <v>269</v>
+      </c>
+      <c r="C36" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="D36" s="62"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>1292</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>1291</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>148</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-    </row>
-    <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="39" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="35" t="s">
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="32" t="s">
+      <c r="D40" s="7"/>
+      <c r="E40" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F40" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G39" s="62"/>
-      <c r="H39" s="62"/>
-      <c r="I39" s="62"/>
-    </row>
-    <row r="40" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="38" t="s">
+      <c r="G40" s="65"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+    </row>
+    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="38" t="s">
         <v>272</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>273</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="C41" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="33" t="s">
-        <v>2033</v>
-      </c>
-      <c r="F40" s="63"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-    </row>
-    <row r="41" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B41" t="s">
-        <v>275</v>
-      </c>
-      <c r="C41" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="68"/>
+      <c r="D41" s="62"/>
       <c r="E41" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31058,17 +31061,17 @@
       <c r="H41" s="64"/>
       <c r="I41" s="64"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B42" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="C42" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D42" s="68"/>
+      <c r="D42" s="62"/>
       <c r="E42" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31079,15 +31082,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B43" t="s">
-        <v>279</v>
-      </c>
-      <c r="C43" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="C43" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="68"/>
+      <c r="D43" s="62"/>
       <c r="E43" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31098,15 +31101,15 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B44" t="s">
-        <v>281</v>
-      </c>
-      <c r="C44" s="68" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="68"/>
+      <c r="D44" s="62"/>
       <c r="E44" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31115,17 +31118,17 @@
       <c r="H44" s="64"/>
       <c r="I44" s="64"/>
     </row>
-    <row r="45" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B45" t="s">
-        <v>283</v>
-      </c>
-      <c r="C45" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="C45" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D45" s="68"/>
+      <c r="D45" s="62"/>
       <c r="E45" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31134,17 +31137,17 @@
       <c r="H45" s="64"/>
       <c r="I45" s="64"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B46" t="s">
-        <v>285</v>
-      </c>
-      <c r="C46" s="68" t="s">
+        <v>283</v>
+      </c>
+      <c r="C46" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D46" s="68"/>
+      <c r="D46" s="62"/>
       <c r="E46" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31155,15 +31158,15 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C47" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="C47" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D47" s="68"/>
+      <c r="D47" s="62"/>
       <c r="E47" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31174,15 +31177,15 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s">
-        <v>289</v>
-      </c>
-      <c r="C48" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="C48" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D48" s="68"/>
+      <c r="D48" s="62"/>
       <c r="E48" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31193,15 +31196,15 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>151</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
-      </c>
-      <c r="C49" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="C49" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D49" s="68"/>
+      <c r="D49" s="62"/>
       <c r="E49" s="33" t="s">
         <v>2033</v>
       </c>
@@ -31212,123 +31215,136 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>2035</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s">
-        <v>2034</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2042</v>
-      </c>
-      <c r="E50" s="78" t="s">
-        <v>2043</v>
-      </c>
-      <c r="F50" s="77"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
+        <v>152</v>
+      </c>
+      <c r="C50" s="62" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="62"/>
+      <c r="E50" s="33" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F50" s="63"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="64"/>
+      <c r="I50" s="64"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B51" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="C51" t="s">
         <v>2042</v>
       </c>
-      <c r="E51" s="78" t="s">
-        <v>2044</v>
-      </c>
-      <c r="F51" s="77"/>
+      <c r="E51" s="33" t="s">
+        <v>2043</v>
+      </c>
+      <c r="F51" s="10"/>
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
       <c r="I51" s="10"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="B52" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="C52" t="s">
         <v>2042</v>
       </c>
-      <c r="E52" s="78" t="s">
-        <v>2045</v>
-      </c>
-      <c r="F52" s="77"/>
+      <c r="E52" s="33" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F52" s="10"/>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
       <c r="I52" s="10"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="B53" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="C53" t="s">
         <v>2042</v>
       </c>
-      <c r="E53" s="78" t="s">
-        <v>2046</v>
-      </c>
-      <c r="F53" s="77"/>
+      <c r="E53" s="33" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F53" s="10"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="55" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+    </row>
+    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
         <v>1813</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="35" t="s">
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="35" t="s">
         <v>1814</v>
       </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="32" t="s">
+      <c r="D57" s="7"/>
+      <c r="E57" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F56" s="62" t="s">
+      <c r="F57" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G56" s="62"/>
-      <c r="H56" s="62"/>
-      <c r="I56" s="62"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="63"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="36"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="33"/>
       <c r="F58" s="63"/>
       <c r="G58" s="64"/>
       <c r="H58" s="64"/>
@@ -31370,71 +31386,77 @@
       <c r="H64" s="64"/>
       <c r="I64" s="64"/>
     </row>
+    <row r="65" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F65" s="63"/>
+      <c r="G65" s="64"/>
+      <c r="H65" s="64"/>
+      <c r="I65" s="64"/>
+    </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="F42:I42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="F44:I44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="F45:I45"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F50:I50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -31445,19 +31467,19 @@
           <x14:formula1>
             <xm:f>'Dataset Intro'!$Q$19:$Q$25</xm:f>
           </x14:formula1>
-          <xm:sqref>H12:H14 H3:H9</xm:sqref>
+          <xm:sqref>H13:H15 H3:H10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B24D9712-92FD-4FAF-9A6E-1E8EBDFE76B8}">
           <x14:formula1>
             <xm:f>'Dataset Intro'!$Q$2:$Q$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F12:F14 F3:F9</xm:sqref>
+          <xm:sqref>F13:F15 F3:F10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6D8C75E5-5A65-4DE7-A33D-07775C2BE52D}">
           <x14:formula1>
             <xm:f>'Dataset Intro'!$Q$13:$Q$15</xm:f>
           </x14:formula1>
-          <xm:sqref>G12:G14 G3:G9</xm:sqref>
+          <xm:sqref>G13:G15 G3:G10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -31727,12 +31749,12 @@
       <c r="E13" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="F13" s="62" t="s">
+      <c r="F13" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
@@ -31741,10 +31763,10 @@
       <c r="B14" t="s">
         <v>311</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="34" t="s">
         <v>312</v>
       </c>
@@ -31760,10 +31782,10 @@
       <c r="B15" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="34" t="s">
         <v>315</v>
       </c>
@@ -31779,10 +31801,10 @@
       <c r="B16" t="s">
         <v>250</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="34" t="s">
         <v>316</v>
       </c>
@@ -31798,10 +31820,10 @@
       <c r="B17" t="s">
         <v>318</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="34" t="s">
         <v>319</v>
       </c>
@@ -31817,10 +31839,10 @@
       <c r="B18" t="s">
         <v>254</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="34" t="s">
         <v>320</v>
       </c>
@@ -31836,10 +31858,10 @@
       <c r="B19" t="s">
         <v>260</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="34" t="s">
         <v>322</v>
       </c>
@@ -31855,10 +31877,10 @@
       <c r="B20" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="34" t="s">
         <v>323</v>
       </c>
@@ -31914,6 +31936,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:I15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C20:D20"/>
@@ -31924,13 +31953,6 @@
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="F19:I19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:I15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -32188,12 +32210,12 @@
       <c r="E12" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -32202,10 +32224,10 @@
       <c r="B13" t="s">
         <v>343</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D13" s="68"/>
+      <c r="D13" s="62"/>
       <c r="E13" s="33"/>
       <c r="F13" s="63"/>
       <c r="G13" s="64"/>
@@ -32219,10 +32241,10 @@
       <c r="B14" t="s">
         <v>346</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D14" s="68"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="33"/>
       <c r="F14" s="63"/>
       <c r="G14" s="64"/>
@@ -32236,10 +32258,10 @@
       <c r="B15" t="s">
         <v>348</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D15" s="68"/>
+      <c r="D15" s="62"/>
       <c r="E15" s="33"/>
       <c r="F15" s="63"/>
       <c r="G15" s="64"/>
@@ -32253,10 +32275,10 @@
       <c r="B16" t="s">
         <v>350</v>
       </c>
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D16" s="68"/>
+      <c r="D16" s="62"/>
       <c r="E16" s="33"/>
       <c r="F16" s="63"/>
       <c r="G16" s="64"/>
@@ -32270,10 +32292,10 @@
       <c r="B17" t="s">
         <v>352</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="C17" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D17" s="68"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="33"/>
       <c r="F17" s="63"/>
       <c r="G17" s="64"/>
@@ -32287,10 +32309,10 @@
       <c r="B18" t="s">
         <v>354</v>
       </c>
-      <c r="C18" s="68" t="s">
+      <c r="C18" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D18" s="68"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="33"/>
       <c r="F18" s="63"/>
       <c r="G18" s="64"/>
@@ -32304,10 +32326,10 @@
       <c r="B19" t="s">
         <v>356</v>
       </c>
-      <c r="C19" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="33"/>
       <c r="F19" s="63"/>
       <c r="G19" s="64"/>
@@ -32321,10 +32343,10 @@
       <c r="B20" t="s">
         <v>358</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="62" t="s">
         <v>344</v>
       </c>
-      <c r="D20" s="68"/>
+      <c r="D20" s="62"/>
       <c r="E20" s="33"/>
       <c r="F20" s="63"/>
       <c r="G20" s="64"/>
@@ -32333,11 +32355,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="C20:D20"/>
@@ -32350,6 +32367,11 @@
     <mergeCell ref="F20:I20"/>
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32381,6 +32403,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="eda01c43-580c-44af-a5fd-4ea1802e476c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004592A3ADBB772D4689FCD56C8516F45D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e6dee92c918a6173969cc6829137ba01">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c" xmlns:ns3="eda01c43-580c-44af-a5fd-4ea1802e476c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2e0be94b10bd652582aed8d62fec2d74" ns2:_="" ns3:_="">
     <xsd:import namespace="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c"/>
@@ -32609,41 +32651,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="eda01c43-580c-44af-a5fd-4ea1802e476c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0A127A-D0D0-4182-84ED-7D64B945D928}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB40FF6F-009E-4D48-B4D3-33D1A3C62497}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c"/>
-    <ds:schemaRef ds:uri="eda01c43-580c-44af-a5fd-4ea1802e476c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -32666,9 +32677,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB40FF6F-009E-4D48-B4D3-33D1A3C62497}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0A127A-D0D0-4182-84ED-7D64B945D928}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c"/>
+    <ds:schemaRef ds:uri="eda01c43-580c-44af-a5fd-4ea1802e476c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/CommonDataModel.xlsx
+++ b/CommonDataModel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\db\dt4h\common-data-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\doguk\OneDrive\Desktop\DT4H\Repositories\common-data-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C732E6CA-4B70-4A8C-B92F-57B081F366F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD04997D-ADFB-4592-A021-C32AA3CAB63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="10635" windowWidth="38640" windowHeight="21120" tabRatio="901" firstSheet="10" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="901" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="10" r:id="rId1"/>
@@ -864,7 +864,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="2137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4817" uniqueCount="2142">
   <si>
     <t>Required</t>
   </si>
@@ -7295,6 +7295,21 @@
   </si>
   <si>
     <t>The heading of a single note within the visit note document, identifying which part of the clinical record the accompanying text belongs to (e.g. "Reason for presentation", "Anamnesis", "Physical examination", "Conclusion", "Management plan"). A visit note may contain several sections.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  referenceRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    high</t>
+  </si>
+  <si>
+    <t>SimpleQuantity</t>
+  </si>
+  <si>
+    <t>Provides reference ranges for the measurement.</t>
+  </si>
+  <si>
+    <t>High range</t>
   </si>
 </sst>
 </file>
@@ -7673,22 +7688,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9082,6 +9097,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="F15:I15"/>
     <mergeCell ref="F12:I12"/>
@@ -9089,17 +9115,6 @@
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:I20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9958,41 +9973,14 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
@@ -10009,14 +9997,41 @@
     <mergeCell ref="F31:I31"/>
     <mergeCell ref="F32:I32"/>
     <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E41" xr:uid="{14C408A9-075A-4B77-84C3-9F689D082B68}">
@@ -10716,13 +10731,13 @@
         <v>461</v>
       </c>
       <c r="D39" s="67"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="72" t="s">
+      <c r="E39" s="70"/>
+      <c r="F39" s="73" t="s">
         <v>462</v>
       </c>
-      <c r="G39" s="72"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="72"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="42" t="s">
@@ -10731,11 +10746,11 @@
       <c r="B40" s="42" t="s">
         <v>464</v>
       </c>
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="71" t="s">
         <v>465</v>
       </c>
-      <c r="D40" s="69"/>
-      <c r="E40" s="70"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="72"/>
       <c r="F40" s="68"/>
       <c r="G40" s="66"/>
       <c r="H40" s="66"/>
@@ -10748,11 +10763,11 @@
       <c r="B41" s="42" t="s">
         <v>467</v>
       </c>
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="71" t="s">
         <v>468</v>
       </c>
-      <c r="D41" s="69"/>
-      <c r="E41" s="70"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="72"/>
       <c r="F41" s="68"/>
       <c r="G41" s="66"/>
       <c r="H41" s="66"/>
@@ -10765,11 +10780,11 @@
       <c r="B42" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="C42" s="69" t="s">
+      <c r="C42" s="71" t="s">
         <v>471</v>
       </c>
-      <c r="D42" s="69"/>
-      <c r="E42" s="70"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="72"/>
       <c r="F42" s="68"/>
       <c r="G42" s="66"/>
       <c r="H42" s="66"/>
@@ -10782,11 +10797,11 @@
       <c r="B43" s="42" t="s">
         <v>473</v>
       </c>
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="71" t="s">
         <v>1996</v>
       </c>
-      <c r="D43" s="69"/>
-      <c r="E43" s="70"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="72"/>
       <c r="F43" s="68"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
@@ -10799,11 +10814,11 @@
       <c r="B44" s="42" t="s">
         <v>475</v>
       </c>
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="71" t="s">
         <v>476</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="70"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="72"/>
       <c r="F44" s="68"/>
       <c r="G44" s="66"/>
       <c r="H44" s="66"/>
@@ -10816,11 +10831,11 @@
       <c r="B45" s="42" t="s">
         <v>478</v>
       </c>
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="71" t="s">
         <v>479</v>
       </c>
-      <c r="D45" s="69"/>
-      <c r="E45" s="70"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="72"/>
       <c r="F45" s="68"/>
       <c r="G45" s="66"/>
       <c r="H45" s="66"/>
@@ -10833,11 +10848,11 @@
       <c r="B46" s="42" t="s">
         <v>481</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="71" t="s">
         <v>482</v>
       </c>
-      <c r="D46" s="69"/>
-      <c r="E46" s="70"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="72"/>
       <c r="F46" s="68"/>
       <c r="G46" s="66"/>
       <c r="H46" s="66"/>
@@ -10850,11 +10865,11 @@
       <c r="B47" s="42" t="s">
         <v>484</v>
       </c>
-      <c r="C47" s="69" t="s">
+      <c r="C47" s="71" t="s">
         <v>2006</v>
       </c>
-      <c r="D47" s="69"/>
-      <c r="E47" s="70"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="72"/>
       <c r="F47" s="68"/>
       <c r="G47" s="66"/>
       <c r="H47" s="66"/>
@@ -10867,11 +10882,11 @@
       <c r="B48" s="42" t="s">
         <v>485</v>
       </c>
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="71" t="s">
         <v>1997</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="70"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="72"/>
       <c r="F48" s="68"/>
       <c r="G48" s="66"/>
       <c r="H48" s="66"/>
@@ -10884,11 +10899,11 @@
       <c r="B49" s="42" t="s">
         <v>487</v>
       </c>
-      <c r="C49" s="69" t="s">
+      <c r="C49" s="71" t="s">
         <v>488</v>
       </c>
-      <c r="D49" s="69"/>
-      <c r="E49" s="70"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="72"/>
       <c r="F49" s="68"/>
       <c r="G49" s="66"/>
       <c r="H49" s="66"/>
@@ -10901,11 +10916,11 @@
       <c r="B50" s="42" t="s">
         <v>490</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="C50" s="71" t="s">
         <v>491</v>
       </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="70"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="72"/>
       <c r="F50" s="68"/>
       <c r="G50" s="66"/>
       <c r="H50" s="66"/>
@@ -10918,11 +10933,11 @@
       <c r="B51" s="42" t="s">
         <v>493</v>
       </c>
-      <c r="C51" s="69" t="s">
+      <c r="C51" s="71" t="s">
         <v>494</v>
       </c>
-      <c r="D51" s="69"/>
-      <c r="E51" s="70"/>
+      <c r="D51" s="71"/>
+      <c r="E51" s="72"/>
       <c r="F51" s="68"/>
       <c r="G51" s="66"/>
       <c r="H51" s="66"/>
@@ -10935,11 +10950,11 @@
       <c r="B52" s="42" t="s">
         <v>496</v>
       </c>
-      <c r="C52" s="69" t="s">
+      <c r="C52" s="71" t="s">
         <v>497</v>
       </c>
-      <c r="D52" s="69"/>
-      <c r="E52" s="70"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="72"/>
       <c r="F52" s="68"/>
       <c r="G52" s="66"/>
       <c r="H52" s="66"/>
@@ -10952,11 +10967,11 @@
       <c r="B53" s="42" t="s">
         <v>499</v>
       </c>
-      <c r="C53" s="69" t="s">
+      <c r="C53" s="71" t="s">
         <v>500</v>
       </c>
-      <c r="D53" s="69"/>
-      <c r="E53" s="70"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="72"/>
       <c r="F53" s="68"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
@@ -10969,11 +10984,11 @@
       <c r="B54" s="42" t="s">
         <v>502</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="71" t="s">
         <v>503</v>
       </c>
-      <c r="D54" s="69"/>
-      <c r="E54" s="70"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="72"/>
       <c r="F54" s="68"/>
       <c r="G54" s="66"/>
       <c r="H54" s="66"/>
@@ -10986,11 +11001,11 @@
       <c r="B55" s="42" t="s">
         <v>505</v>
       </c>
-      <c r="C55" s="69" t="s">
+      <c r="C55" s="71" t="s">
         <v>506</v>
       </c>
-      <c r="D55" s="69"/>
-      <c r="E55" s="70"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="72"/>
       <c r="F55" s="68"/>
       <c r="G55" s="66"/>
       <c r="H55" s="66"/>
@@ -11003,11 +11018,11 @@
       <c r="B56" s="42" t="s">
         <v>508</v>
       </c>
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="71" t="s">
         <v>509</v>
       </c>
-      <c r="D56" s="69"/>
-      <c r="E56" s="70"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="72"/>
       <c r="F56" s="68"/>
       <c r="G56" s="66"/>
       <c r="H56" s="66"/>
@@ -11020,11 +11035,11 @@
       <c r="B57" s="42" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="71" t="s">
         <v>512</v>
       </c>
-      <c r="D57" s="69"/>
-      <c r="E57" s="70"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="72"/>
       <c r="F57" s="68"/>
       <c r="G57" s="66"/>
       <c r="H57" s="66"/>
@@ -11037,11 +11052,11 @@
       <c r="B58" s="42" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="71" t="s">
         <v>515</v>
       </c>
-      <c r="D58" s="69"/>
-      <c r="E58" s="70"/>
+      <c r="D58" s="71"/>
+      <c r="E58" s="72"/>
       <c r="F58" s="68"/>
       <c r="G58" s="66"/>
       <c r="H58" s="66"/>
@@ -11054,11 +11069,11 @@
       <c r="B59" s="42" t="s">
         <v>517</v>
       </c>
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="71" t="s">
         <v>518</v>
       </c>
-      <c r="D59" s="69"/>
-      <c r="E59" s="70"/>
+      <c r="D59" s="71"/>
+      <c r="E59" s="72"/>
       <c r="F59" s="68"/>
       <c r="G59" s="66"/>
       <c r="H59" s="66"/>
@@ -11071,11 +11086,11 @@
       <c r="B60" s="42" t="s">
         <v>520</v>
       </c>
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="71" t="s">
         <v>521</v>
       </c>
-      <c r="D60" s="69"/>
-      <c r="E60" s="70"/>
+      <c r="D60" s="71"/>
+      <c r="E60" s="72"/>
       <c r="F60" s="68"/>
       <c r="G60" s="66"/>
       <c r="H60" s="66"/>
@@ -11088,11 +11103,11 @@
       <c r="B61" s="42" t="s">
         <v>523</v>
       </c>
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="71" t="s">
         <v>524</v>
       </c>
-      <c r="D61" s="69"/>
-      <c r="E61" s="70"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="72"/>
       <c r="F61" s="68"/>
       <c r="G61" s="66"/>
       <c r="H61" s="66"/>
@@ -11105,11 +11120,11 @@
       <c r="B62" s="42" t="s">
         <v>526</v>
       </c>
-      <c r="C62" s="69" t="s">
+      <c r="C62" s="71" t="s">
         <v>527</v>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="70"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="72"/>
       <c r="F62" s="68"/>
       <c r="G62" s="66"/>
       <c r="H62" s="66"/>
@@ -11122,11 +11137,11 @@
       <c r="B63" s="42" t="s">
         <v>529</v>
       </c>
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="71" t="s">
         <v>530</v>
       </c>
-      <c r="D63" s="69"/>
-      <c r="E63" s="70"/>
+      <c r="D63" s="71"/>
+      <c r="E63" s="72"/>
       <c r="F63" s="68"/>
       <c r="G63" s="66"/>
       <c r="H63" s="66"/>
@@ -11139,11 +11154,11 @@
       <c r="B64" s="42" t="s">
         <v>531</v>
       </c>
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="71" t="s">
         <v>532</v>
       </c>
-      <c r="D64" s="69"/>
-      <c r="E64" s="70"/>
+      <c r="D64" s="71"/>
+      <c r="E64" s="72"/>
       <c r="F64" s="68"/>
       <c r="G64" s="66"/>
       <c r="H64" s="66"/>
@@ -11156,11 +11171,11 @@
       <c r="B65" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="C65" s="69" t="s">
+      <c r="C65" s="71" t="s">
         <v>535</v>
       </c>
-      <c r="D65" s="69"/>
-      <c r="E65" s="70"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="72"/>
       <c r="F65" s="68"/>
       <c r="G65" s="66"/>
       <c r="H65" s="66"/>
@@ -11173,11 +11188,11 @@
       <c r="B66" s="42" t="s">
         <v>537</v>
       </c>
-      <c r="C66" s="69" t="s">
+      <c r="C66" s="71" t="s">
         <v>1998</v>
       </c>
-      <c r="D66" s="69"/>
-      <c r="E66" s="70"/>
+      <c r="D66" s="71"/>
+      <c r="E66" s="72"/>
       <c r="F66" s="68"/>
       <c r="G66" s="66"/>
       <c r="H66" s="66"/>
@@ -11190,11 +11205,11 @@
       <c r="B67" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="C67" s="69" t="s">
+      <c r="C67" s="71" t="s">
         <v>540</v>
       </c>
-      <c r="D67" s="69"/>
-      <c r="E67" s="70"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="72"/>
       <c r="F67" s="68"/>
       <c r="G67" s="66"/>
       <c r="H67" s="66"/>
@@ -11207,11 +11222,11 @@
       <c r="B68" s="42" t="s">
         <v>542</v>
       </c>
-      <c r="C68" s="69" t="s">
+      <c r="C68" s="71" t="s">
         <v>543</v>
       </c>
-      <c r="D68" s="69"/>
-      <c r="E68" s="70"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="72"/>
       <c r="F68" s="68"/>
       <c r="G68" s="66"/>
       <c r="H68" s="66"/>
@@ -11224,11 +11239,11 @@
       <c r="B69" s="42" t="s">
         <v>545</v>
       </c>
-      <c r="C69" s="69" t="s">
+      <c r="C69" s="71" t="s">
         <v>546</v>
       </c>
-      <c r="D69" s="69"/>
-      <c r="E69" s="70"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="72"/>
       <c r="F69" s="68"/>
       <c r="G69" s="66"/>
       <c r="H69" s="66"/>
@@ -11241,11 +11256,11 @@
       <c r="B70" s="42" t="s">
         <v>548</v>
       </c>
-      <c r="C70" s="69" t="s">
+      <c r="C70" s="71" t="s">
         <v>549</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="70"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="72"/>
       <c r="F70" s="68"/>
       <c r="G70" s="66"/>
       <c r="H70" s="66"/>
@@ -11258,11 +11273,11 @@
       <c r="B71" s="42" t="s">
         <v>551</v>
       </c>
-      <c r="C71" s="69" t="s">
+      <c r="C71" s="71" t="s">
         <v>552</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="70"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="72"/>
       <c r="F71" s="68"/>
       <c r="G71" s="66"/>
       <c r="H71" s="66"/>
@@ -11275,11 +11290,11 @@
       <c r="B72" s="42" t="s">
         <v>554</v>
       </c>
-      <c r="C72" s="69" t="s">
+      <c r="C72" s="71" t="s">
         <v>555</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="70"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="72"/>
       <c r="F72" s="68"/>
       <c r="G72" s="66"/>
       <c r="H72" s="66"/>
@@ -11292,11 +11307,11 @@
       <c r="B73" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="71" t="s">
         <v>558</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="70"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="72"/>
       <c r="F73" s="68"/>
       <c r="G73" s="66"/>
       <c r="H73" s="66"/>
@@ -11309,11 +11324,11 @@
       <c r="B74" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="C74" s="69" t="s">
+      <c r="C74" s="71" t="s">
         <v>561</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="70"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="72"/>
       <c r="F74" s="68"/>
       <c r="G74" s="66"/>
       <c r="H74" s="66"/>
@@ -11326,11 +11341,11 @@
       <c r="B75" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="C75" s="69" t="s">
+      <c r="C75" s="71" t="s">
         <v>564</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="70"/>
+      <c r="D75" s="71"/>
+      <c r="E75" s="72"/>
       <c r="F75" s="68"/>
       <c r="G75" s="66"/>
       <c r="H75" s="66"/>
@@ -11343,11 +11358,11 @@
       <c r="B76" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="C76" s="69" t="s">
+      <c r="C76" s="71" t="s">
         <v>567</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="70"/>
+      <c r="D76" s="71"/>
+      <c r="E76" s="72"/>
       <c r="F76" s="68"/>
       <c r="G76" s="66"/>
       <c r="H76" s="66"/>
@@ -11360,11 +11375,11 @@
       <c r="B77" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="71" t="s">
         <v>570</v>
       </c>
-      <c r="D77" s="69"/>
-      <c r="E77" s="70"/>
+      <c r="D77" s="71"/>
+      <c r="E77" s="72"/>
       <c r="F77" s="68"/>
       <c r="G77" s="66"/>
       <c r="H77" s="66"/>
@@ -11377,11 +11392,11 @@
       <c r="B78" s="42" t="s">
         <v>572</v>
       </c>
-      <c r="C78" s="69" t="s">
+      <c r="C78" s="71" t="s">
         <v>573</v>
       </c>
-      <c r="D78" s="69"/>
-      <c r="E78" s="70"/>
+      <c r="D78" s="71"/>
+      <c r="E78" s="72"/>
       <c r="F78" s="68"/>
       <c r="G78" s="66"/>
       <c r="H78" s="66"/>
@@ -11394,11 +11409,11 @@
       <c r="B79" s="42" t="s">
         <v>575</v>
       </c>
-      <c r="C79" s="69" t="s">
+      <c r="C79" s="71" t="s">
         <v>576</v>
       </c>
-      <c r="D79" s="69"/>
-      <c r="E79" s="70"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="72"/>
       <c r="F79" s="68"/>
       <c r="G79" s="66"/>
       <c r="H79" s="66"/>
@@ -11411,11 +11426,11 @@
       <c r="B80" s="42" t="s">
         <v>578</v>
       </c>
-      <c r="C80" s="69" t="s">
+      <c r="C80" s="71" t="s">
         <v>579</v>
       </c>
-      <c r="D80" s="69"/>
-      <c r="E80" s="70"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="72"/>
       <c r="F80" s="68"/>
       <c r="G80" s="66"/>
       <c r="H80" s="66"/>
@@ -11428,11 +11443,11 @@
       <c r="B81" s="42" t="s">
         <v>581</v>
       </c>
-      <c r="C81" s="69" t="s">
+      <c r="C81" s="71" t="s">
         <v>582</v>
       </c>
-      <c r="D81" s="69"/>
-      <c r="E81" s="70"/>
+      <c r="D81" s="71"/>
+      <c r="E81" s="72"/>
       <c r="F81" s="68"/>
       <c r="G81" s="66"/>
       <c r="H81" s="66"/>
@@ -11445,11 +11460,11 @@
       <c r="B82" t="s">
         <v>2003</v>
       </c>
-      <c r="C82" s="73" t="s">
+      <c r="C82" s="69" t="s">
         <v>2000</v>
       </c>
-      <c r="D82" s="73"/>
-      <c r="E82" s="73"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="69"/>
       <c r="F82" s="68"/>
       <c r="G82" s="66"/>
       <c r="H82" s="66"/>
@@ -11462,11 +11477,11 @@
       <c r="B83" t="s">
         <v>2004</v>
       </c>
-      <c r="C83" s="73" t="s">
+      <c r="C83" s="69" t="s">
         <v>2002</v>
       </c>
-      <c r="D83" s="73"/>
-      <c r="E83" s="73"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="69"/>
       <c r="F83" s="68"/>
       <c r="G83" s="66"/>
       <c r="H83" s="66"/>
@@ -11474,6 +11489,103 @@
     </row>
   </sheetData>
   <mergeCells count="121">
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F70:I70"/>
+    <mergeCell ref="F71:I71"/>
+    <mergeCell ref="F72:I72"/>
+    <mergeCell ref="F73:I73"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="C82:E82"/>
     <mergeCell ref="C83:E83"/>
     <mergeCell ref="F82:I82"/>
@@ -11498,103 +11610,6 @@
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="F25:I25"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="F67:I67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="F69:I69"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F70:I70"/>
-    <mergeCell ref="F71:I71"/>
-    <mergeCell ref="F72:I72"/>
-    <mergeCell ref="F73:I73"/>
-    <mergeCell ref="F74:I74"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12755,7 +12770,7 @@
       <c r="I35" s="66"/>
       <c r="J35" s="66"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="16.2" x14ac:dyDescent="0.4">
       <c r="A36" s="49" t="s">
         <v>1777</v>
       </c>
@@ -12809,19 +12824,29 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="G34:J34"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="G36:J36"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
@@ -12835,29 +12860,19 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C34:D34"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:F21" xr:uid="{7FAB08B6-9907-44B4-A82A-4A3E200D36A8}">
@@ -12895,7 +12910,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BB695D-4821-4052-8E37-D71854C5F317}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5546875" customWidth="1"/>
@@ -13094,182 +13109,182 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>672</v>
+        <v>2137</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>673</v>
+        <v>2140</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="B12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E13" s="33"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>674</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="35" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="35" t="s">
         <v>675</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E15" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="67" t="s">
+      <c r="F15" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>1817</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>676</v>
-      </c>
-      <c r="C14" t="s">
-        <v>344</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1324</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>677</v>
-      </c>
-      <c r="F14" s="68"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>1824</v>
-      </c>
-      <c r="C15" t="s">
-        <v>344</v>
-      </c>
-      <c r="D15" t="s">
-        <v>714</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1825</v>
-      </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>1827</v>
       </c>
       <c r="C16" t="s">
         <v>344</v>
       </c>
       <c r="D16" t="s">
-        <v>714</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1826</v>
-      </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+        <v>1324</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>677</v>
+      </c>
+      <c r="F16" s="68"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>678</v>
-      </c>
       <c r="B17" t="s">
-        <v>679</v>
+        <v>1824</v>
       </c>
       <c r="C17" t="s">
         <v>344</v>
       </c>
       <c r="D17" t="s">
-        <v>1778</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>681</v>
-      </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
+        <v>714</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F17" s="46"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>682</v>
-      </c>
       <c r="B18" t="s">
-        <v>683</v>
+        <v>1827</v>
       </c>
       <c r="C18" t="s">
         <v>344</v>
       </c>
       <c r="D18" t="s">
-        <v>666</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>684</v>
-      </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
+        <v>714</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F18" s="46"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B19" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="C19" t="s">
         <v>344</v>
       </c>
       <c r="D19" t="s">
-        <v>687</v>
+        <v>1778</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="F19" s="68"/>
       <c r="G19" s="66"/>
@@ -13278,19 +13293,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B20" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="C20" t="s">
         <v>344</v>
       </c>
       <c r="D20" t="s">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="F20" s="68"/>
       <c r="G20" s="66"/>
@@ -13299,19 +13314,19 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="B21" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C21" t="s">
         <v>344</v>
       </c>
       <c r="D21" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="F21" s="68"/>
       <c r="G21" s="66"/>
@@ -13320,19 +13335,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B22" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C22" t="s">
         <v>344</v>
       </c>
       <c r="D22" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="F22" s="68"/>
       <c r="G22" s="66"/>
@@ -13341,19 +13356,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B23" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="C23" t="s">
         <v>344</v>
       </c>
       <c r="D23" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="F23" s="68"/>
       <c r="G23" s="66"/>
@@ -13362,19 +13377,19 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B24" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="C24" t="s">
         <v>344</v>
       </c>
       <c r="D24" t="s">
-        <v>701</v>
-      </c>
-      <c r="E24" t="s">
-        <v>705</v>
+        <v>694</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>698</v>
       </c>
       <c r="F24" s="68"/>
       <c r="G24" s="66"/>
@@ -13383,19 +13398,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="B25" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="C25" t="s">
         <v>344</v>
       </c>
       <c r="D25" t="s">
-        <v>680</v>
-      </c>
-      <c r="E25" t="s">
-        <v>708</v>
+        <v>701</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>702</v>
       </c>
       <c r="F25" s="68"/>
       <c r="G25" s="66"/>
@@ -13404,19 +13419,19 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B26" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C26" t="s">
         <v>344</v>
       </c>
       <c r="D26" t="s">
-        <v>1325</v>
+        <v>701</v>
       </c>
       <c r="E26" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="F26" s="68"/>
       <c r="G26" s="66"/>
@@ -13425,19 +13440,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B27" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C27" t="s">
         <v>344</v>
       </c>
       <c r="D27" t="s">
-        <v>714</v>
+        <v>680</v>
       </c>
       <c r="E27" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="F27" s="68"/>
       <c r="G27" s="66"/>
@@ -13446,19 +13461,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B28" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C28" t="s">
         <v>344</v>
       </c>
       <c r="D28" t="s">
-        <v>714</v>
+        <v>1325</v>
       </c>
       <c r="E28" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="F28" s="68"/>
       <c r="G28" s="66"/>
@@ -13467,10 +13482,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="B29" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C29" t="s">
         <v>344</v>
@@ -13479,7 +13494,7 @@
         <v>714</v>
       </c>
       <c r="E29" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F29" s="68"/>
       <c r="G29" s="66"/>
@@ -13488,10 +13503,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="B30" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C30" t="s">
         <v>344</v>
@@ -13500,7 +13515,7 @@
         <v>714</v>
       </c>
       <c r="E30" t="s">
-        <v>1779</v>
+        <v>718</v>
       </c>
       <c r="F30" s="68"/>
       <c r="G30" s="66"/>
@@ -13509,10 +13524,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B31" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C31" t="s">
         <v>344</v>
@@ -13521,7 +13536,7 @@
         <v>714</v>
       </c>
       <c r="E31" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="F31" s="68"/>
       <c r="G31" s="66"/>
@@ -13529,8 +13544,11 @@
       <c r="I31" s="66"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>722</v>
+      </c>
       <c r="B32" t="s">
-        <v>1790</v>
+        <v>723</v>
       </c>
       <c r="C32" t="s">
         <v>344</v>
@@ -13539,19 +13557,19 @@
         <v>714</v>
       </c>
       <c r="E32" t="s">
-        <v>1789</v>
-      </c>
-      <c r="F32" s="46"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
+        <v>1779</v>
+      </c>
+      <c r="F32" s="68"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B33" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C33" t="s">
         <v>344</v>
@@ -13560,7 +13578,7 @@
         <v>714</v>
       </c>
       <c r="E33" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F33" s="68"/>
       <c r="G33" s="66"/>
@@ -13569,7 +13587,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="C34" t="s">
         <v>344</v>
@@ -13578,28 +13596,28 @@
         <v>714</v>
       </c>
       <c r="E34" t="s">
-        <v>1788</v>
-      </c>
-      <c r="F34" s="68"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="66"/>
+        <v>1789</v>
+      </c>
+      <c r="F34" s="46"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B35" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C35" t="s">
         <v>344</v>
       </c>
       <c r="D35" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="E35" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="F35" s="68"/>
       <c r="G35" s="66"/>
@@ -13607,20 +13625,17 @@
       <c r="I35" s="66"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>733</v>
-      </c>
       <c r="B36" t="s">
-        <v>734</v>
+        <v>1787</v>
       </c>
       <c r="C36" t="s">
         <v>344</v>
       </c>
       <c r="D36" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="E36" t="s">
-        <v>735</v>
+        <v>1788</v>
       </c>
       <c r="F36" s="68"/>
       <c r="G36" s="66"/>
@@ -13629,19 +13644,19 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="B37" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C37" t="s">
         <v>344</v>
       </c>
       <c r="D37" t="s">
-        <v>1324</v>
+        <v>694</v>
       </c>
       <c r="E37" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F37" s="68"/>
       <c r="G37" s="66"/>
@@ -13650,10 +13665,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="B38" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C38" t="s">
         <v>344</v>
@@ -13662,7 +13677,7 @@
         <v>694</v>
       </c>
       <c r="E38" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="F38" s="68"/>
       <c r="G38" s="66"/>
@@ -13671,19 +13686,19 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B39" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C39" t="s">
         <v>344</v>
       </c>
       <c r="D39" t="s">
-        <v>744</v>
+        <v>1324</v>
       </c>
       <c r="E39" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="F39" s="68"/>
       <c r="G39" s="66"/>
@@ -13692,19 +13707,19 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B40" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="C40" t="s">
         <v>344</v>
       </c>
       <c r="D40" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="E40" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="F40" s="68"/>
       <c r="G40" s="66"/>
@@ -13713,49 +13728,52 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="B41" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="C41" t="s">
         <v>344</v>
       </c>
       <c r="D41" t="s">
-        <v>714</v>
+        <v>744</v>
       </c>
       <c r="E41" t="s">
-        <v>763</v>
-      </c>
-      <c r="F41" s="46"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
+        <v>745</v>
+      </c>
+      <c r="F41" s="68"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1784</v>
+        <v>746</v>
       </c>
       <c r="B42" t="s">
-        <v>1785</v>
+        <v>747</v>
       </c>
       <c r="C42" t="s">
         <v>344</v>
       </c>
       <c r="D42" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="E42" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F42" s="46"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
+        <v>748</v>
+      </c>
+      <c r="F42" s="68"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>761</v>
+      </c>
       <c r="B43" t="s">
-        <v>1818</v>
+        <v>762</v>
       </c>
       <c r="C43" t="s">
         <v>344</v>
@@ -13764,7 +13782,7 @@
         <v>714</v>
       </c>
       <c r="E43" t="s">
-        <v>1819</v>
+        <v>763</v>
       </c>
       <c r="F43" s="46"/>
       <c r="G43" s="10"/>
@@ -13772,17 +13790,20 @@
       <c r="I43" s="10"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>1784</v>
+      </c>
       <c r="B44" t="s">
-        <v>1820</v>
+        <v>1785</v>
       </c>
       <c r="C44" t="s">
         <v>344</v>
       </c>
       <c r="D44" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="E44" t="s">
-        <v>1821</v>
+        <v>1786</v>
       </c>
       <c r="F44" s="46"/>
       <c r="G44" s="10"/>
@@ -13791,7 +13812,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
       <c r="C45" t="s">
         <v>344</v>
@@ -13800,7 +13821,7 @@
         <v>714</v>
       </c>
       <c r="E45" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="F45" s="46"/>
       <c r="G45" s="10"/>
@@ -13808,41 +13829,35 @@
       <c r="I45" s="10"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>749</v>
-      </c>
       <c r="B46" t="s">
-        <v>750</v>
+        <v>1820</v>
       </c>
       <c r="C46" t="s">
         <v>344</v>
       </c>
       <c r="D46" t="s">
-        <v>1323</v>
+        <v>714</v>
       </c>
       <c r="E46" t="s">
-        <v>751</v>
-      </c>
-      <c r="F46" s="68"/>
-      <c r="G46" s="66"/>
-      <c r="H46" s="66"/>
-      <c r="I46" s="66"/>
+        <v>1821</v>
+      </c>
+      <c r="F46" s="46"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>1793</v>
-      </c>
       <c r="B47" t="s">
-        <v>1792</v>
+        <v>1822</v>
       </c>
       <c r="C47" t="s">
         <v>344</v>
       </c>
       <c r="D47" t="s">
-        <v>1323</v>
+        <v>714</v>
       </c>
       <c r="E47" t="s">
-        <v>1791</v>
+        <v>1823</v>
       </c>
       <c r="F47" s="46"/>
       <c r="G47" s="10"/>
@@ -13851,19 +13866,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B48" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C48" t="s">
         <v>344</v>
       </c>
       <c r="D48" t="s">
-        <v>666</v>
+        <v>1323</v>
       </c>
       <c r="E48" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F48" s="68"/>
       <c r="G48" s="66"/>
@@ -13872,31 +13887,31 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>755</v>
+        <v>1793</v>
       </c>
       <c r="B49" t="s">
-        <v>756</v>
+        <v>1792</v>
       </c>
       <c r="C49" t="s">
         <v>344</v>
       </c>
       <c r="D49" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="E49" t="s">
-        <v>757</v>
-      </c>
-      <c r="F49" s="68"/>
-      <c r="G49" s="66"/>
-      <c r="H49" s="66"/>
-      <c r="I49" s="66"/>
+        <v>1791</v>
+      </c>
+      <c r="F49" s="46"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="B50" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="C50" t="s">
         <v>344</v>
@@ -13905,7 +13920,7 @@
         <v>666</v>
       </c>
       <c r="E50" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="F50" s="68"/>
       <c r="G50" s="66"/>
@@ -13914,154 +13929,158 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1849</v>
+        <v>755</v>
       </c>
       <c r="B51" t="s">
-        <v>1848</v>
+        <v>756</v>
       </c>
       <c r="C51" t="s">
         <v>344</v>
       </c>
       <c r="D51" t="s">
-        <v>1852</v>
+        <v>1326</v>
       </c>
       <c r="E51" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F51" s="46"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
+        <v>757</v>
+      </c>
+      <c r="F51" s="68"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1850</v>
+        <v>758</v>
       </c>
       <c r="B52" t="s">
-        <v>1853</v>
+        <v>759</v>
       </c>
       <c r="C52" t="s">
         <v>344</v>
       </c>
       <c r="D52" t="s">
-        <v>1852</v>
+        <v>666</v>
       </c>
       <c r="E52" t="s">
-        <v>1854</v>
-      </c>
-      <c r="F52" s="46"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
+        <v>760</v>
+      </c>
+      <c r="F52" s="68"/>
+      <c r="G52" s="66"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="66"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1858</v>
+        <v>1849</v>
       </c>
       <c r="B53" t="s">
-        <v>1855</v>
+        <v>1848</v>
       </c>
       <c r="C53" t="s">
         <v>344</v>
       </c>
       <c r="D53" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
       <c r="E53" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="F53" s="46"/>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
       <c r="I53" s="10"/>
     </row>
-    <row r="54" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C54" t="s">
+        <v>344</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F54" s="46"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C55" t="s">
+        <v>344</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F55" s="46"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+    </row>
+    <row r="56" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
         <v>764</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="35" t="s">
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="35" t="s">
         <v>765</v>
       </c>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-      <c r="I54" s="16"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B57" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C55" s="67" t="s">
+      <c r="C57" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="D55" s="67"/>
-      <c r="E55" s="32" t="s">
+      <c r="D57" s="67"/>
+      <c r="E57" s="32" t="s">
         <v>766</v>
       </c>
-      <c r="F55" s="67" t="s">
+      <c r="F57" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="67"/>
-    </row>
-    <row r="56" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>767</v>
-      </c>
-      <c r="B56" t="s">
-        <v>768</v>
-      </c>
-      <c r="C56" s="65" t="s">
-        <v>148</v>
-      </c>
-      <c r="D56" s="65"/>
-      <c r="E56" s="5" t="s">
-        <v>769</v>
-      </c>
-      <c r="F56" s="68"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
-    </row>
-    <row r="57" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>770</v>
-      </c>
-      <c r="B57" t="s">
-        <v>771</v>
-      </c>
-      <c r="C57" s="65" t="s">
-        <v>148</v>
-      </c>
-      <c r="D57" s="65"/>
-      <c r="E57" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="F57" s="68"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="67"/>
     </row>
     <row r="58" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>768</v>
       </c>
       <c r="C58" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="5" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="F58" s="68"/>
       <c r="G58" s="66"/>
@@ -14070,17 +14089,17 @@
     </row>
     <row r="59" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B59" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C59" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="5" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F59" s="68"/>
       <c r="G59" s="66"/>
@@ -14089,17 +14108,17 @@
     </row>
     <row r="60" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B60" t="s">
-        <v>779</v>
+        <v>269</v>
       </c>
       <c r="C60" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="5" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="F60" s="68"/>
       <c r="G60" s="66"/>
@@ -14108,17 +14127,17 @@
     </row>
     <row r="61" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B61" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="C61" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="5" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="F61" s="68"/>
       <c r="G61" s="66"/>
@@ -14127,17 +14146,17 @@
     </row>
     <row r="62" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B62" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="C62" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="5" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="F62" s="68"/>
       <c r="G62" s="66"/>
@@ -14146,17 +14165,17 @@
     </row>
     <row r="63" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="B63" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="C63" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="5" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="F63" s="68"/>
       <c r="G63" s="66"/>
@@ -14165,35 +14184,96 @@
     </row>
     <row r="64" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B64" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C64" s="65" t="s">
         <v>148</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="5" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="F64" s="68"/>
       <c r="G64" s="66"/>
       <c r="H64" s="66"/>
       <c r="I64" s="66"/>
     </row>
+    <row r="65" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>787</v>
+      </c>
+      <c r="B65" t="s">
+        <v>788</v>
+      </c>
+      <c r="C65" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" s="65"/>
+      <c r="E65" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="F65" s="68"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="66"/>
+      <c r="I65" s="66"/>
+    </row>
+    <row r="66" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>790</v>
+      </c>
+      <c r="B66" t="s">
+        <v>791</v>
+      </c>
+      <c r="C66" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D66" s="65"/>
+      <c r="E66" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="F66" s="68"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="66"/>
+      <c r="I66" s="66"/>
+    </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="F24:I24"/>
     <mergeCell ref="F25:I25"/>
     <mergeCell ref="F26:I26"/>
@@ -14201,43 +14281,20 @@
     <mergeCell ref="F28:I28"/>
     <mergeCell ref="F29:I29"/>
     <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E17:E23 E14" xr:uid="{7F27821C-1386-4223-AB50-4D30E422ACE2}">
-      <formula1>$L$14:$L$23</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E19:E25 E16" xr:uid="{7F27821C-1386-4223-AB50-4D30E422ACE2}">
+      <formula1>$L$16:$L$25</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14249,19 +14306,19 @@
           <x14:formula1>
             <xm:f>'Dataset Intro'!$Q$2:$Q$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F3:F5 F7:F10</xm:sqref>
+          <xm:sqref>F3:F5 F7:F12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A4148597-CF07-4DDD-8D04-F1672B50AA0E}">
           <x14:formula1>
             <xm:f>'Dataset Intro'!$Q$19:$Q$25</xm:f>
           </x14:formula1>
-          <xm:sqref>H3:H5 H7:H10</xm:sqref>
+          <xm:sqref>H3:H5 H7:H12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{090570FF-7B7D-4904-B66D-6784E72F104C}">
           <x14:formula1>
             <xm:f>'Dataset Intro'!$Q$13:$Q$15</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G5 G7:G10</xm:sqref>
+          <xm:sqref>G3:G5 G7:G12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -18796,15 +18853,96 @@
   </sheetData>
   <dataConsolidate link="1"/>
   <mergeCells count="111">
-    <mergeCell ref="H150:K150"/>
-    <mergeCell ref="H151:K151"/>
-    <mergeCell ref="H152:K152"/>
-    <mergeCell ref="H144:K144"/>
-    <mergeCell ref="H145:K145"/>
-    <mergeCell ref="H146:K146"/>
-    <mergeCell ref="H147:K147"/>
-    <mergeCell ref="H148:K148"/>
-    <mergeCell ref="H149:K149"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="H44:K44"/>
+    <mergeCell ref="H62:K62"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="H64:K64"/>
+    <mergeCell ref="H65:K65"/>
+    <mergeCell ref="H66:K66"/>
+    <mergeCell ref="H68:K68"/>
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="H60:K60"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="H77:K77"/>
+    <mergeCell ref="H78:K78"/>
+    <mergeCell ref="H79:K79"/>
+    <mergeCell ref="H80:K80"/>
+    <mergeCell ref="H81:K81"/>
+    <mergeCell ref="H82:K82"/>
+    <mergeCell ref="H69:K69"/>
+    <mergeCell ref="H70:K70"/>
+    <mergeCell ref="H72:K72"/>
+    <mergeCell ref="H73:K73"/>
+    <mergeCell ref="H75:K75"/>
+    <mergeCell ref="H76:K76"/>
+    <mergeCell ref="H89:K89"/>
+    <mergeCell ref="H90:K90"/>
+    <mergeCell ref="H91:K91"/>
+    <mergeCell ref="H92:K92"/>
+    <mergeCell ref="H93:K93"/>
+    <mergeCell ref="H94:K94"/>
+    <mergeCell ref="H83:K83"/>
+    <mergeCell ref="H84:K84"/>
+    <mergeCell ref="H85:K85"/>
+    <mergeCell ref="H86:K86"/>
+    <mergeCell ref="H87:K87"/>
+    <mergeCell ref="H88:K88"/>
+    <mergeCell ref="H101:K101"/>
+    <mergeCell ref="H102:K102"/>
+    <mergeCell ref="H103:K103"/>
+    <mergeCell ref="H104:K104"/>
+    <mergeCell ref="H105:K105"/>
+    <mergeCell ref="H107:K107"/>
+    <mergeCell ref="H95:K95"/>
+    <mergeCell ref="H96:K96"/>
+    <mergeCell ref="H97:K97"/>
+    <mergeCell ref="H98:K98"/>
+    <mergeCell ref="H99:K99"/>
+    <mergeCell ref="H100:K100"/>
+    <mergeCell ref="H114:K114"/>
+    <mergeCell ref="H115:K115"/>
+    <mergeCell ref="H116:K116"/>
+    <mergeCell ref="H117:K117"/>
+    <mergeCell ref="H118:K118"/>
+    <mergeCell ref="H119:K119"/>
+    <mergeCell ref="H108:K108"/>
+    <mergeCell ref="H109:K109"/>
+    <mergeCell ref="H110:K110"/>
+    <mergeCell ref="H111:K111"/>
+    <mergeCell ref="H112:K112"/>
+    <mergeCell ref="H113:K113"/>
+    <mergeCell ref="H126:K126"/>
+    <mergeCell ref="H127:K127"/>
+    <mergeCell ref="H128:K128"/>
+    <mergeCell ref="H129:K129"/>
+    <mergeCell ref="H130:K130"/>
+    <mergeCell ref="H131:K131"/>
+    <mergeCell ref="H120:K120"/>
+    <mergeCell ref="H121:K121"/>
+    <mergeCell ref="H122:K122"/>
+    <mergeCell ref="H123:K123"/>
+    <mergeCell ref="H124:K124"/>
+    <mergeCell ref="H125:K125"/>
     <mergeCell ref="H138:K138"/>
     <mergeCell ref="H139:K139"/>
     <mergeCell ref="H140:K140"/>
@@ -18817,96 +18955,15 @@
     <mergeCell ref="H135:K135"/>
     <mergeCell ref="H136:K136"/>
     <mergeCell ref="H137:K137"/>
-    <mergeCell ref="H126:K126"/>
-    <mergeCell ref="H127:K127"/>
-    <mergeCell ref="H128:K128"/>
-    <mergeCell ref="H129:K129"/>
-    <mergeCell ref="H130:K130"/>
-    <mergeCell ref="H131:K131"/>
-    <mergeCell ref="H120:K120"/>
-    <mergeCell ref="H121:K121"/>
-    <mergeCell ref="H122:K122"/>
-    <mergeCell ref="H123:K123"/>
-    <mergeCell ref="H124:K124"/>
-    <mergeCell ref="H125:K125"/>
-    <mergeCell ref="H114:K114"/>
-    <mergeCell ref="H115:K115"/>
-    <mergeCell ref="H116:K116"/>
-    <mergeCell ref="H117:K117"/>
-    <mergeCell ref="H118:K118"/>
-    <mergeCell ref="H119:K119"/>
-    <mergeCell ref="H108:K108"/>
-    <mergeCell ref="H109:K109"/>
-    <mergeCell ref="H110:K110"/>
-    <mergeCell ref="H111:K111"/>
-    <mergeCell ref="H112:K112"/>
-    <mergeCell ref="H113:K113"/>
-    <mergeCell ref="H101:K101"/>
-    <mergeCell ref="H102:K102"/>
-    <mergeCell ref="H103:K103"/>
-    <mergeCell ref="H104:K104"/>
-    <mergeCell ref="H105:K105"/>
-    <mergeCell ref="H107:K107"/>
-    <mergeCell ref="H95:K95"/>
-    <mergeCell ref="H96:K96"/>
-    <mergeCell ref="H97:K97"/>
-    <mergeCell ref="H98:K98"/>
-    <mergeCell ref="H99:K99"/>
-    <mergeCell ref="H100:K100"/>
-    <mergeCell ref="H89:K89"/>
-    <mergeCell ref="H90:K90"/>
-    <mergeCell ref="H91:K91"/>
-    <mergeCell ref="H92:K92"/>
-    <mergeCell ref="H93:K93"/>
-    <mergeCell ref="H94:K94"/>
-    <mergeCell ref="H83:K83"/>
-    <mergeCell ref="H84:K84"/>
-    <mergeCell ref="H85:K85"/>
-    <mergeCell ref="H86:K86"/>
-    <mergeCell ref="H87:K87"/>
-    <mergeCell ref="H88:K88"/>
-    <mergeCell ref="H77:K77"/>
-    <mergeCell ref="H78:K78"/>
-    <mergeCell ref="H79:K79"/>
-    <mergeCell ref="H80:K80"/>
-    <mergeCell ref="H81:K81"/>
-    <mergeCell ref="H82:K82"/>
-    <mergeCell ref="H69:K69"/>
-    <mergeCell ref="H70:K70"/>
-    <mergeCell ref="H72:K72"/>
-    <mergeCell ref="H73:K73"/>
-    <mergeCell ref="H75:K75"/>
-    <mergeCell ref="H76:K76"/>
-    <mergeCell ref="H62:K62"/>
-    <mergeCell ref="H63:K63"/>
-    <mergeCell ref="H64:K64"/>
-    <mergeCell ref="H65:K65"/>
-    <mergeCell ref="H66:K66"/>
-    <mergeCell ref="H68:K68"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="H58:K58"/>
-    <mergeCell ref="H60:K60"/>
-    <mergeCell ref="H61:K61"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H44:K44"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H150:K150"/>
+    <mergeCell ref="H151:K151"/>
+    <mergeCell ref="H152:K152"/>
+    <mergeCell ref="H144:K144"/>
+    <mergeCell ref="H145:K145"/>
+    <mergeCell ref="H146:K146"/>
+    <mergeCell ref="H147:K147"/>
+    <mergeCell ref="H148:K148"/>
+    <mergeCell ref="H149:K149"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21485,6 +21542,21 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="F113:I113"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C125:D125"/>
     <mergeCell ref="F109:I109"/>
     <mergeCell ref="F110:I110"/>
     <mergeCell ref="F111:I111"/>
@@ -21493,21 +21565,6 @@
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="C111:D111"/>
     <mergeCell ref="C112:D112"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="F113:I113"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -22323,6 +22380,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="H54:K54"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:K56"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="H53:K53"/>
     <mergeCell ref="H44:K44"/>
     <mergeCell ref="H13:K13"/>
     <mergeCell ref="H14:K14"/>
@@ -22335,15 +22401,6 @@
     <mergeCell ref="H41:K41"/>
     <mergeCell ref="H42:K42"/>
     <mergeCell ref="H43:K43"/>
-    <mergeCell ref="H54:K54"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="H56:K56"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="H51:K51"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="H53:K53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -22692,14 +22749,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="H22:K22"/>
     <mergeCell ref="H33:K33"/>
     <mergeCell ref="H34:K34"/>
     <mergeCell ref="H35:K35"/>
@@ -22709,6 +22758,14 @@
     <mergeCell ref="H30:K30"/>
     <mergeCell ref="H31:K31"/>
     <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="H22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -23058,6 +23115,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="H35:K35"/>
     <mergeCell ref="H30:K30"/>
     <mergeCell ref="H16:K16"/>
     <mergeCell ref="H17:K17"/>
@@ -23070,11 +23132,6 @@
     <mergeCell ref="H24:K24"/>
     <mergeCell ref="H25:K25"/>
     <mergeCell ref="H27:K27"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -24135,10 +24192,10 @@
       <c r="B44" s="48" t="s">
         <v>1162</v>
       </c>
-      <c r="C44" s="73" t="s">
+      <c r="C44" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D44" s="73"/>
+      <c r="D44" s="69"/>
       <c r="E44" s="5" t="s">
         <v>1163</v>
       </c>
@@ -24152,10 +24209,10 @@
       <c r="B45" s="48" t="s">
         <v>1164</v>
       </c>
-      <c r="C45" s="73" t="s">
+      <c r="C45" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D45" s="73"/>
+      <c r="D45" s="69"/>
       <c r="E45" s="5" t="s">
         <v>1165</v>
       </c>
@@ -24169,10 +24226,10 @@
       <c r="B46" s="48" t="s">
         <v>1166</v>
       </c>
-      <c r="C46" s="73" t="s">
+      <c r="C46" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D46" s="73"/>
+      <c r="D46" s="69"/>
       <c r="E46" s="5" t="s">
         <v>1167</v>
       </c>
@@ -24186,10 +24243,10 @@
       <c r="B47" s="48" t="s">
         <v>1168</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="C47" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D47" s="73"/>
+      <c r="D47" s="69"/>
       <c r="E47" s="5" t="s">
         <v>1169</v>
       </c>
@@ -24203,10 +24260,10 @@
       <c r="B48" s="48" t="s">
         <v>1170</v>
       </c>
-      <c r="C48" s="73" t="s">
+      <c r="C48" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D48" s="73"/>
+      <c r="D48" s="69"/>
       <c r="E48" s="5" t="s">
         <v>1171</v>
       </c>
@@ -24220,10 +24277,10 @@
       <c r="B49" s="48" t="s">
         <v>1172</v>
       </c>
-      <c r="C49" s="73" t="s">
+      <c r="C49" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D49" s="73"/>
+      <c r="D49" s="69"/>
       <c r="E49" s="5" t="s">
         <v>1173</v>
       </c>
@@ -24237,10 +24294,10 @@
       <c r="B50" s="48" t="s">
         <v>1174</v>
       </c>
-      <c r="C50" s="73" t="s">
+      <c r="C50" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D50" s="73"/>
+      <c r="D50" s="69"/>
       <c r="E50" s="5" t="s">
         <v>1175</v>
       </c>
@@ -24254,10 +24311,10 @@
       <c r="B51" s="48" t="s">
         <v>1176</v>
       </c>
-      <c r="C51" s="73" t="s">
+      <c r="C51" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D51" s="73"/>
+      <c r="D51" s="69"/>
       <c r="E51" s="5" t="s">
         <v>1177</v>
       </c>
@@ -24271,10 +24328,10 @@
       <c r="B52" s="48" t="s">
         <v>1178</v>
       </c>
-      <c r="C52" s="73" t="s">
+      <c r="C52" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D52" s="73"/>
+      <c r="D52" s="69"/>
       <c r="E52" s="5" t="s">
         <v>1179</v>
       </c>
@@ -24288,10 +24345,10 @@
       <c r="B53" s="48" t="s">
         <v>1180</v>
       </c>
-      <c r="C53" s="73" t="s">
+      <c r="C53" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D53" s="73"/>
+      <c r="D53" s="69"/>
       <c r="E53" s="5" t="s">
         <v>1181</v>
       </c>
@@ -24305,10 +24362,10 @@
       <c r="B54" s="48" t="s">
         <v>1182</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="C54" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D54" s="73"/>
+      <c r="D54" s="69"/>
       <c r="E54" s="5" t="s">
         <v>1183</v>
       </c>
@@ -24322,10 +24379,10 @@
       <c r="B55" s="48" t="s">
         <v>1184</v>
       </c>
-      <c r="C55" s="73" t="s">
+      <c r="C55" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D55" s="73"/>
+      <c r="D55" s="69"/>
       <c r="E55" s="5" t="s">
         <v>1185</v>
       </c>
@@ -24339,10 +24396,10 @@
       <c r="B56" s="48" t="s">
         <v>1186</v>
       </c>
-      <c r="C56" s="73" t="s">
+      <c r="C56" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D56" s="73"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="5" t="s">
         <v>1187</v>
       </c>
@@ -24356,10 +24413,10 @@
       <c r="B57" s="48" t="s">
         <v>1188</v>
       </c>
-      <c r="C57" s="73" t="s">
+      <c r="C57" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D57" s="73"/>
+      <c r="D57" s="69"/>
       <c r="E57" s="5" t="s">
         <v>1189</v>
       </c>
@@ -24373,10 +24430,10 @@
       <c r="B58" s="48" t="s">
         <v>1190</v>
       </c>
-      <c r="C58" s="73" t="s">
+      <c r="C58" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D58" s="73"/>
+      <c r="D58" s="69"/>
       <c r="E58" s="5" t="s">
         <v>1191</v>
       </c>
@@ -24390,10 +24447,10 @@
       <c r="B59" s="48" t="s">
         <v>1192</v>
       </c>
-      <c r="C59" s="73" t="s">
+      <c r="C59" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D59" s="73"/>
+      <c r="D59" s="69"/>
       <c r="E59" s="5" t="s">
         <v>1193</v>
       </c>
@@ -24407,10 +24464,10 @@
       <c r="B60" s="48" t="s">
         <v>1194</v>
       </c>
-      <c r="C60" s="73" t="s">
+      <c r="C60" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D60" s="73"/>
+      <c r="D60" s="69"/>
       <c r="E60" s="5" t="s">
         <v>1195</v>
       </c>
@@ -24424,10 +24481,10 @@
       <c r="B61" s="48" t="s">
         <v>1196</v>
       </c>
-      <c r="C61" s="73" t="s">
+      <c r="C61" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D61" s="73"/>
+      <c r="D61" s="69"/>
       <c r="E61" s="5" t="s">
         <v>1197</v>
       </c>
@@ -24441,10 +24498,10 @@
       <c r="B62" s="48" t="s">
         <v>1198</v>
       </c>
-      <c r="C62" s="73" t="s">
+      <c r="C62" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D62" s="73"/>
+      <c r="D62" s="69"/>
       <c r="E62" s="5" t="s">
         <v>1199</v>
       </c>
@@ -24458,10 +24515,10 @@
       <c r="B63" s="48" t="s">
         <v>1200</v>
       </c>
-      <c r="C63" s="73" t="s">
+      <c r="C63" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D63" s="73"/>
+      <c r="D63" s="69"/>
       <c r="E63" s="5" t="s">
         <v>1201</v>
       </c>
@@ -24475,10 +24532,10 @@
       <c r="B64" s="48" t="s">
         <v>1202</v>
       </c>
-      <c r="C64" s="73" t="s">
+      <c r="C64" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D64" s="73"/>
+      <c r="D64" s="69"/>
       <c r="E64" s="5" t="s">
         <v>1203</v>
       </c>
@@ -24492,10 +24549,10 @@
       <c r="B65" s="48" t="s">
         <v>1204</v>
       </c>
-      <c r="C65" s="73" t="s">
+      <c r="C65" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D65" s="73"/>
+      <c r="D65" s="69"/>
       <c r="E65" s="5" t="s">
         <v>1205</v>
       </c>
@@ -24509,10 +24566,10 @@
       <c r="B66" s="48" t="s">
         <v>1206</v>
       </c>
-      <c r="C66" s="73" t="s">
+      <c r="C66" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D66" s="73"/>
+      <c r="D66" s="69"/>
       <c r="E66" s="5" t="s">
         <v>1207</v>
       </c>
@@ -24526,10 +24583,10 @@
       <c r="B67" s="48" t="s">
         <v>1208</v>
       </c>
-      <c r="C67" s="73" t="s">
+      <c r="C67" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D67" s="73"/>
+      <c r="D67" s="69"/>
       <c r="E67" s="5" t="s">
         <v>1209</v>
       </c>
@@ -24543,10 +24600,10 @@
       <c r="B68" s="48" t="s">
         <v>1210</v>
       </c>
-      <c r="C68" s="73" t="s">
+      <c r="C68" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D68" s="73"/>
+      <c r="D68" s="69"/>
       <c r="E68" s="5" t="s">
         <v>1211</v>
       </c>
@@ -24560,10 +24617,10 @@
       <c r="B69" s="48" t="s">
         <v>1212</v>
       </c>
-      <c r="C69" s="73" t="s">
+      <c r="C69" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D69" s="73"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="5" t="s">
         <v>1213</v>
       </c>
@@ -24577,10 +24634,10 @@
       <c r="B70" s="48" t="s">
         <v>1214</v>
       </c>
-      <c r="C70" s="73" t="s">
+      <c r="C70" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D70" s="73"/>
+      <c r="D70" s="69"/>
       <c r="E70" s="5" t="s">
         <v>1215</v>
       </c>
@@ -24594,10 +24651,10 @@
       <c r="B71" s="48" t="s">
         <v>1216</v>
       </c>
-      <c r="C71" s="73" t="s">
+      <c r="C71" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D71" s="73"/>
+      <c r="D71" s="69"/>
       <c r="E71" s="5" t="s">
         <v>1217</v>
       </c>
@@ -24611,10 +24668,10 @@
       <c r="B72" s="48" t="s">
         <v>1218</v>
       </c>
-      <c r="C72" s="73" t="s">
+      <c r="C72" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D72" s="73"/>
+      <c r="D72" s="69"/>
       <c r="E72" s="5" t="s">
         <v>1219</v>
       </c>
@@ -24628,10 +24685,10 @@
       <c r="B73" s="48" t="s">
         <v>1220</v>
       </c>
-      <c r="C73" s="73" t="s">
+      <c r="C73" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D73" s="73"/>
+      <c r="D73" s="69"/>
       <c r="E73" s="5" t="s">
         <v>1221</v>
       </c>
@@ -24645,10 +24702,10 @@
       <c r="B74" s="48" t="s">
         <v>1222</v>
       </c>
-      <c r="C74" s="73" t="s">
+      <c r="C74" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D74" s="73"/>
+      <c r="D74" s="69"/>
       <c r="E74" s="5" t="s">
         <v>1223</v>
       </c>
@@ -24662,10 +24719,10 @@
       <c r="B75" s="48" t="s">
         <v>1224</v>
       </c>
-      <c r="C75" s="73" t="s">
+      <c r="C75" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D75" s="73"/>
+      <c r="D75" s="69"/>
       <c r="E75" s="5" t="s">
         <v>1225</v>
       </c>
@@ -24679,10 +24736,10 @@
       <c r="B76" s="48" t="s">
         <v>1226</v>
       </c>
-      <c r="C76" s="73" t="s">
+      <c r="C76" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D76" s="73"/>
+      <c r="D76" s="69"/>
       <c r="E76" s="5" t="s">
         <v>1227</v>
       </c>
@@ -24696,10 +24753,10 @@
       <c r="B77" s="48" t="s">
         <v>1228</v>
       </c>
-      <c r="C77" s="73" t="s">
+      <c r="C77" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D77" s="73"/>
+      <c r="D77" s="69"/>
       <c r="E77" s="5" t="s">
         <v>1229</v>
       </c>
@@ -24713,10 +24770,10 @@
       <c r="B78" s="48" t="s">
         <v>1230</v>
       </c>
-      <c r="C78" s="73" t="s">
+      <c r="C78" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D78" s="73"/>
+      <c r="D78" s="69"/>
       <c r="E78" s="5" t="s">
         <v>1231</v>
       </c>
@@ -24730,10 +24787,10 @@
       <c r="B79" s="48" t="s">
         <v>1232</v>
       </c>
-      <c r="C79" s="73" t="s">
+      <c r="C79" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D79" s="73"/>
+      <c r="D79" s="69"/>
       <c r="E79" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24747,10 +24804,10 @@
       <c r="B80" s="48" t="s">
         <v>1234</v>
       </c>
-      <c r="C80" s="73" t="s">
+      <c r="C80" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D80" s="73"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24764,10 +24821,10 @@
       <c r="B81" s="48" t="s">
         <v>1236</v>
       </c>
-      <c r="C81" s="73" t="s">
+      <c r="C81" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D81" s="73"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24781,10 +24838,10 @@
       <c r="B82" s="48" t="s">
         <v>1238</v>
       </c>
-      <c r="C82" s="73" t="s">
+      <c r="C82" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D82" s="73"/>
+      <c r="D82" s="69"/>
       <c r="E82" s="5" t="s">
         <v>1239</v>
       </c>
@@ -24798,10 +24855,10 @@
       <c r="B83" s="48" t="s">
         <v>1267</v>
       </c>
-      <c r="C83" s="73" t="s">
+      <c r="C83" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D83" s="73"/>
+      <c r="D83" s="69"/>
       <c r="E83" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24815,10 +24872,10 @@
       <c r="B84" s="48" t="s">
         <v>1268</v>
       </c>
-      <c r="C84" s="73" t="s">
+      <c r="C84" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D84" s="73"/>
+      <c r="D84" s="69"/>
       <c r="E84" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24832,10 +24889,10 @@
       <c r="B85" s="48" t="s">
         <v>1269</v>
       </c>
-      <c r="C85" s="73" t="s">
+      <c r="C85" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D85" s="73"/>
+      <c r="D85" s="69"/>
       <c r="E85" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24849,10 +24906,10 @@
       <c r="B86" s="48" t="s">
         <v>1270</v>
       </c>
-      <c r="C86" s="73" t="s">
+      <c r="C86" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D86" s="73"/>
+      <c r="D86" s="69"/>
       <c r="E86" s="5" t="s">
         <v>1240</v>
       </c>
@@ -24866,10 +24923,10 @@
       <c r="B87" s="48" t="s">
         <v>1241</v>
       </c>
-      <c r="C87" s="73" t="s">
+      <c r="C87" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D87" s="73"/>
+      <c r="D87" s="69"/>
       <c r="E87" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24883,10 +24940,10 @@
       <c r="B88" s="48" t="s">
         <v>1242</v>
       </c>
-      <c r="C88" s="73" t="s">
+      <c r="C88" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D88" s="73"/>
+      <c r="D88" s="69"/>
       <c r="E88" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24900,10 +24957,10 @@
       <c r="B89" s="48" t="s">
         <v>1243</v>
       </c>
-      <c r="C89" s="73" t="s">
+      <c r="C89" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D89" s="73"/>
+      <c r="D89" s="69"/>
       <c r="E89" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24917,10 +24974,10 @@
       <c r="B90" s="48" t="s">
         <v>1244</v>
       </c>
-      <c r="C90" s="73" t="s">
+      <c r="C90" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D90" s="73"/>
+      <c r="D90" s="69"/>
       <c r="E90" s="5" t="s">
         <v>1240</v>
       </c>
@@ -24934,10 +24991,10 @@
       <c r="B91" s="48" t="s">
         <v>1271</v>
       </c>
-      <c r="C91" s="73" t="s">
+      <c r="C91" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D91" s="73"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="5" t="s">
         <v>1233</v>
       </c>
@@ -24951,10 +25008,10 @@
       <c r="B92" s="48" t="s">
         <v>1272</v>
       </c>
-      <c r="C92" s="73" t="s">
+      <c r="C92" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D92" s="73"/>
+      <c r="D92" s="69"/>
       <c r="E92" s="5" t="s">
         <v>1235</v>
       </c>
@@ -24968,10 +25025,10 @@
       <c r="B93" s="48" t="s">
         <v>1273</v>
       </c>
-      <c r="C93" s="73" t="s">
+      <c r="C93" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D93" s="73"/>
+      <c r="D93" s="69"/>
       <c r="E93" s="5" t="s">
         <v>1237</v>
       </c>
@@ -24985,10 +25042,10 @@
       <c r="B94" s="48" t="s">
         <v>1274</v>
       </c>
-      <c r="C94" s="73" t="s">
+      <c r="C94" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D94" s="73"/>
+      <c r="D94" s="69"/>
       <c r="E94" s="5" t="s">
         <v>1240</v>
       </c>
@@ -25002,10 +25059,10 @@
       <c r="B95" s="48" t="s">
         <v>1275</v>
       </c>
-      <c r="C95" s="73" t="s">
+      <c r="C95" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D95" s="73"/>
+      <c r="D95" s="69"/>
       <c r="E95" s="5" t="s">
         <v>1245</v>
       </c>
@@ -25019,10 +25076,10 @@
       <c r="B96" s="48" t="s">
         <v>1246</v>
       </c>
-      <c r="C96" s="73" t="s">
+      <c r="C96" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D96" s="73"/>
+      <c r="D96" s="69"/>
       <c r="E96" s="5" t="s">
         <v>1247</v>
       </c>
@@ -25036,10 +25093,10 @@
       <c r="B97" s="48" t="s">
         <v>1248</v>
       </c>
-      <c r="C97" s="73" t="s">
+      <c r="C97" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D97" s="73"/>
+      <c r="D97" s="69"/>
       <c r="E97" s="5" t="s">
         <v>1249</v>
       </c>
@@ -25053,10 +25110,10 @@
       <c r="B98" s="48" t="s">
         <v>1250</v>
       </c>
-      <c r="C98" s="73" t="s">
+      <c r="C98" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D98" s="73"/>
+      <c r="D98" s="69"/>
       <c r="E98" s="5" t="s">
         <v>1251</v>
       </c>
@@ -25070,10 +25127,10 @@
       <c r="B99" s="48" t="s">
         <v>1252</v>
       </c>
-      <c r="C99" s="73" t="s">
+      <c r="C99" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D99" s="73"/>
+      <c r="D99" s="69"/>
       <c r="E99" s="5" t="s">
         <v>1253</v>
       </c>
@@ -25087,10 +25144,10 @@
       <c r="B100" s="48" t="s">
         <v>1254</v>
       </c>
-      <c r="C100" s="73" t="s">
+      <c r="C100" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D100" s="73"/>
+      <c r="D100" s="69"/>
       <c r="E100" s="5" t="s">
         <v>1255</v>
       </c>
@@ -25104,10 +25161,10 @@
       <c r="B101" s="48" t="s">
         <v>1256</v>
       </c>
-      <c r="C101" s="73" t="s">
+      <c r="C101" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D101" s="73"/>
+      <c r="D101" s="69"/>
       <c r="E101" s="5" t="s">
         <v>1257</v>
       </c>
@@ -25121,10 +25178,10 @@
       <c r="B102" s="48" t="s">
         <v>1258</v>
       </c>
-      <c r="C102" s="73" t="s">
+      <c r="C102" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D102" s="73"/>
+      <c r="D102" s="69"/>
       <c r="E102" s="5" t="s">
         <v>1251</v>
       </c>
@@ -25138,10 +25195,10 @@
       <c r="B103" s="48" t="s">
         <v>1259</v>
       </c>
-      <c r="C103" s="73" t="s">
+      <c r="C103" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D103" s="73"/>
+      <c r="D103" s="69"/>
       <c r="E103" s="5" t="s">
         <v>1253</v>
       </c>
@@ -25155,10 +25212,10 @@
       <c r="B104" s="48" t="s">
         <v>1260</v>
       </c>
-      <c r="C104" s="73" t="s">
+      <c r="C104" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D104" s="73"/>
+      <c r="D104" s="69"/>
       <c r="E104" s="5" t="s">
         <v>1255</v>
       </c>
@@ -25172,10 +25229,10 @@
       <c r="B105" s="48" t="s">
         <v>1261</v>
       </c>
-      <c r="C105" s="73" t="s">
+      <c r="C105" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D105" s="73"/>
+      <c r="D105" s="69"/>
       <c r="E105" s="5" t="s">
         <v>1257</v>
       </c>
@@ -25189,10 +25246,10 @@
       <c r="B106" s="48" t="s">
         <v>1262</v>
       </c>
-      <c r="C106" s="73" t="s">
+      <c r="C106" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D106" s="73"/>
+      <c r="D106" s="69"/>
       <c r="E106" s="5" t="s">
         <v>1263</v>
       </c>
@@ -25206,10 +25263,10 @@
       <c r="B107" s="48" t="s">
         <v>1264</v>
       </c>
-      <c r="C107" s="73" t="s">
+      <c r="C107" s="69" t="s">
         <v>1276</v>
       </c>
-      <c r="D107" s="73"/>
+      <c r="D107" s="69"/>
       <c r="E107" s="5" t="s">
         <v>1265</v>
       </c>
@@ -25220,48 +25277,109 @@
     </row>
   </sheetData>
   <mergeCells count="169">
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F104:I104"/>
+    <mergeCell ref="F105:I105"/>
+    <mergeCell ref="F106:I106"/>
+    <mergeCell ref="F107:I107"/>
+    <mergeCell ref="F99:I99"/>
+    <mergeCell ref="F100:I100"/>
+    <mergeCell ref="F101:I101"/>
+    <mergeCell ref="F102:I102"/>
+    <mergeCell ref="F103:I103"/>
+    <mergeCell ref="F94:I94"/>
+    <mergeCell ref="F95:I95"/>
+    <mergeCell ref="F96:I96"/>
+    <mergeCell ref="F97:I97"/>
+    <mergeCell ref="F98:I98"/>
+    <mergeCell ref="F89:I89"/>
+    <mergeCell ref="F90:I90"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="F92:I92"/>
+    <mergeCell ref="F93:I93"/>
+    <mergeCell ref="F84:I84"/>
+    <mergeCell ref="F85:I85"/>
+    <mergeCell ref="F86:I86"/>
+    <mergeCell ref="F87:I87"/>
+    <mergeCell ref="F88:I88"/>
+    <mergeCell ref="F79:I79"/>
+    <mergeCell ref="F80:I80"/>
+    <mergeCell ref="F81:I81"/>
+    <mergeCell ref="F82:I82"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="F66:I66"/>
+    <mergeCell ref="F67:I67"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F74:I74"/>
+    <mergeCell ref="F75:I75"/>
+    <mergeCell ref="F76:I76"/>
+    <mergeCell ref="F77:I77"/>
+    <mergeCell ref="F78:I78"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="F70:I70"/>
+    <mergeCell ref="F71:I71"/>
+    <mergeCell ref="F72:I72"/>
+    <mergeCell ref="F73:I73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
     <mergeCell ref="C58:D58"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="C60:D60"/>
@@ -25286,109 +25404,48 @@
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="F44:I44"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F74:I74"/>
-    <mergeCell ref="F75:I75"/>
-    <mergeCell ref="F76:I76"/>
-    <mergeCell ref="F77:I77"/>
-    <mergeCell ref="F78:I78"/>
-    <mergeCell ref="F69:I69"/>
-    <mergeCell ref="F70:I70"/>
-    <mergeCell ref="F71:I71"/>
-    <mergeCell ref="F72:I72"/>
-    <mergeCell ref="F73:I73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F65:I65"/>
-    <mergeCell ref="F66:I66"/>
-    <mergeCell ref="F67:I67"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F84:I84"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="F86:I86"/>
-    <mergeCell ref="F87:I87"/>
-    <mergeCell ref="F88:I88"/>
-    <mergeCell ref="F79:I79"/>
-    <mergeCell ref="F80:I80"/>
-    <mergeCell ref="F81:I81"/>
-    <mergeCell ref="F82:I82"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="F94:I94"/>
-    <mergeCell ref="F95:I95"/>
-    <mergeCell ref="F96:I96"/>
-    <mergeCell ref="F97:I97"/>
-    <mergeCell ref="F98:I98"/>
-    <mergeCell ref="F89:I89"/>
-    <mergeCell ref="F90:I90"/>
-    <mergeCell ref="F91:I91"/>
-    <mergeCell ref="F92:I92"/>
-    <mergeCell ref="F93:I93"/>
-    <mergeCell ref="F104:I104"/>
-    <mergeCell ref="F105:I105"/>
-    <mergeCell ref="F106:I106"/>
-    <mergeCell ref="F107:I107"/>
-    <mergeCell ref="F99:I99"/>
-    <mergeCell ref="F100:I100"/>
-    <mergeCell ref="F101:I101"/>
-    <mergeCell ref="F102:I102"/>
-    <mergeCell ref="F103:I103"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F29:I29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27890,210 +27947,210 @@
         <v>1035</v>
       </c>
       <c r="D14" s="67"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72" t="s">
+      <c r="E14" s="70"/>
+      <c r="F14" s="73" t="s">
         <v>462</v>
       </c>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="75" t="s">
+      <c r="A15" s="74" t="s">
         <v>1036</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>1037</v>
       </c>
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="71" t="s">
         <v>1038</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="70"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="72"/>
       <c r="F15" s="68"/>
       <c r="G15" s="66"/>
       <c r="H15" s="66"/>
       <c r="I15" s="66"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="75"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="42" t="s">
         <v>1039</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="71" t="s">
         <v>1040</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="70"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="72"/>
       <c r="F16" s="68"/>
       <c r="G16" s="66"/>
       <c r="H16" s="66"/>
       <c r="I16" s="66"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
+      <c r="A17" s="74"/>
       <c r="B17" s="42" t="s">
         <v>1041</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="71" t="s">
         <v>1042</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="70"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="72"/>
       <c r="F17" s="68"/>
       <c r="G17" s="66"/>
       <c r="H17" s="66"/>
       <c r="I17" s="66"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="75"/>
+      <c r="A18" s="74"/>
       <c r="B18" s="42" t="s">
         <v>1043</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="72" t="s">
         <v>1044</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
       <c r="F18" s="68"/>
       <c r="G18" s="66"/>
       <c r="H18" s="66"/>
       <c r="I18" s="66"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
+      <c r="A19" s="74"/>
       <c r="B19" s="42" t="s">
         <v>1045</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="72" t="s">
         <v>1046</v>
       </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
       <c r="F19" s="68"/>
       <c r="G19" s="66"/>
       <c r="H19" s="66"/>
       <c r="I19" s="66"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="75" t="s">
         <v>1047</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>1048</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="72" t="s">
         <v>1049</v>
       </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
       <c r="F20" s="68"/>
       <c r="G20" s="66"/>
       <c r="H20" s="66"/>
       <c r="I20" s="66"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="76"/>
+      <c r="A21" s="75"/>
       <c r="B21" s="42" t="s">
         <v>1050</v>
       </c>
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="72" t="s">
         <v>1051</v>
       </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
       <c r="F21" s="68"/>
       <c r="G21" s="66"/>
       <c r="H21" s="66"/>
       <c r="I21" s="66"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="76"/>
+      <c r="A22" s="75"/>
       <c r="B22" s="42" t="s">
         <v>1052</v>
       </c>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="72" t="s">
         <v>1053</v>
       </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
       <c r="F22" s="68"/>
       <c r="G22" s="66"/>
       <c r="H22" s="66"/>
       <c r="I22" s="66"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="76"/>
+      <c r="A23" s="75"/>
       <c r="B23" s="42" t="s">
         <v>1054</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="72" t="s">
         <v>1055</v>
       </c>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
       <c r="F23" s="68"/>
       <c r="G23" s="66"/>
       <c r="H23" s="66"/>
       <c r="I23" s="66"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="76" t="s">
+      <c r="A24" s="75" t="s">
         <v>1056</v>
       </c>
       <c r="B24" s="42" t="s">
         <v>1048</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="72" t="s">
         <v>1057</v>
       </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
       <c r="F24" s="68"/>
       <c r="G24" s="66"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="76"/>
+      <c r="A25" s="75"/>
       <c r="B25" s="42" t="s">
         <v>1058</v>
       </c>
-      <c r="C25" s="70" t="s">
+      <c r="C25" s="72" t="s">
         <v>1059</v>
       </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
       <c r="F25" s="68"/>
       <c r="G25" s="66"/>
       <c r="H25" s="66"/>
       <c r="I25" s="66"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="76"/>
+      <c r="A26" s="75"/>
       <c r="B26" s="42" t="s">
         <v>1052</v>
       </c>
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="72" t="s">
         <v>1060</v>
       </c>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
       <c r="F26" s="68"/>
       <c r="G26" s="66"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="76"/>
+      <c r="A27" s="75"/>
       <c r="B27" s="42" t="s">
         <v>1054</v>
       </c>
-      <c r="C27" s="74" t="s">
+      <c r="C27" s="76" t="s">
         <v>1061</v>
       </c>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
       <c r="F27" s="68"/>
       <c r="G27" s="66"/>
       <c r="H27" s="66"/>
@@ -28106,137 +28163,137 @@
       <c r="B28" s="45" t="s">
         <v>1063</v>
       </c>
-      <c r="C28" s="74" t="s">
+      <c r="C28" s="76" t="s">
         <v>1064</v>
       </c>
-      <c r="D28" s="74"/>
-      <c r="E28" s="74"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
       <c r="F28" s="68"/>
       <c r="G28" s="66"/>
       <c r="H28" s="66"/>
       <c r="I28" s="66"/>
     </row>
     <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="76" t="s">
+      <c r="A29" s="75" t="s">
         <v>1065</v>
       </c>
       <c r="B29" s="45" t="s">
         <v>1066</v>
       </c>
-      <c r="C29" s="74" t="s">
+      <c r="C29" s="76" t="s">
         <v>1067</v>
       </c>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
       <c r="F29" s="68"/>
       <c r="G29" s="66"/>
       <c r="H29" s="66"/>
       <c r="I29" s="66"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="76"/>
+      <c r="A30" s="75"/>
       <c r="B30" s="45" t="s">
         <v>1068</v>
       </c>
-      <c r="C30" s="74" t="s">
+      <c r="C30" s="76" t="s">
         <v>1069</v>
       </c>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
       <c r="F30" s="68"/>
       <c r="G30" s="66"/>
       <c r="H30" s="66"/>
       <c r="I30" s="66"/>
     </row>
     <row r="31" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="75" t="s">
         <v>1070</v>
       </c>
       <c r="B31" s="45" t="s">
         <v>1071</v>
       </c>
-      <c r="C31" s="74" t="s">
+      <c r="C31" s="76" t="s">
         <v>1072</v>
       </c>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
       <c r="F31" s="68"/>
       <c r="G31" s="66"/>
       <c r="H31" s="66"/>
       <c r="I31" s="66"/>
     </row>
     <row r="32" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
+      <c r="A32" s="75"/>
       <c r="B32" s="45" t="s">
         <v>1073</v>
       </c>
-      <c r="C32" s="74" t="s">
+      <c r="C32" s="76" t="s">
         <v>1074</v>
       </c>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
       <c r="F32" s="68"/>
       <c r="G32" s="66"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="76" t="s">
+      <c r="A33" s="75" t="s">
         <v>1075</v>
       </c>
       <c r="B33" s="45" t="s">
         <v>1048</v>
       </c>
-      <c r="C33" s="74" t="s">
+      <c r="C33" s="76" t="s">
         <v>1076</v>
       </c>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
       <c r="F33" s="68"/>
       <c r="G33" s="66"/>
       <c r="H33" s="66"/>
       <c r="I33" s="66"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="76"/>
+      <c r="A34" s="75"/>
       <c r="B34" s="45" t="s">
         <v>1077</v>
       </c>
-      <c r="C34" s="74" t="s">
+      <c r="C34" s="76" t="s">
         <v>1078</v>
       </c>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
       <c r="F34" s="68"/>
       <c r="G34" s="66"/>
       <c r="H34" s="66"/>
       <c r="I34" s="66"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="76"/>
+      <c r="A35" s="75"/>
       <c r="B35" s="45" t="s">
         <v>1079</v>
       </c>
-      <c r="C35" s="74" t="s">
+      <c r="C35" s="76" t="s">
         <v>1080</v>
       </c>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
       <c r="F35" s="68"/>
       <c r="G35" s="66"/>
       <c r="H35" s="66"/>
       <c r="I35" s="66"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="76"/>
+      <c r="A36" s="75"/>
       <c r="B36" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="74" t="s">
+      <c r="C36" s="76" t="s">
         <v>1081</v>
       </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
       <c r="F36" s="68"/>
       <c r="G36" s="66"/>
       <c r="H36" s="66"/>
@@ -28249,97 +28306,97 @@
       <c r="B37" s="45" t="s">
         <v>1063</v>
       </c>
-      <c r="C37" s="74" t="s">
+      <c r="C37" s="76" t="s">
         <v>1083</v>
       </c>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
       <c r="F37" s="68"/>
       <c r="G37" s="66"/>
       <c r="H37" s="66"/>
       <c r="I37" s="66"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="76" t="s">
+      <c r="A38" s="75" t="s">
         <v>1084</v>
       </c>
       <c r="B38" s="45" t="s">
         <v>1085</v>
       </c>
-      <c r="C38" s="74" t="s">
+      <c r="C38" s="76" t="s">
         <v>1086</v>
       </c>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
       <c r="F38" s="68"/>
       <c r="G38" s="66"/>
       <c r="H38" s="66"/>
       <c r="I38" s="66"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="76"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="45" t="s">
         <v>1087</v>
       </c>
-      <c r="C39" s="74" t="s">
+      <c r="C39" s="76" t="s">
         <v>1088</v>
       </c>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
       <c r="F39" s="68"/>
       <c r="G39" s="66"/>
       <c r="H39" s="66"/>
       <c r="I39" s="66"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="76"/>
+      <c r="A40" s="75"/>
       <c r="B40" s="45" t="s">
         <v>1089</v>
       </c>
-      <c r="C40" s="74" t="s">
+      <c r="C40" s="76" t="s">
         <v>1090</v>
       </c>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
       <c r="F40" s="68"/>
       <c r="G40" s="66"/>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="76" t="s">
+      <c r="A41" s="75" t="s">
         <v>1091</v>
       </c>
       <c r="B41" s="45" t="s">
         <v>1092</v>
       </c>
-      <c r="C41" s="74" t="s">
+      <c r="C41" s="76" t="s">
         <v>1093</v>
       </c>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
       <c r="F41" s="68"/>
       <c r="G41" s="66"/>
       <c r="H41" s="66"/>
       <c r="I41" s="66"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="76"/>
+      <c r="A42" s="75"/>
       <c r="B42" s="45" t="s">
         <v>1094</v>
       </c>
-      <c r="C42" s="74" t="s">
+      <c r="C42" s="76" t="s">
         <v>1095</v>
       </c>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
       <c r="F42" s="68"/>
       <c r="G42" s="66"/>
       <c r="H42" s="66"/>
       <c r="I42" s="66"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="76"/>
+      <c r="A43" s="75"/>
       <c r="B43" s="45" t="s">
         <v>1096</v>
       </c>
@@ -28354,47 +28411,47 @@
       <c r="I43" s="66"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="76"/>
+      <c r="A44" s="75"/>
       <c r="B44" s="45" t="s">
         <v>1098</v>
       </c>
-      <c r="C44" s="75" t="s">
+      <c r="C44" s="74" t="s">
         <v>1099</v>
       </c>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
       <c r="F44" s="68"/>
       <c r="G44" s="66"/>
       <c r="H44" s="66"/>
       <c r="I44" s="66"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="76" t="s">
+      <c r="A45" s="75" t="s">
         <v>1100</v>
       </c>
       <c r="B45" s="45" t="s">
         <v>1101</v>
       </c>
-      <c r="C45" s="75" t="s">
+      <c r="C45" s="74" t="s">
         <v>1102</v>
       </c>
-      <c r="D45" s="75"/>
-      <c r="E45" s="75"/>
+      <c r="D45" s="74"/>
+      <c r="E45" s="74"/>
       <c r="F45" s="68"/>
       <c r="G45" s="66"/>
       <c r="H45" s="66"/>
       <c r="I45" s="66"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="76"/>
+      <c r="A46" s="75"/>
       <c r="B46" s="45" t="s">
         <v>1103</v>
       </c>
-      <c r="C46" s="75" t="s">
+      <c r="C46" s="74" t="s">
         <v>1104</v>
       </c>
-      <c r="D46" s="75"/>
-      <c r="E46" s="75"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
       <c r="F46" s="68"/>
       <c r="G46" s="66"/>
       <c r="H46" s="66"/>
@@ -28407,11 +28464,11 @@
       <c r="B47" s="45" t="s">
         <v>1063</v>
       </c>
-      <c r="C47" s="75" t="s">
+      <c r="C47" s="74" t="s">
         <v>1106</v>
       </c>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="74"/>
       <c r="F47" s="68"/>
       <c r="G47" s="66"/>
       <c r="H47" s="66"/>
@@ -28424,165 +28481,165 @@
       <c r="B48" s="45" t="s">
         <v>1108</v>
       </c>
-      <c r="C48" s="75" t="s">
+      <c r="C48" s="74" t="s">
         <v>1109</v>
       </c>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
       <c r="F48" s="68"/>
       <c r="G48" s="66"/>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="76" t="s">
+      <c r="A49" s="75" t="s">
         <v>1110</v>
       </c>
       <c r="B49" s="45" t="s">
         <v>1111</v>
       </c>
-      <c r="C49" s="75" t="s">
+      <c r="C49" s="74" t="s">
         <v>1112</v>
       </c>
-      <c r="D49" s="75"/>
-      <c r="E49" s="75"/>
+      <c r="D49" s="74"/>
+      <c r="E49" s="74"/>
       <c r="F49" s="68"/>
       <c r="G49" s="66"/>
       <c r="H49" s="66"/>
       <c r="I49" s="66"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="76"/>
+      <c r="A50" s="75"/>
       <c r="B50" s="45" t="s">
         <v>1113</v>
       </c>
-      <c r="C50" s="75" t="s">
+      <c r="C50" s="74" t="s">
         <v>1114</v>
       </c>
-      <c r="D50" s="75"/>
-      <c r="E50" s="75"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="74"/>
       <c r="F50" s="68"/>
       <c r="G50" s="66"/>
       <c r="H50" s="66"/>
       <c r="I50" s="66"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="76"/>
+      <c r="A51" s="75"/>
       <c r="B51" s="45" t="s">
         <v>1058</v>
       </c>
-      <c r="C51" s="75" t="s">
+      <c r="C51" s="74" t="s">
         <v>1115</v>
       </c>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="74"/>
       <c r="F51" s="68"/>
       <c r="G51" s="66"/>
       <c r="H51" s="66"/>
       <c r="I51" s="66"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="76"/>
+      <c r="A52" s="75"/>
       <c r="B52" s="45" t="s">
         <v>1116</v>
       </c>
-      <c r="C52" s="75" t="s">
+      <c r="C52" s="74" t="s">
         <v>1117</v>
       </c>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="74"/>
       <c r="F52" s="68"/>
       <c r="G52" s="66"/>
       <c r="H52" s="66"/>
       <c r="I52" s="66"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="76"/>
+      <c r="A53" s="75"/>
       <c r="B53" s="45" t="s">
         <v>1054</v>
       </c>
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="74" t="s">
         <v>1118</v>
       </c>
-      <c r="D53" s="75"/>
-      <c r="E53" s="75"/>
+      <c r="D53" s="74"/>
+      <c r="E53" s="74"/>
       <c r="F53" s="68"/>
       <c r="G53" s="66"/>
       <c r="H53" s="66"/>
       <c r="I53" s="66"/>
     </row>
     <row r="54" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="76" t="s">
+      <c r="A54" s="75" t="s">
         <v>1119</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="74" t="s">
         <v>1121</v>
       </c>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
       <c r="F54" s="68"/>
       <c r="G54" s="66"/>
       <c r="H54" s="66"/>
       <c r="I54" s="66"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="76"/>
+      <c r="A55" s="75"/>
       <c r="B55" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="C55" s="75" t="s">
+      <c r="C55" s="74" t="s">
         <v>1123</v>
       </c>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
       <c r="F55" s="68"/>
       <c r="G55" s="66"/>
       <c r="H55" s="66"/>
       <c r="I55" s="66"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="76"/>
+      <c r="A56" s="75"/>
       <c r="B56" s="5" t="s">
         <v>1124</v>
       </c>
-      <c r="C56" s="75" t="s">
+      <c r="C56" s="74" t="s">
         <v>1125</v>
       </c>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="74"/>
       <c r="F56" s="68"/>
       <c r="G56" s="66"/>
       <c r="H56" s="66"/>
       <c r="I56" s="66"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="76"/>
+      <c r="A57" s="75"/>
       <c r="B57" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="C57" s="75" t="s">
+      <c r="C57" s="74" t="s">
         <v>1127</v>
       </c>
-      <c r="D57" s="75"/>
-      <c r="E57" s="75"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="74"/>
       <c r="F57" s="68"/>
       <c r="G57" s="66"/>
       <c r="H57" s="66"/>
       <c r="I57" s="66"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="76"/>
+      <c r="A58" s="75"/>
       <c r="B58" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="C58" s="75" t="s">
+      <c r="C58" s="74" t="s">
         <v>1129</v>
       </c>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75"/>
+      <c r="D58" s="74"/>
+      <c r="E58" s="74"/>
       <c r="F58" s="68"/>
       <c r="G58" s="66"/>
       <c r="H58" s="66"/>
@@ -28595,88 +28652,88 @@
       <c r="B59" s="5" t="s">
         <v>1063</v>
       </c>
-      <c r="C59" s="75" t="s">
+      <c r="C59" s="74" t="s">
         <v>1131</v>
       </c>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="74"/>
       <c r="F59" s="68"/>
       <c r="G59" s="66"/>
       <c r="H59" s="66"/>
       <c r="I59" s="66"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="76" t="s">
+      <c r="A60" s="75" t="s">
         <v>1132</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>1133</v>
       </c>
-      <c r="C60" s="75" t="s">
+      <c r="C60" s="74" t="s">
         <v>1134</v>
       </c>
-      <c r="D60" s="75"/>
-      <c r="E60" s="75"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="74"/>
       <c r="F60" s="68"/>
       <c r="G60" s="66"/>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="76"/>
+      <c r="A61" s="75"/>
       <c r="B61" s="5" t="s">
         <v>1135</v>
       </c>
-      <c r="C61" s="75" t="s">
+      <c r="C61" s="74" t="s">
         <v>1136</v>
       </c>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="74"/>
       <c r="F61" s="68"/>
       <c r="G61" s="66"/>
       <c r="H61" s="66"/>
       <c r="I61" s="66"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="76"/>
+      <c r="A62" s="75"/>
       <c r="B62" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="C62" s="75" t="s">
+      <c r="C62" s="74" t="s">
         <v>1138</v>
       </c>
-      <c r="D62" s="75"/>
-      <c r="E62" s="75"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="74"/>
       <c r="F62" s="68"/>
       <c r="G62" s="66"/>
       <c r="H62" s="66"/>
       <c r="I62" s="66"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="76"/>
+      <c r="A63" s="75"/>
       <c r="B63" s="5" t="s">
         <v>1139</v>
       </c>
-      <c r="C63" s="75" t="s">
+      <c r="C63" s="74" t="s">
         <v>1140</v>
       </c>
-      <c r="D63" s="75"/>
-      <c r="E63" s="75"/>
+      <c r="D63" s="74"/>
+      <c r="E63" s="74"/>
       <c r="F63" s="68"/>
       <c r="G63" s="66"/>
       <c r="H63" s="66"/>
       <c r="I63" s="66"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="76"/>
+      <c r="A64" s="75"/>
       <c r="B64" s="5" t="s">
         <v>1141</v>
       </c>
-      <c r="C64" s="75" t="s">
+      <c r="C64" s="74" t="s">
         <v>1142</v>
       </c>
-      <c r="D64" s="75"/>
-      <c r="E64" s="75"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="74"/>
       <c r="F64" s="68"/>
       <c r="G64" s="66"/>
       <c r="H64" s="66"/>
@@ -28684,36 +28741,66 @@
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F52:I52"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F30:I30"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="C63:E63"/>
     <mergeCell ref="C64:E64"/>
     <mergeCell ref="A54:A58"/>
@@ -28738,66 +28825,36 @@
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="C52:E52"/>
     <mergeCell ref="C53:E53"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F28:I28"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F52:I52"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -29290,11 +29347,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
@@ -29309,6 +29361,11 @@
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -30079,6 +30136,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="F17:I17"/>
@@ -30091,13 +30155,6 @@
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F29:I29"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -30463,6 +30520,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="F9:I9"/>
@@ -30470,18 +30539,6 @@
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="F11:I11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -30943,19 +31000,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="F23:I23"/>
@@ -30969,6 +31013,19 @@
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:I10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -32036,29 +32093,33 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="F60:I60"/>
-    <mergeCell ref="F61:I61"/>
-    <mergeCell ref="F62:I62"/>
-    <mergeCell ref="F63:I63"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="F56:I56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:I57"/>
-    <mergeCell ref="F58:I58"/>
-    <mergeCell ref="F59:I59"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F46:I46"/>
+    <mergeCell ref="F47:I47"/>
+    <mergeCell ref="F48:I48"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F44:I44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="F45:I45"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="F42:I42"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:I34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="F32:I32"/>
     <mergeCell ref="C24:D24"/>
@@ -32072,33 +32133,29 @@
     <mergeCell ref="F30:I30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:I31"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="F42:I42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="F43:I43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F46:I46"/>
-    <mergeCell ref="F47:I47"/>
-    <mergeCell ref="F48:I48"/>
-    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="F56:I56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:I57"/>
+    <mergeCell ref="F58:I58"/>
+    <mergeCell ref="F59:I59"/>
+    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F61:I61"/>
+    <mergeCell ref="F62:I62"/>
+    <mergeCell ref="F63:I63"/>
+    <mergeCell ref="F64:I64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32578,13 +32635,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:I15"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C20:D20"/>
@@ -32595,6 +32645,13 @@
     <mergeCell ref="F18:I18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="F19:I19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:I15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -32997,6 +33054,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F16:I16"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="C20:D20"/>
@@ -33009,11 +33071,6 @@
     <mergeCell ref="F20:I20"/>
     <mergeCell ref="F17:I17"/>
     <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F12:I12"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -33045,26 +33102,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="eda01c43-580c-44af-a5fd-4ea1802e476c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004592A3ADBB772D4689FCD56C8516F45D" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e6dee92c918a6173969cc6829137ba01">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c" xmlns:ns3="eda01c43-580c-44af-a5fd-4ea1802e476c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2e0be94b10bd652582aed8d62fec2d74" ns2:_="" ns3:_="">
     <xsd:import namespace="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c"/>
@@ -33293,10 +33330,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="eda01c43-580c-44af-a5fd-4ea1802e476c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB40FF6F-009E-4D48-B4D3-33D1A3C62497}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0A127A-D0D0-4182-84ED-7D64B945D928}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c"/>
+    <ds:schemaRef ds:uri="eda01c43-580c-44af-a5fd-4ea1802e476c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -33319,20 +33387,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0A127A-D0D0-4182-84ED-7D64B945D928}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB40FF6F-009E-4D48-B4D3-33D1A3C62497}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9a1da51d-87f1-4c78-b9e6-a6488d1ad35c"/>
-    <ds:schemaRef ds:uri="eda01c43-580c-44af-a5fd-4ea1802e476c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>